--- a/artfynd/A 39562-2026 artfynd.xlsx
+++ b/artfynd/A 39562-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ55"/>
+  <dimension ref="A1:AZ70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1102,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120590202</v>
+        <v>136866766</v>
       </c>
       <c r="B6" t="n">
-        <v>92147</v>
+        <v>79142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,40 +1113,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1101</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, söder om, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616867</v>
+        <v>616604</v>
       </c>
       <c r="R6" t="n">
-        <v>6651610</v>
+        <v>6651495</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1170,17 +1167,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På av mossa övervuxen granstubbe</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,34 +1191,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120590202</t>
+          <t>https://artportalen.se/Sighting/136866766</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120760977</v>
+        <v>136866780</v>
       </c>
       <c r="B7" t="n">
-        <v>92147</v>
+        <v>79142</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1224,48 +1225,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1101</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, syd om, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616848</v>
+        <v>616665</v>
       </c>
       <c r="R7" t="n">
-        <v>6651616</v>
+        <v>6651693</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1289,12 +1279,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1303,87 +1303,74 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stump</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120760977</t>
+          <t>https://artportalen.se/Sighting/136866780</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120513434</v>
+        <v>120590202</v>
       </c>
       <c r="B8" t="n">
-        <v>96601</v>
+        <v>92147</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2170</v>
+        <v>1101</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stora Hålsjön syd om, Upl</t>
+          <t>Stora Hålsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616954</v>
+        <v>616867</v>
       </c>
       <c r="R8" t="n">
-        <v>6651400</v>
+        <v>6651610</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1410,19 +1397,14 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:02</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På av mossa övervuxen granstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,68 +1413,80 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120513434</t>
+          <t>https://artportalen.se/Sighting/120590202</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120518741</v>
+        <v>120760977</v>
       </c>
       <c r="B9" t="n">
-        <v>96601</v>
+        <v>92147</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2170</v>
+        <v>1101</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stora Hålsjön syd om, Upl</t>
+          <t>Stora Hålsjön, syd om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616852</v>
+        <v>616848</v>
       </c>
       <c r="R9" t="n">
-        <v>6651662</v>
+        <v>6651616</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,92 +1516,98 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120518741</t>
+          <t>https://artportalen.se/Sighting/120760977</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120543211</v>
+        <v>136866767</v>
       </c>
       <c r="B10" t="n">
-        <v>96601</v>
+        <v>92749</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2170</v>
+        <v>1101</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616936</v>
+        <v>616676</v>
       </c>
       <c r="R10" t="n">
-        <v>6651400</v>
+        <v>6651546</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,12 +1631,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,31 +1657,51 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elin Sjögren Englund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elin Sjögren Englund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120543211</t>
+          <t>https://artportalen.se/Sighting/136866767</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120761198</v>
+        <v>136866777</v>
       </c>
       <c r="B11" t="n">
-        <v>93197</v>
+        <v>92113</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1679,48 +1709,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, syd om, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>616726</v>
+        <v>616587</v>
       </c>
       <c r="R11" t="n">
-        <v>6651651</v>
+        <v>6651708</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1744,12 +1763,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,77 +1787,71 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120761198</t>
+          <t>https://artportalen.se/Sighting/136866777</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120519500</v>
+        <v>136866772</v>
       </c>
       <c r="B12" t="n">
-        <v>91282</v>
+        <v>92292</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5685</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>616604</v>
+        <v>616702</v>
       </c>
       <c r="R12" t="n">
-        <v>6651608</v>
+        <v>6651664</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1852,22 +1875,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,27 +1905,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519500</t>
+          <t>https://artportalen.se/Sighting/136866772</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120551261</v>
+        <v>120513434</v>
       </c>
       <c r="B13" t="n">
-        <v>91282</v>
+        <v>96601</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,37 +1933,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5685</v>
+        <v>2170</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön syd om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>616607</v>
+        <v>616954</v>
       </c>
       <c r="R13" t="n">
-        <v>6651614</v>
+        <v>6651400</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1967,9 +1990,19 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1984,65 +2017,65 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551261</t>
+          <t>https://artportalen.se/Sighting/120513434</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120511104</v>
+        <v>120518741</v>
       </c>
       <c r="B14" t="n">
-        <v>93235</v>
+        <v>96601</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>2170</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
+          <t>Stora Hålsjön syd om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>616704</v>
+        <v>616852</v>
       </c>
       <c r="R14" t="n">
-        <v>6651675</v>
+        <v>6651662</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2071,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2081,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,74 +2129,65 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511104</t>
+          <t>https://artportalen.se/Sighting/120518741</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120511417</v>
+        <v>120543211</v>
       </c>
       <c r="B15" t="n">
-        <v>93235</v>
+        <v>96601</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>2170</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>616708</v>
+        <v>616936</v>
       </c>
       <c r="R15" t="n">
-        <v>6651685</v>
+        <v>6651400</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2190,19 +2214,9 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-20</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2217,74 +2231,65 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Elin Sjögren Englund</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Elin Sjögren Englund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511417</t>
+          <t>https://artportalen.se/Sighting/120543211</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120512327</v>
+        <v>136866774</v>
       </c>
       <c r="B16" t="n">
-        <v>93235</v>
+        <v>96831</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>2170</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stora Hålsjön syd om, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>616886</v>
+        <v>616698</v>
       </c>
       <c r="R16" t="n">
-        <v>6651550</v>
+        <v>6651745</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2308,22 +2313,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,27 +2343,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120512327</t>
+          <t>https://artportalen.se/Sighting/136866774</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120549502</v>
+        <v>120761198</v>
       </c>
       <c r="B17" t="n">
-        <v>93235</v>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,37 +2371,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, syd om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>616708</v>
+        <v>616726</v>
       </c>
       <c r="R17" t="n">
-        <v>6651552</v>
+        <v>6651651</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2441,71 +2454,73 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sofia Lundell</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sofia Lundell</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120549502</t>
+          <t>https://artportalen.se/Sighting/120761198</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120590195</v>
+        <v>120519500</v>
       </c>
       <c r="B18" t="n">
-        <v>93235</v>
+        <v>91282</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>5685</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, söder om, Upl</t>
+          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616874</v>
+        <v>616604</v>
       </c>
       <c r="R18" t="n">
-        <v>6651669</v>
+        <v>6651608</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2532,86 +2547,92 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120590195</t>
+          <t>https://artportalen.se/Sighting/120519500</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120590197</v>
+        <v>120551261</v>
       </c>
       <c r="B19" t="n">
-        <v>93235</v>
+        <v>91282</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>5685</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, söder om, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616705</v>
+        <v>616607</v>
       </c>
       <c r="R19" t="n">
-        <v>6651645</v>
+        <v>6651614</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2649,31 +2670,30 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120590197</t>
+          <t>https://artportalen.se/Sighting/120551261</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120590198</v>
+        <v>120511104</v>
       </c>
       <c r="B20" t="n">
         <v>93235</v>
@@ -2702,22 +2722,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, söder om, Upl</t>
+          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>616898</v>
+        <v>616704</v>
       </c>
       <c r="R20" t="n">
-        <v>6651543</v>
+        <v>6651675</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2744,42 +2761,51 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120590198</t>
+          <t>https://artportalen.se/Sighting/120511104</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120761144</v>
+        <v>120511417</v>
       </c>
       <c r="B21" t="n">
         <v>93235</v>
@@ -2809,7 +2835,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2817,18 +2843,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, syd om, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>616707</v>
+        <v>616708</v>
       </c>
       <c r="R21" t="n">
-        <v>6651675</v>
+        <v>6651685</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2858,50 +2882,54 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Tallskog på blockmark</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120761144</t>
+          <t>https://artportalen.se/Sighting/120511417</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120518661</v>
+        <v>120512327</v>
       </c>
       <c r="B22" t="n">
-        <v>79084</v>
+        <v>93235</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,27 +2937,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2938,10 +2970,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>616852</v>
+        <v>616886</v>
       </c>
       <c r="R22" t="n">
-        <v>6651662</v>
+        <v>6651550</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2973,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2983,12 +3015,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Flera fläckar utan apothecier och en klunga med apothecier!</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3014,16 +3041,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120518661</t>
+          <t>https://artportalen.se/Sighting/120512327</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120510603</v>
+        <v>120549502</v>
       </c>
       <c r="B23" t="n">
-        <v>79946</v>
+        <v>93235</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3031,34 +3058,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>616717</v>
+        <v>616708</v>
       </c>
       <c r="R23" t="n">
-        <v>6651623</v>
+        <v>6651552</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3088,54 +3118,45 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Sofia Lundell</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Sofia Lundell</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510603</t>
+          <t>https://artportalen.se/Sighting/120549502</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120518677</v>
+        <v>120590195</v>
       </c>
       <c r="B24" t="n">
-        <v>79946</v>
+        <v>93235</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3143,37 +3164,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stora Hålsjön syd om, Upl</t>
+          <t>Stora Hålsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>616852</v>
+        <v>616874</v>
       </c>
       <c r="R24" t="n">
-        <v>6651662</v>
+        <v>6651669</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3200,54 +3224,45 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120518677</t>
+          <t>https://artportalen.se/Sighting/120590195</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120518963</v>
+        <v>120590197</v>
       </c>
       <c r="B25" t="n">
-        <v>79946</v>
+        <v>93235</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3255,37 +3270,40 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stora Hålsjön syd om, Upl</t>
+          <t>Stora Hålsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>616658</v>
+        <v>616705</v>
       </c>
       <c r="R25" t="n">
-        <v>6651670</v>
+        <v>6651645</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3312,54 +3330,45 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120518963</t>
+          <t>https://artportalen.se/Sighting/120590197</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120519139</v>
+        <v>120590198</v>
       </c>
       <c r="B26" t="n">
-        <v>79946</v>
+        <v>93235</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,37 +3376,40 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stora Hålsjön syd om, Upl</t>
+          <t>Stora Hålsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>616625</v>
+        <v>616898</v>
       </c>
       <c r="R26" t="n">
-        <v>6651656</v>
+        <v>6651543</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3424,54 +3436,45 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:47</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:47</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519139</t>
+          <t>https://artportalen.se/Sighting/120590198</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120527703</v>
+        <v>120761144</v>
       </c>
       <c r="B27" t="n">
-        <v>79946</v>
+        <v>93235</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3479,40 +3482,48 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norr om Tarmlången, Upl</t>
+          <t>Stora Hålsjön, syd om, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>616650</v>
+        <v>616707</v>
       </c>
       <c r="R27" t="n">
-        <v>6651661</v>
+        <v>6651675</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3539,19 +3550,9 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-20</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3564,30 +3565,35 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Tallskog på blockmark</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120527703</t>
+          <t>https://artportalen.se/Sighting/120761144</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120543208</v>
+        <v>120518661</v>
       </c>
       <c r="B28" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3595,37 +3601,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön syd om, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>616888</v>
+        <v>616852</v>
       </c>
       <c r="R28" t="n">
-        <v>6651557</v>
+        <v>6651662</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3652,9 +3663,24 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Flera fläckar utan apothecier och en klunga med apothecier!</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3669,27 +3695,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Sjögren Englund</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Sjögren Englund</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120543208</t>
+          <t>https://artportalen.se/Sighting/120518661</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120549513</v>
+        <v>136866775</v>
       </c>
       <c r="B29" t="n">
-        <v>79946</v>
+        <v>79233</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3697,40 +3723,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>616740</v>
+        <v>616710</v>
       </c>
       <c r="R29" t="n">
-        <v>6651532</v>
+        <v>6651797</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3754,12 +3777,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3768,31 +3801,30 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Sofia Lundell</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sofia Lundell</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120549513</t>
+          <t>https://artportalen.se/Sighting/136866775</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120549579</v>
+        <v>120510603</v>
       </c>
       <c r="B30" t="n">
         <v>79946</v>
@@ -3821,19 +3853,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>616696</v>
+        <v>616717</v>
       </c>
       <c r="R30" t="n">
-        <v>6651548</v>
+        <v>6651623</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3863,42 +3892,51 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Sofia Lundell</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sofia Lundell</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120549579</t>
+          <t>https://artportalen.se/Sighting/120510603</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120551237</v>
+        <v>120518677</v>
       </c>
       <c r="B31" t="n">
         <v>79946</v>
@@ -3929,17 +3967,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön syd om, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>616697</v>
+        <v>616852</v>
       </c>
       <c r="R31" t="n">
-        <v>6651696</v>
+        <v>6651662</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3966,9 +4004,19 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3983,70 +4031,65 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551237</t>
+          <t>https://artportalen.se/Sighting/120518677</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120510212</v>
+        <v>120518963</v>
       </c>
       <c r="B32" t="n">
-        <v>57141</v>
+        <v>79946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön syd om, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>616701</v>
+        <v>616658</v>
       </c>
       <c r="R32" t="n">
-        <v>6651514</v>
+        <v>6651670</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4075,7 +4118,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4085,12 +4128,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Fjäderpenna på häll.</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4116,16 +4154,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510212</t>
+          <t>https://artportalen.se/Sighting/120518963</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120510599</v>
+        <v>120519139</v>
       </c>
       <c r="B33" t="n">
-        <v>6284</v>
+        <v>79946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4133,42 +4171,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100524</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovlig flatbagge</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Calitys scabra</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Thunberg, 1784)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Stora Hålsjön syd om, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>616710</v>
+        <v>616625</v>
       </c>
       <c r="R33" t="n">
-        <v>6651594</v>
+        <v>6651656</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4195,92 +4228,95 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510599</t>
+          <t>https://artportalen.se/Sighting/120519139</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120541190</v>
+        <v>120527703</v>
       </c>
       <c r="B34" t="n">
-        <v>44177</v>
+        <v>79946</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>101735</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Norr om Tarmlången, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>616925</v>
+        <v>616650</v>
       </c>
       <c r="R34" t="n">
-        <v>6651481</v>
+        <v>6651661</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4307,9 +4343,19 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4325,74 +4371,65 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541190</t>
+          <t>https://artportalen.se/Sighting/120527703</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120510178</v>
+        <v>120543208</v>
       </c>
       <c r="B35" t="n">
-        <v>5482</v>
+        <v>79946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>616618</v>
+        <v>616888</v>
       </c>
       <c r="R35" t="n">
-        <v>6651514</v>
+        <v>6651557</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4430,78 +4467,71 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Elin Sjögren Englund</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Elin Sjögren Englund</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510178</t>
+          <t>https://artportalen.se/Sighting/120543208</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120510277</v>
+        <v>120549513</v>
       </c>
       <c r="B36" t="n">
-        <v>5482</v>
+        <v>79946</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>616622</v>
+        <v>616740</v>
       </c>
       <c r="R36" t="n">
-        <v>6651505</v>
+        <v>6651532</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4549,71 +4579,65 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Sofia Lundell</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Sofia Lundell</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510277</t>
+          <t>https://artportalen.se/Sighting/120549513</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120511479</v>
+        <v>120549579</v>
       </c>
       <c r="B37" t="n">
-        <v>5482</v>
+        <v>79946</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>616731</v>
+        <v>616696</v>
       </c>
       <c r="R37" t="n">
-        <v>6651699</v>
+        <v>6651548</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4661,74 +4685,65 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Sofia Lundell</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Sofia Lundell</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511479</t>
+          <t>https://artportalen.se/Sighting/120549579</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120512577</v>
+        <v>120551237</v>
       </c>
       <c r="B38" t="n">
-        <v>5482</v>
+        <v>79946</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>616900</v>
+        <v>616697</v>
       </c>
       <c r="R38" t="n">
-        <v>6651584</v>
+        <v>6651696</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4766,81 +4781,71 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120512577</t>
+          <t>https://artportalen.se/Sighting/120551237</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120519343</v>
+        <v>136866769</v>
       </c>
       <c r="B39" t="n">
-        <v>5482</v>
+        <v>80095</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>616603</v>
+        <v>616663</v>
       </c>
       <c r="R39" t="n">
-        <v>6651619</v>
+        <v>6651632</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4864,12 +4869,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4878,72 +4893,76 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519343</t>
+          <t>https://artportalen.se/Sighting/136866769</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120590194</v>
+        <v>136866771</v>
       </c>
       <c r="B40" t="n">
-        <v>5482</v>
+        <v>58005</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>101920</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, söder om, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>616745</v>
+        <v>616718</v>
       </c>
       <c r="R40" t="n">
-        <v>6651703</v>
+        <v>6651643</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4967,12 +4986,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4987,27 +5016,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120590194</t>
+          <t>https://artportalen.se/Sighting/136866771</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120511338</v>
+        <v>136866773</v>
       </c>
       <c r="B41" t="n">
-        <v>4781</v>
+        <v>58005</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5015,42 +5044,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>616705</v>
+        <v>616719</v>
       </c>
       <c r="R41" t="n">
-        <v>6651732</v>
+        <v>6651683</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5074,12 +5103,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5088,34 +5127,33 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511338</t>
+          <t>https://artportalen.se/Sighting/136866773</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120541184</v>
+        <v>120510212</v>
       </c>
       <c r="B42" t="n">
-        <v>4781</v>
+        <v>57141</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5123,46 +5161,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102306</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>616800</v>
+        <v>616701</v>
       </c>
       <c r="R42" t="n">
-        <v>6651576</v>
+        <v>6651514</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5189,92 +5223,102 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Fjäderpenna på häll.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541184</t>
+          <t>https://artportalen.se/Sighting/120510212</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120541185</v>
+        <v>120510599</v>
       </c>
       <c r="B43" t="n">
-        <v>4781</v>
+        <v>6284</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102306</v>
+        <v>100524</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Skrovlig flatbagge</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Calitys scabra</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Thunberg, 1784)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>616723</v>
+        <v>616710</v>
       </c>
       <c r="R43" t="n">
-        <v>6651708</v>
+        <v>6651594</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5319,73 +5363,65 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541185</t>
+          <t>https://artportalen.se/Sighting/120510599</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120666046</v>
+        <v>136866779</v>
       </c>
       <c r="B44" t="n">
-        <v>58114</v>
+        <v>5182</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, söder om, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>616874</v>
+        <v>616605</v>
       </c>
       <c r="R44" t="n">
-        <v>6651669</v>
+        <v>6651693</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5409,12 +5445,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5429,74 +5475,74 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120666046</t>
+          <t>https://artportalen.se/Sighting/136866779</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120519559</v>
+        <v>120541190</v>
       </c>
       <c r="B45" t="n">
-        <v>5004</v>
+        <v>44177</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>105212</v>
+        <v>101735</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>616596</v>
+        <v>616925</v>
       </c>
       <c r="R45" t="n">
-        <v>6651599</v>
+        <v>6651481</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5541,71 +5587,71 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519559</t>
+          <t>https://artportalen.se/Sighting/120541190</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120519563</v>
+        <v>120510178</v>
       </c>
       <c r="B46" t="n">
-        <v>5199</v>
+        <v>5482</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>105930</v>
+        <v>101920</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>616596</v>
+        <v>616618</v>
       </c>
       <c r="R46" t="n">
-        <v>6651599</v>
+        <v>6651514</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5664,38 +5710,38 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519563</t>
+          <t>https://artportalen.se/Sighting/120510178</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120541189</v>
+        <v>120510277</v>
       </c>
       <c r="B47" t="n">
-        <v>8444</v>
+        <v>5482</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106554</v>
+        <v>101920</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5704,23 +5750,23 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>616925</v>
+        <v>616622</v>
       </c>
       <c r="R47" t="n">
-        <v>6651481</v>
+        <v>6651505</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5765,65 +5811,74 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541189</t>
+          <t>https://artportalen.se/Sighting/120510277</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120511304</v>
+        <v>120511479</v>
       </c>
       <c r="B48" t="n">
-        <v>58790</v>
+        <v>5482</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>208245</v>
+        <v>101920</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>616728</v>
+        <v>616731</v>
       </c>
       <c r="R48" t="n">
-        <v>6651675</v>
+        <v>6651699</v>
       </c>
       <c r="S48" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5850,83 +5905,78 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511304</t>
+          <t>https://artportalen.se/Sighting/120511479</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120512658</v>
+        <v>120512577</v>
       </c>
       <c r="B49" t="n">
-        <v>40269</v>
+        <v>5482</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>214815</v>
+        <v>101920</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Större träfjäril</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cossus cossus</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5996,16 +6046,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120512658</t>
+          <t>https://artportalen.se/Sighting/120512577</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120511748</v>
+        <v>120519343</v>
       </c>
       <c r="B50" t="n">
-        <v>99118</v>
+        <v>5482</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,48 +6063,43 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>101920</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1767)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>616739</v>
+        <v>616603</v>
       </c>
       <c r="R50" t="n">
-        <v>6651702</v>
+        <v>6651619</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6084,54 +6129,45 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511748</t>
+          <t>https://artportalen.se/Sighting/120519343</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120551257</v>
+        <v>120590194</v>
       </c>
       <c r="B51" t="n">
-        <v>99118</v>
+        <v>5482</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6139,41 +6175,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>101920</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1767)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>616797</v>
+        <v>616745</v>
       </c>
       <c r="R51" t="n">
-        <v>6651566</v>
+        <v>6651703</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6200,19 +6232,9 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-20</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:25</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6227,27 +6249,27 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551257</t>
+          <t>https://artportalen.se/Sighting/120590194</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120551249</v>
+        <v>120511338</v>
       </c>
       <c r="B52" t="n">
-        <v>97983</v>
+        <v>4781</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6255,37 +6277,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>102306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>616771</v>
+        <v>616705</v>
       </c>
       <c r="R52" t="n">
-        <v>6651647</v>
+        <v>6651732</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6323,33 +6350,34 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551249</t>
+          <t>https://artportalen.se/Sighting/120511338</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120551250</v>
+        <v>120541184</v>
       </c>
       <c r="B53" t="n">
-        <v>97983</v>
+        <v>4781</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6357,37 +6385,46 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>102306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>616787</v>
+        <v>616800</v>
       </c>
       <c r="R53" t="n">
-        <v>6651642</v>
+        <v>6651576</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6425,33 +6462,34 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551250</t>
+          <t>https://artportalen.se/Sighting/120541184</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120511185</v>
+        <v>120541185</v>
       </c>
       <c r="B54" t="n">
-        <v>97986</v>
+        <v>4781</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6459,37 +6497,46 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221946</v>
+        <v>102306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>616730</v>
+        <v>616723</v>
       </c>
       <c r="R54" t="n">
-        <v>6651675</v>
+        <v>6651708</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6516,54 +6563,45 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511185</t>
+          <t>https://artportalen.se/Sighting/120541185</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120551251</v>
+        <v>120666046</v>
       </c>
       <c r="B55" t="n">
-        <v>92328</v>
+        <v>58114</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6571,37 +6609,45 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6040162</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>616656</v>
+        <v>616874</v>
       </c>
       <c r="R55" t="n">
-        <v>6651527</v>
+        <v>6651669</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6645,16 +6691,1699 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120666046</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>136866768</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>St Hålsjön S, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>616676</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6651546</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136866768</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>136866770</v>
+      </c>
+      <c r="B57" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>St Hålsjön S, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>616702</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6651635</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136866770</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>120519559</v>
+      </c>
+      <c r="B58" t="n">
+        <v>5004</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>105212</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Barrpraktbagge</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Chrysobothris chrysostigma</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hjärtmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>616596</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6651599</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120519559</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>120519563</v>
+      </c>
+      <c r="B59" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hjärtmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>616596</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6651599</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120519563</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>136866778</v>
+      </c>
+      <c r="B60" t="n">
+        <v>5202</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>St Hålsjön S, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>616599</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6651694</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136866778</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>120541189</v>
+      </c>
+      <c r="B61" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>616925</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6651481</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120541189</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>120511304</v>
+      </c>
+      <c r="B62" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>616728</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6651675</v>
+      </c>
+      <c r="S62" t="n">
+        <v>50</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jake Bull</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jake Bull</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511304</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120512658</v>
+      </c>
+      <c r="B63" t="n">
+        <v>40269</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>214815</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Större träfjäril</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Cossus cossus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hjärtmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>616900</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6651584</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120512658</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120511748</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>616739</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6651702</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511748</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120551257</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>616797</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6651566</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120551257</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>136866776</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>St Hålsjön S, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>616618</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6651762</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136866776</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>120551249</v>
+      </c>
+      <c r="B67" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>616771</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6651647</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120551249</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>120551250</v>
+      </c>
+      <c r="B68" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>616787</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6651642</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120551250</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>120511185</v>
+      </c>
+      <c r="B69" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>616730</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6651675</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511185</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>120551251</v>
+      </c>
+      <c r="B70" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>616656</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6651527</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/120551251</t>
         </is>
@@ -6716,6 +8445,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39562-2026 artfynd.xlsx
+++ b/artfynd/A 39562-2026 artfynd.xlsx
@@ -1105,7 +1105,7 @@
         <v>136866766</v>
       </c>
       <c r="B6" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136866780</v>
       </c>
       <c r="B7" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136866767</v>
       </c>
       <c r="B10" t="n">
-        <v>92749</v>
+        <v>92751</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136866777</v>
       </c>
       <c r="B11" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136866772</v>
       </c>
       <c r="B12" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136866774</v>
       </c>
       <c r="B16" t="n">
-        <v>96831</v>
+        <v>96837</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136866775</v>
       </c>
       <c r="B29" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>136866769</v>
       </c>
       <c r="B39" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>136866776</v>
       </c>
       <c r="B66" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 39562-2026 artfynd.xlsx
+++ b/artfynd/A 39562-2026 artfynd.xlsx
@@ -1105,7 +1105,7 @@
         <v>136866766</v>
       </c>
       <c r="B6" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136866780</v>
       </c>
       <c r="B7" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136866767</v>
       </c>
       <c r="B10" t="n">
-        <v>92751</v>
+        <v>92753</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136866777</v>
       </c>
       <c r="B11" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136866772</v>
       </c>
       <c r="B12" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136866774</v>
       </c>
       <c r="B16" t="n">
-        <v>96837</v>
+        <v>96839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136866775</v>
       </c>
       <c r="B29" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>136866769</v>
       </c>
       <c r="B39" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>136866776</v>
       </c>
       <c r="B66" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 39562-2026 artfynd.xlsx
+++ b/artfynd/A 39562-2026 artfynd.xlsx
@@ -1105,7 +1105,7 @@
         <v>136866766</v>
       </c>
       <c r="B6" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136866780</v>
       </c>
       <c r="B7" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136866767</v>
       </c>
       <c r="B10" t="n">
-        <v>92753</v>
+        <v>92754</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136866777</v>
       </c>
       <c r="B11" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136866772</v>
       </c>
       <c r="B12" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136866774</v>
       </c>
       <c r="B16" t="n">
-        <v>96839</v>
+        <v>96840</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136866775</v>
       </c>
       <c r="B29" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>136866769</v>
       </c>
       <c r="B39" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>136866776</v>
       </c>
       <c r="B66" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 39562-2026 artfynd.xlsx
+++ b/artfynd/A 39562-2026 artfynd.xlsx
@@ -1569,7 +1569,7 @@
         <v>136866767</v>
       </c>
       <c r="B10" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136866777</v>
       </c>
       <c r="B11" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136866772</v>
       </c>
       <c r="B12" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136866774</v>
       </c>
       <c r="B16" t="n">
-        <v>96840</v>
+        <v>96846</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>136866776</v>
       </c>
       <c r="B66" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 39562-2026 artfynd.xlsx
+++ b/artfynd/A 39562-2026 artfynd.xlsx
@@ -1105,7 +1105,7 @@
         <v>136866766</v>
       </c>
       <c r="B6" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136866780</v>
       </c>
       <c r="B7" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136866767</v>
       </c>
       <c r="B10" t="n">
-        <v>92760</v>
+        <v>92764</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136866777</v>
       </c>
       <c r="B11" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136866772</v>
       </c>
       <c r="B12" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136866774</v>
       </c>
       <c r="B16" t="n">
-        <v>96846</v>
+        <v>96850</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136866775</v>
       </c>
       <c r="B29" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>136866769</v>
       </c>
       <c r="B39" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>136866776</v>
       </c>
       <c r="B66" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 39562-2026 artfynd.xlsx
+++ b/artfynd/A 39562-2026 artfynd.xlsx
@@ -2251,7 +2251,7 @@
         <v>136866774</v>
       </c>
       <c r="B16" t="n">
-        <v>96850</v>
+        <v>96852</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>136866776</v>
       </c>
       <c r="B66" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 39562-2026 artfynd.xlsx
+++ b/artfynd/A 39562-2026 artfynd.xlsx
@@ -1105,7 +1105,7 @@
         <v>136866766</v>
       </c>
       <c r="B6" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136866780</v>
       </c>
       <c r="B7" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136866767</v>
       </c>
       <c r="B10" t="n">
-        <v>92764</v>
+        <v>92766</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136866777</v>
       </c>
       <c r="B11" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136866772</v>
       </c>
       <c r="B12" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136866774</v>
       </c>
       <c r="B16" t="n">
-        <v>96852</v>
+        <v>96854</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136866775</v>
       </c>
       <c r="B29" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>136866769</v>
       </c>
       <c r="B39" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>136866776</v>
       </c>
       <c r="B66" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 39562-2026 artfynd.xlsx
+++ b/artfynd/A 39562-2026 artfynd.xlsx
@@ -1105,7 +1105,7 @@
         <v>136866766</v>
       </c>
       <c r="B6" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136866780</v>
       </c>
       <c r="B7" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136866767</v>
       </c>
       <c r="B10" t="n">
-        <v>92766</v>
+        <v>92779</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136866777</v>
       </c>
       <c r="B11" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136866772</v>
       </c>
       <c r="B12" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136866774</v>
       </c>
       <c r="B16" t="n">
-        <v>96854</v>
+        <v>96867</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136866775</v>
       </c>
       <c r="B29" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>136866769</v>
       </c>
       <c r="B39" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>136866771</v>
       </c>
       <c r="B40" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>136866773</v>
       </c>
       <c r="B41" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>136866768</v>
       </c>
       <c r="B56" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>136866770</v>
       </c>
       <c r="B57" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>136866776</v>
       </c>
       <c r="B66" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 39562-2026 artfynd.xlsx
+++ b/artfynd/A 39562-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ70"/>
+  <dimension ref="A1:AZ81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1105,7 +1105,7 @@
         <v>136866766</v>
       </c>
       <c r="B6" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136866780</v>
       </c>
       <c r="B7" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120590202</v>
+        <v>137250010</v>
       </c>
       <c r="B8" t="n">
-        <v>92147</v>
+        <v>79169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,40 +1337,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1101</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, söder om, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616867</v>
+        <v>616663</v>
       </c>
       <c r="R8" t="n">
-        <v>6651610</v>
+        <v>6651688</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,17 +1391,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På av mossa övervuxen granstubbe</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1413,34 +1415,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120590202</t>
+          <t>https://artportalen.se/Sighting/137250010</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120760977</v>
+        <v>137252175</v>
       </c>
       <c r="B9" t="n">
-        <v>92147</v>
+        <v>81472</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1448,48 +1449,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1101</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, syd om, Upl</t>
+          <t>st Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>616848</v>
       </c>
       <c r="R9" t="n">
-        <v>6651616</v>
+        <v>6651660</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1513,12 +1503,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,49 +1527,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stump</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120760977</t>
+          <t>https://artportalen.se/Sighting/137252175</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136866767</v>
+        <v>120590202</v>
       </c>
       <c r="B10" t="n">
-        <v>92779</v>
+        <v>92147</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,19 +1579,22 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Stora Hålsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616676</v>
+        <v>616867</v>
       </c>
       <c r="R10" t="n">
-        <v>6651546</v>
+        <v>6651610</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,22 +1618,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På av mossa övervuxen granstubbe</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,53 +1637,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866767</t>
+          <t>https://artportalen.se/Sighting/120590202</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136866777</v>
+        <v>120760977</v>
       </c>
       <c r="B11" t="n">
-        <v>92143</v>
+        <v>92147</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,37 +1672,48 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1101</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Stora Hålsjön, syd om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>616587</v>
+        <v>616848</v>
       </c>
       <c r="R11" t="n">
-        <v>6651708</v>
+        <v>6651616</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1763,22 +1737,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:31</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:31</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1787,55 +1751,71 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866777</t>
+          <t>https://artportalen.se/Sighting/120760977</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136866772</v>
+        <v>136866767</v>
       </c>
       <c r="B12" t="n">
-        <v>92322</v>
+        <v>92781</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1503</v>
+        <v>1101</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>616702</v>
+        <v>616676</v>
       </c>
       <c r="R12" t="n">
-        <v>6651664</v>
+        <v>6651546</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1880,7 +1860,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1870,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,6 +1881,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1916,54 +1916,54 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866772</t>
+          <t>https://artportalen.se/Sighting/136866767</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120513434</v>
+        <v>136866777</v>
       </c>
       <c r="B13" t="n">
-        <v>96601</v>
+        <v>92145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2170</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stora Hålsjön syd om, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>616954</v>
+        <v>616587</v>
       </c>
       <c r="R13" t="n">
-        <v>6651400</v>
+        <v>6651708</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1987,22 +1987,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,65 +2017,65 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120513434</t>
+          <t>https://artportalen.se/Sighting/136866777</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120518741</v>
+        <v>136866772</v>
       </c>
       <c r="B14" t="n">
-        <v>96601</v>
+        <v>92324</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2170</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stora Hålsjön syd om, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>616852</v>
+        <v>616702</v>
       </c>
       <c r="R14" t="n">
-        <v>6651662</v>
+        <v>6651664</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2099,22 +2099,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,24 +2129,24 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120518741</t>
+          <t>https://artportalen.se/Sighting/136866772</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120543211</v>
+        <v>120513434</v>
       </c>
       <c r="B15" t="n">
         <v>96601</v>
@@ -2177,17 +2177,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön syd om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>616936</v>
+        <v>616954</v>
       </c>
       <c r="R15" t="n">
         <v>6651400</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2214,9 +2214,19 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,27 +2241,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elin Sjögren Englund</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Sjögren Englund</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120543211</t>
+          <t>https://artportalen.se/Sighting/120513434</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136866774</v>
+        <v>120518741</v>
       </c>
       <c r="B16" t="n">
-        <v>96867</v>
+        <v>96601</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2279,17 +2289,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Stora Hålsjön syd om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>616698</v>
+        <v>616852</v>
       </c>
       <c r="R16" t="n">
-        <v>6651745</v>
+        <v>6651662</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2313,22 +2323,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,76 +2353,65 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866774</t>
+          <t>https://artportalen.se/Sighting/120518741</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120761198</v>
+        <v>120543211</v>
       </c>
       <c r="B17" t="n">
-        <v>93197</v>
+        <v>96601</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>2170</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, syd om, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>616726</v>
+        <v>616936</v>
       </c>
       <c r="R17" t="n">
-        <v>6651651</v>
+        <v>6651400</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2450,39 +2449,33 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Elin Sjögren Englund</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Elin Sjögren Englund</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120761198</t>
+          <t>https://artportalen.se/Sighting/120543211</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120519500</v>
+        <v>136866774</v>
       </c>
       <c r="B18" t="n">
-        <v>91282</v>
+        <v>96869</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2490,37 +2483,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5685</v>
+        <v>2170</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616604</v>
+        <v>616698</v>
       </c>
       <c r="R18" t="n">
-        <v>6651608</v>
+        <v>6651745</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2544,22 +2537,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2574,27 +2567,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519500</t>
+          <t>https://artportalen.se/Sighting/136866774</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120551261</v>
+        <v>137250000</v>
       </c>
       <c r="B19" t="n">
-        <v>91282</v>
+        <v>91921</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2602,31 +2595,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5685</v>
+        <v>3215</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616607</v>
+        <v>616772</v>
       </c>
       <c r="R19" t="n">
         <v>6651614</v>
@@ -2656,12 +2649,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2676,27 +2679,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551261</t>
+          <t>https://artportalen.se/Sighting/137250000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120511104</v>
+        <v>120761198</v>
       </c>
       <c r="B20" t="n">
-        <v>93235</v>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2704,37 +2707,48 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
+          <t>Stora Hålsjön, syd om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>616704</v>
+        <v>616726</v>
       </c>
       <c r="R20" t="n">
-        <v>6651675</v>
+        <v>6651651</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2761,98 +2775,85 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511104</t>
+          <t>https://artportalen.se/Sighting/120761198</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120511417</v>
+        <v>120519500</v>
       </c>
       <c r="B21" t="n">
-        <v>93235</v>
+        <v>91282</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>5685</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>616708</v>
+        <v>616604</v>
       </c>
       <c r="R21" t="n">
-        <v>6651685</v>
+        <v>6651608</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2884,7 +2885,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2894,7 +2895,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2909,74 +2910,65 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511417</t>
+          <t>https://artportalen.se/Sighting/120519500</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120512327</v>
+        <v>120551261</v>
       </c>
       <c r="B22" t="n">
-        <v>93235</v>
+        <v>91282</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>5685</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stora Hålsjön syd om, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>616886</v>
+        <v>616607</v>
       </c>
       <c r="R22" t="n">
-        <v>6651550</v>
+        <v>6651614</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3003,19 +2995,9 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-20</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3030,24 +3012,24 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120512327</t>
+          <t>https://artportalen.se/Sighting/120551261</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120549502</v>
+        <v>120511104</v>
       </c>
       <c r="B23" t="n">
         <v>93235</v>
@@ -3076,22 +3058,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>616708</v>
+        <v>616704</v>
       </c>
       <c r="R23" t="n">
-        <v>6651552</v>
+        <v>6651675</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3118,42 +3097,51 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Sofia Lundell</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sofia Lundell</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120549502</t>
+          <t>https://artportalen.se/Sighting/120511104</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120590195</v>
+        <v>120511417</v>
       </c>
       <c r="B24" t="n">
         <v>93235</v>
@@ -3181,23 +3169,29 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, söder om, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>616874</v>
+        <v>616708</v>
       </c>
       <c r="R24" t="n">
-        <v>6651669</v>
+        <v>6651685</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3224,42 +3218,51 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120590195</t>
+          <t>https://artportalen.se/Sighting/120511417</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120590197</v>
+        <v>120512327</v>
       </c>
       <c r="B25" t="n">
         <v>93235</v>
@@ -3287,23 +3290,29 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, söder om, Upl</t>
+          <t>Stora Hålsjön syd om, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>616705</v>
+        <v>616886</v>
       </c>
       <c r="R25" t="n">
-        <v>6651645</v>
+        <v>6651550</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3330,42 +3339,51 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120590197</t>
+          <t>https://artportalen.se/Sighting/120512327</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120590198</v>
+        <v>120549502</v>
       </c>
       <c r="B26" t="n">
         <v>93235</v>
@@ -3399,17 +3417,17 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, söder om, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>616898</v>
+        <v>616708</v>
       </c>
       <c r="R26" t="n">
-        <v>6651543</v>
+        <v>6651552</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3454,24 +3472,24 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Sofia Lundell</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Sofia Lundell</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120590198</t>
+          <t>https://artportalen.se/Sighting/120549502</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120761144</v>
+        <v>120590195</v>
       </c>
       <c r="B27" t="n">
         <v>93235</v>
@@ -3499,31 +3517,23 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, syd om, Upl</t>
+          <t>Stora Hålsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>616707</v>
+        <v>616874</v>
       </c>
       <c r="R27" t="n">
-        <v>6651675</v>
+        <v>6651669</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3565,35 +3575,30 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Tallskog på blockmark</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120761144</t>
+          <t>https://artportalen.se/Sighting/120590195</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120518661</v>
+        <v>120590197</v>
       </c>
       <c r="B28" t="n">
-        <v>79084</v>
+        <v>93235</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3601,42 +3606,40 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stora Hålsjön syd om, Upl</t>
+          <t>Stora Hålsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>616852</v>
+        <v>616705</v>
       </c>
       <c r="R28" t="n">
-        <v>6651662</v>
+        <v>6651645</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3663,59 +3666,45 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Flera fläckar utan apothecier och en klunga med apothecier!</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120518661</t>
+          <t>https://artportalen.se/Sighting/120590197</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136866775</v>
+        <v>120590198</v>
       </c>
       <c r="B29" t="n">
-        <v>79258</v>
+        <v>93235</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3723,37 +3712,40 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Stora Hålsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>616710</v>
+        <v>616898</v>
       </c>
       <c r="R29" t="n">
-        <v>6651797</v>
+        <v>6651543</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3777,22 +3769,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>15:11</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:11</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3801,33 +3783,34 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866775</t>
+          <t>https://artportalen.se/Sighting/120590198</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120510603</v>
+        <v>120761144</v>
       </c>
       <c r="B30" t="n">
-        <v>79946</v>
+        <v>93235</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3835,34 +3818,45 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, syd om, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>616717</v>
+        <v>616707</v>
       </c>
       <c r="R30" t="n">
-        <v>6651623</v>
+        <v>6651675</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3892,54 +3886,50 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Tallskog på blockmark</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510603</t>
+          <t>https://artportalen.se/Sighting/120761144</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120518677</v>
+        <v>120518661</v>
       </c>
       <c r="B31" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3947,24 +3937,29 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stora Hålsjön syd om, Upl</t>
@@ -4019,6 +4014,11 @@
           <t>15:25</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Flera fläckar utan apothecier och en klunga med apothecier!</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4042,16 +4042,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120518677</t>
+          <t>https://artportalen.se/Sighting/120518661</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120518963</v>
+        <v>136866775</v>
       </c>
       <c r="B32" t="n">
-        <v>79946</v>
+        <v>79260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4059,34 +4059,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stora Hålsjön syd om, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>616658</v>
+        <v>616710</v>
       </c>
       <c r="R32" t="n">
-        <v>6651670</v>
+        <v>6651797</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4113,22 +4113,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4143,24 +4143,24 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120518963</t>
+          <t>https://artportalen.se/Sighting/136866775</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120519139</v>
+        <v>120510603</v>
       </c>
       <c r="B33" t="n">
         <v>79946</v>
@@ -4191,14 +4191,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stora Hålsjön syd om, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>616625</v>
+        <v>616717</v>
       </c>
       <c r="R33" t="n">
-        <v>6651656</v>
+        <v>6651623</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4266,13 +4266,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519139</t>
+          <t>https://artportalen.se/Sighting/120510603</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120527703</v>
+        <v>120518677</v>
       </c>
       <c r="B34" t="n">
         <v>79946</v>
@@ -4301,22 +4301,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norr om Tarmlången, Upl</t>
+          <t>Stora Hålsjön syd om, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>616650</v>
+        <v>616852</v>
       </c>
       <c r="R34" t="n">
-        <v>6651661</v>
+        <v>6651662</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4345,7 +4342,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4355,7 +4352,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4364,31 +4361,30 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120527703</t>
+          <t>https://artportalen.se/Sighting/120518677</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120543208</v>
+        <v>120518963</v>
       </c>
       <c r="B35" t="n">
         <v>79946</v>
@@ -4419,17 +4415,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön syd om, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>616888</v>
+        <v>616658</v>
       </c>
       <c r="R35" t="n">
-        <v>6651557</v>
+        <v>6651670</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4456,9 +4452,19 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4473,24 +4479,24 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Sjögren Englund</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elin Sjögren Englund</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120543208</t>
+          <t>https://artportalen.se/Sighting/120518963</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120549513</v>
+        <v>120519139</v>
       </c>
       <c r="B36" t="n">
         <v>79946</v>
@@ -4519,19 +4525,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön syd om, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>616740</v>
+        <v>616625</v>
       </c>
       <c r="R36" t="n">
-        <v>6651532</v>
+        <v>6651656</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4561,42 +4564,51 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Sofia Lundell</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sofia Lundell</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120549513</t>
+          <t>https://artportalen.se/Sighting/120519139</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120549579</v>
+        <v>120527703</v>
       </c>
       <c r="B37" t="n">
         <v>79946</v>
@@ -4630,17 +4642,17 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Norr om Tarmlången, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>616696</v>
+        <v>616650</v>
       </c>
       <c r="R37" t="n">
-        <v>6651548</v>
+        <v>6651661</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4667,9 +4679,19 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4685,24 +4707,24 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Sofia Lundell</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sofia Lundell</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120549579</t>
+          <t>https://artportalen.se/Sighting/120527703</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120551237</v>
+        <v>120543208</v>
       </c>
       <c r="B38" t="n">
         <v>79946</v>
@@ -4737,13 +4759,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>616697</v>
+        <v>616888</v>
       </c>
       <c r="R38" t="n">
-        <v>6651696</v>
+        <v>6651557</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4787,27 +4809,27 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Elin Sjögren Englund</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Elin Sjögren Englund</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551237</t>
+          <t>https://artportalen.se/Sighting/120543208</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136866769</v>
+        <v>120549513</v>
       </c>
       <c r="B39" t="n">
-        <v>80120</v>
+        <v>79946</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4833,19 +4855,22 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>616663</v>
+        <v>616740</v>
       </c>
       <c r="R39" t="n">
-        <v>6651632</v>
+        <v>6651532</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4869,22 +4894,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4893,76 +4908,75 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Sofia Lundell</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Sofia Lundell</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866769</t>
+          <t>https://artportalen.se/Sighting/120549513</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136866771</v>
+        <v>120549579</v>
       </c>
       <c r="B40" t="n">
-        <v>58018</v>
+        <v>79946</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>616718</v>
+        <v>616696</v>
       </c>
       <c r="R40" t="n">
-        <v>6651643</v>
+        <v>6651548</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4986,22 +5000,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5010,73 +5014,69 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Sofia Lundell</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Sofia Lundell</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866771</t>
+          <t>https://artportalen.se/Sighting/120549579</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136866773</v>
+        <v>120551237</v>
       </c>
       <c r="B41" t="n">
-        <v>58018</v>
+        <v>79946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>616719</v>
+        <v>616697</v>
       </c>
       <c r="R41" t="n">
-        <v>6651683</v>
+        <v>6651696</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5103,22 +5103,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:46</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:46</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5133,70 +5123,65 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866773</t>
+          <t>https://artportalen.se/Sighting/120551237</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120510212</v>
+        <v>136866769</v>
       </c>
       <c r="B42" t="n">
-        <v>57141</v>
+        <v>80122</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>616701</v>
+        <v>616663</v>
       </c>
       <c r="R42" t="n">
-        <v>6651514</v>
+        <v>6651632</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5220,27 +5205,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Fjäderpenna på häll.</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5255,27 +5235,27 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510212</t>
+          <t>https://artportalen.se/Sighting/136866769</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120510599</v>
+        <v>137250002</v>
       </c>
       <c r="B43" t="n">
-        <v>6284</v>
+        <v>80122</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5283,42 +5263,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100524</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovlig flatbagge</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Calitys scabra</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Thunberg, 1784)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>616710</v>
+        <v>616868</v>
       </c>
       <c r="R43" t="n">
-        <v>6651594</v>
+        <v>6651544</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5342,12 +5317,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5356,69 +5341,68 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510599</t>
+          <t>https://artportalen.se/Sighting/137250002</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136866779</v>
+        <v>137250003</v>
       </c>
       <c r="B44" t="n">
-        <v>5182</v>
+        <v>80122</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>616605</v>
+        <v>616909</v>
       </c>
       <c r="R44" t="n">
-        <v>6651693</v>
+        <v>6651517</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5445,22 +5429,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5486,63 +5470,54 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866779</t>
+          <t>https://artportalen.se/Sighting/137250003</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120541190</v>
+        <v>137250009</v>
       </c>
       <c r="B45" t="n">
-        <v>44177</v>
+        <v>80122</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>101735</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>616925</v>
+        <v>616729</v>
       </c>
       <c r="R45" t="n">
-        <v>6651481</v>
+        <v>6651628</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5566,12 +5541,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5580,81 +5565,76 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541190</t>
+          <t>https://artportalen.se/Sighting/137250009</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120510178</v>
+        <v>136866771</v>
       </c>
       <c r="B46" t="n">
-        <v>5482</v>
+        <v>58020</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>101920</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>616618</v>
+        <v>616718</v>
       </c>
       <c r="R46" t="n">
-        <v>6651514</v>
+        <v>6651643</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5678,12 +5658,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5692,81 +5682,76 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510178</t>
+          <t>https://artportalen.se/Sighting/136866771</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120510277</v>
+        <v>136866773</v>
       </c>
       <c r="B47" t="n">
-        <v>5482</v>
+        <v>58020</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>101920</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>616622</v>
+        <v>616719</v>
       </c>
       <c r="R47" t="n">
-        <v>6651505</v>
+        <v>6651683</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5790,12 +5775,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5804,78 +5799,73 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510277</t>
+          <t>https://artportalen.se/Sighting/136866773</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120511479</v>
+        <v>120510212</v>
       </c>
       <c r="B48" t="n">
-        <v>5482</v>
+        <v>57141</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>101920</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>616731</v>
+        <v>616701</v>
       </c>
       <c r="R48" t="n">
-        <v>6651699</v>
+        <v>6651514</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5905,78 +5895,88 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Fjäderpenna på häll.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511479</t>
+          <t>https://artportalen.se/Sighting/120510212</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120512577</v>
+        <v>120510599</v>
       </c>
       <c r="B49" t="n">
-        <v>5482</v>
+        <v>6284</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>101920</v>
+        <v>100524</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Skrovlig flatbagge</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Calitys scabra</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Thunberg, 1784)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5984,13 +5984,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>616900</v>
+        <v>616710</v>
       </c>
       <c r="R49" t="n">
-        <v>6651584</v>
+        <v>6651594</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6046,63 +6046,54 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120512577</t>
+          <t>https://artportalen.se/Sighting/120510599</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120519343</v>
+        <v>136866779</v>
       </c>
       <c r="B50" t="n">
-        <v>5482</v>
+        <v>5182</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>101920</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>616603</v>
+        <v>616605</v>
       </c>
       <c r="R50" t="n">
-        <v>6651619</v>
+        <v>6651693</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6126,12 +6117,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6140,72 +6141,80 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519343</t>
+          <t>https://artportalen.se/Sighting/136866779</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120590194</v>
+        <v>120541190</v>
       </c>
       <c r="B51" t="n">
-        <v>5482</v>
+        <v>44177</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>101920</v>
+        <v>101735</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, söder om, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>616745</v>
+        <v>616925</v>
       </c>
       <c r="R51" t="n">
-        <v>6651703</v>
+        <v>6651481</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6243,73 +6252,78 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120590194</t>
+          <t>https://artportalen.se/Sighting/120541190</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120511338</v>
+        <v>120510178</v>
       </c>
       <c r="B52" t="n">
-        <v>4781</v>
+        <v>5482</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102306</v>
+        <v>101920</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>616705</v>
+        <v>616618</v>
       </c>
       <c r="R52" t="n">
-        <v>6651732</v>
+        <v>6651514</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6368,38 +6382,38 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511338</t>
+          <t>https://artportalen.se/Sighting/120510178</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120541184</v>
+        <v>120510277</v>
       </c>
       <c r="B53" t="n">
-        <v>4781</v>
+        <v>5482</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102306</v>
+        <v>101920</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6408,23 +6422,23 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>616800</v>
+        <v>616622</v>
       </c>
       <c r="R53" t="n">
-        <v>6651576</v>
+        <v>6651505</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6469,49 +6483,49 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541184</t>
+          <t>https://artportalen.se/Sighting/120510277</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120541185</v>
+        <v>120511479</v>
       </c>
       <c r="B54" t="n">
-        <v>4781</v>
+        <v>5482</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>102306</v>
+        <v>101920</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6520,23 +6534,23 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>616723</v>
+        <v>616731</v>
       </c>
       <c r="R54" t="n">
-        <v>6651708</v>
+        <v>6651699</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6581,73 +6595,74 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541185</t>
+          <t>https://artportalen.se/Sighting/120511479</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120666046</v>
+        <v>120512577</v>
       </c>
       <c r="B55" t="n">
-        <v>58114</v>
+        <v>5482</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>101920</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, söder om, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>616874</v>
+        <v>616900</v>
       </c>
       <c r="R55" t="n">
-        <v>6651669</v>
+        <v>6651584</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6685,76 +6700,81 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120666046</t>
+          <t>https://artportalen.se/Sighting/120512577</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>136866768</v>
+        <v>120519343</v>
       </c>
       <c r="B56" t="n">
-        <v>58182</v>
+        <v>5482</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>101920</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>616676</v>
+        <v>616603</v>
       </c>
       <c r="R56" t="n">
-        <v>6651546</v>
+        <v>6651619</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6778,22 +6798,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6802,76 +6812,72 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866768</t>
+          <t>https://artportalen.se/Sighting/120519343</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>136866770</v>
+        <v>120590194</v>
       </c>
       <c r="B57" t="n">
-        <v>58182</v>
+        <v>5482</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>101920</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Stora Hålsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>616702</v>
+        <v>616745</v>
       </c>
       <c r="R57" t="n">
-        <v>6651635</v>
+        <v>6651703</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6895,22 +6901,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>14:34</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>14:34</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6925,74 +6921,65 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866770</t>
+          <t>https://artportalen.se/Sighting/120590194</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120519559</v>
+        <v>137250004</v>
       </c>
       <c r="B58" t="n">
-        <v>5004</v>
+        <v>5485</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>105212</v>
+        <v>101920</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>616596</v>
+        <v>616876</v>
       </c>
       <c r="R58" t="n">
-        <v>6651599</v>
+        <v>6651538</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7016,12 +7003,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7030,34 +7027,33 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519559</t>
+          <t>https://artportalen.se/Sighting/137250004</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120519563</v>
+        <v>120511338</v>
       </c>
       <c r="B59" t="n">
-        <v>5199</v>
+        <v>4781</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7065,21 +7061,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7087,21 +7083,17 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>616596</v>
+        <v>616705</v>
       </c>
       <c r="R59" t="n">
-        <v>6651599</v>
+        <v>6651732</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7160,16 +7152,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519563</t>
+          <t>https://artportalen.se/Sighting/120511338</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>136866778</v>
+        <v>120541184</v>
       </c>
       <c r="B60" t="n">
-        <v>5202</v>
+        <v>4781</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7177,37 +7169,46 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>616599</v>
+        <v>616800</v>
       </c>
       <c r="R60" t="n">
-        <v>6651694</v>
+        <v>6651576</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7231,22 +7232,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>15:34</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>15:34</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7255,33 +7246,34 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866778</t>
+          <t>https://artportalen.se/Sighting/120541184</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120541189</v>
+        <v>120541185</v>
       </c>
       <c r="B61" t="n">
-        <v>8444</v>
+        <v>4781</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7289,21 +7281,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106554</v>
+        <v>102306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7322,10 +7314,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>616925</v>
+        <v>616723</v>
       </c>
       <c r="R61" t="n">
-        <v>6651481</v>
+        <v>6651708</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7384,54 +7376,62 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541189</t>
+          <t>https://artportalen.se/Sighting/120541185</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120511304</v>
+        <v>120666046</v>
       </c>
       <c r="B62" t="n">
-        <v>58790</v>
+        <v>58114</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>208245</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
+          <t>Stora Hålsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>616728</v>
+        <v>616874</v>
       </c>
       <c r="R62" t="n">
-        <v>6651675</v>
+        <v>6651669</v>
       </c>
       <c r="S62" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7458,19 +7458,9 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-20</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>10:37</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7485,70 +7475,70 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511304</t>
+          <t>https://artportalen.se/Sighting/120666046</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120512658</v>
+        <v>136866768</v>
       </c>
       <c r="B63" t="n">
-        <v>40269</v>
+        <v>58184</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>214815</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Större träfjäril</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cossus cossus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>616900</v>
+        <v>616676</v>
       </c>
       <c r="R63" t="n">
-        <v>6651584</v>
+        <v>6651546</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7572,12 +7562,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7586,86 +7586,76 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120512658</t>
+          <t>https://artportalen.se/Sighting/136866768</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120511748</v>
+        <v>136866770</v>
       </c>
       <c r="B64" t="n">
-        <v>99118</v>
+        <v>58184</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>616739</v>
+        <v>616702</v>
       </c>
       <c r="R64" t="n">
-        <v>6651702</v>
+        <v>6651635</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7689,22 +7679,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7719,66 +7709,67 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511748</t>
+          <t>https://artportalen.se/Sighting/136866770</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120551257</v>
+        <v>137250006</v>
       </c>
       <c r="B65" t="n">
-        <v>99118</v>
+        <v>58184</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>616797</v>
+        <v>616867</v>
       </c>
       <c r="R65" t="n">
-        <v>6651566</v>
+        <v>6651589</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7805,22 +7796,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7835,74 +7826,74 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551257</t>
+          <t>https://artportalen.se/Sighting/137250006</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>136866776</v>
+        <v>120519559</v>
       </c>
       <c r="B66" t="n">
-        <v>99389</v>
+        <v>5004</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>105212</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>616618</v>
+        <v>616596</v>
       </c>
       <c r="R66" t="n">
-        <v>6651762</v>
+        <v>6651599</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7926,22 +7917,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7950,33 +7931,34 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866776</t>
+          <t>https://artportalen.se/Sighting/120519559</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120551249</v>
+        <v>120519563</v>
       </c>
       <c r="B67" t="n">
-        <v>97983</v>
+        <v>5199</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7984,37 +7966,46 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>616771</v>
+        <v>616596</v>
       </c>
       <c r="R67" t="n">
-        <v>6651647</v>
+        <v>6651599</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8052,33 +8043,34 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551249</t>
+          <t>https://artportalen.se/Sighting/120519563</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120551250</v>
+        <v>136866778</v>
       </c>
       <c r="B68" t="n">
-        <v>97983</v>
+        <v>5202</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8086,34 +8078,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>616787</v>
+        <v>616599</v>
       </c>
       <c r="R68" t="n">
-        <v>6651642</v>
+        <v>6651694</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8140,12 +8132,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8160,27 +8162,27 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551250</t>
+          <t>https://artportalen.se/Sighting/136866778</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120511185</v>
+        <v>120541189</v>
       </c>
       <c r="B69" t="n">
-        <v>97986</v>
+        <v>8444</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8188,37 +8190,46 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221946</v>
+        <v>106554</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>616730</v>
+        <v>616925</v>
       </c>
       <c r="R69" t="n">
-        <v>6651675</v>
+        <v>6651481</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8245,89 +8256,80 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511185</t>
+          <t>https://artportalen.se/Sighting/120541189</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120551251</v>
+        <v>137250005</v>
       </c>
       <c r="B70" t="n">
-        <v>92328</v>
+        <v>8453</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6040162</v>
+        <v>106554</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>616656</v>
+        <v>616838</v>
       </c>
       <c r="R70" t="n">
-        <v>6651527</v>
+        <v>6651458</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8354,12 +8356,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8374,16 +8386,1246 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137250005</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>120511304</v>
+      </c>
+      <c r="B71" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>616728</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6651675</v>
+      </c>
+      <c r="S71" t="n">
+        <v>50</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Jake Bull</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Jake Bull</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511304</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>120512658</v>
+      </c>
+      <c r="B72" t="n">
+        <v>40269</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>214815</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Större träfjäril</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Cossus cossus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Hjärtmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>616900</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6651584</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120512658</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>120511748</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>616739</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6651702</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511748</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>120551257</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>616797</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6651566</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120551257</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>136866776</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99391</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>St Hålsjön S, Upl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>616618</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6651762</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136866776</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>137250001</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99391</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>st Hålsjön S, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>616795</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6651571</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137250001</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>137250011</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99391</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>st Hålsjön S, Upl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>616616</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6651766</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137250011</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>120551249</v>
+      </c>
+      <c r="B78" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>616771</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6651647</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120551249</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>120551250</v>
+      </c>
+      <c r="B79" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>616787</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6651642</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120551250</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>120511185</v>
+      </c>
+      <c r="B80" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>616730</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6651675</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511185</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>120551251</v>
+      </c>
+      <c r="B81" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>616656</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6651527</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/120551251</t>
         </is>
@@ -8460,6 +9702,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39562-2026 artfynd.xlsx
+++ b/artfynd/A 39562-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ81"/>
+  <dimension ref="A1:AZ86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5617,11 +5617,7 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>St Hålsjön S, Upl</t>
@@ -5734,11 +5730,7 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>St Hålsjön S, Upl</t>
@@ -5822,10 +5814,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120510212</v>
+        <v>137273223</v>
       </c>
       <c r="B48" t="n">
-        <v>57141</v>
+        <v>58020</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5833,39 +5825,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>616701</v>
+        <v>616733</v>
       </c>
       <c r="R48" t="n">
-        <v>6651514</v>
+        <v>6651699</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5892,27 +5883,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Fjäderpenna på häll.</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5927,70 +5913,66 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510212</t>
+          <t>https://artportalen.se/Sighting/137273223</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120510599</v>
+        <v>137273225</v>
       </c>
       <c r="B49" t="n">
-        <v>6284</v>
+        <v>58020</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100524</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovlig flatbagge</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Calitys scabra</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Thunberg, 1784)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>616710</v>
+        <v>616633</v>
       </c>
       <c r="R49" t="n">
-        <v>6651594</v>
+        <v>6651595</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6014,12 +5996,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6028,34 +6020,33 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510599</t>
+          <t>https://artportalen.se/Sighting/137273225</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>136866779</v>
+        <v>120510212</v>
       </c>
       <c r="B50" t="n">
-        <v>5182</v>
+        <v>57141</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6063,37 +6054,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>616605</v>
+        <v>616701</v>
       </c>
       <c r="R50" t="n">
-        <v>6651693</v>
+        <v>6651514</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6117,22 +6113,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Fjäderpenna på häll.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6147,27 +6148,27 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866779</t>
+          <t>https://artportalen.se/Sighting/120510212</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120541190</v>
+        <v>137273224</v>
       </c>
       <c r="B51" t="n">
-        <v>44177</v>
+        <v>57210</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6175,46 +6176,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>101735</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>616925</v>
+        <v>616823</v>
       </c>
       <c r="R51" t="n">
-        <v>6651481</v>
+        <v>6651621</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6238,12 +6234,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6252,81 +6258,76 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541190</t>
+          <t>https://artportalen.se/Sighting/137273224</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120510178</v>
+        <v>120510599</v>
       </c>
       <c r="B52" t="n">
-        <v>5482</v>
+        <v>6284</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>101920</v>
+        <v>100524</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Skrovlig flatbagge</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Calitys scabra</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Thunberg, 1784)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>616618</v>
+        <v>616710</v>
       </c>
       <c r="R52" t="n">
-        <v>6651514</v>
+        <v>6651594</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6382,63 +6383,54 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510178</t>
+          <t>https://artportalen.se/Sighting/120510599</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120510277</v>
+        <v>136866779</v>
       </c>
       <c r="B53" t="n">
-        <v>5482</v>
+        <v>5182</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>101920</v>
+        <v>100526</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>616622</v>
+        <v>616605</v>
       </c>
       <c r="R53" t="n">
-        <v>6651505</v>
+        <v>6651693</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6462,12 +6454,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6476,56 +6478,55 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510277</t>
+          <t>https://artportalen.se/Sighting/136866779</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120511479</v>
+        <v>120541190</v>
       </c>
       <c r="B54" t="n">
-        <v>5482</v>
+        <v>44177</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>101920</v>
+        <v>101735</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6534,23 +6535,23 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>616731</v>
+        <v>616925</v>
       </c>
       <c r="R54" t="n">
-        <v>6651699</v>
+        <v>6651481</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6595,24 +6596,24 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511479</t>
+          <t>https://artportalen.se/Sighting/120541190</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120512577</v>
+        <v>120510178</v>
       </c>
       <c r="B55" t="n">
         <v>5482</v>
@@ -6652,14 +6653,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>616900</v>
+        <v>616618</v>
       </c>
       <c r="R55" t="n">
-        <v>6651584</v>
+        <v>6651514</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6718,13 +6719,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120512577</t>
+          <t>https://artportalen.se/Sighting/120510178</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120519343</v>
+        <v>120510277</v>
       </c>
       <c r="B56" t="n">
         <v>5482</v>
@@ -6768,10 +6769,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>616603</v>
+        <v>616622</v>
       </c>
       <c r="R56" t="n">
-        <v>6651619</v>
+        <v>6651505</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6830,13 +6831,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519343</t>
+          <t>https://artportalen.se/Sighting/120510277</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120590194</v>
+        <v>120511479</v>
       </c>
       <c r="B57" t="n">
         <v>5482</v>
@@ -6865,19 +6866,28 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, söder om, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>616745</v>
+        <v>616731</v>
       </c>
       <c r="R57" t="n">
-        <v>6651703</v>
+        <v>6651699</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6915,33 +6925,34 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120590194</t>
+          <t>https://artportalen.se/Sighting/120511479</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>137250004</v>
+        <v>120512577</v>
       </c>
       <c r="B58" t="n">
-        <v>5485</v>
+        <v>5482</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6967,19 +6978,28 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>616876</v>
+        <v>616900</v>
       </c>
       <c r="R58" t="n">
-        <v>6651538</v>
+        <v>6651584</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7003,22 +7023,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7027,62 +7037,67 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250004</t>
+          <t>https://artportalen.se/Sighting/120512577</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120511338</v>
+        <v>120519343</v>
       </c>
       <c r="B59" t="n">
-        <v>4781</v>
+        <v>5482</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102306</v>
+        <v>101920</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7090,10 +7105,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>616705</v>
+        <v>616603</v>
       </c>
       <c r="R59" t="n">
-        <v>6651732</v>
+        <v>6651619</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7152,63 +7167,54 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511338</t>
+          <t>https://artportalen.se/Sighting/120519343</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120541184</v>
+        <v>120590194</v>
       </c>
       <c r="B60" t="n">
-        <v>4781</v>
+        <v>5482</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102306</v>
+        <v>101920</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>616800</v>
+        <v>616745</v>
       </c>
       <c r="R60" t="n">
-        <v>6651576</v>
+        <v>6651703</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7246,81 +7252,71 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541184</t>
+          <t>https://artportalen.se/Sighting/120590194</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120541185</v>
+        <v>137250004</v>
       </c>
       <c r="B61" t="n">
-        <v>4781</v>
+        <v>5485</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>102306</v>
+        <v>101920</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>616723</v>
+        <v>616876</v>
       </c>
       <c r="R61" t="n">
-        <v>6651708</v>
+        <v>6651538</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7344,12 +7340,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7358,80 +7364,76 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541185</t>
+          <t>https://artportalen.se/Sighting/137250004</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120666046</v>
+        <v>120511338</v>
       </c>
       <c r="B62" t="n">
-        <v>58114</v>
+        <v>4781</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, söder om, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>616874</v>
+        <v>616705</v>
       </c>
       <c r="R62" t="n">
-        <v>6651669</v>
+        <v>6651732</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7469,76 +7471,81 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120666046</t>
+          <t>https://artportalen.se/Sighting/120511338</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>136866768</v>
+        <v>120541184</v>
       </c>
       <c r="B63" t="n">
-        <v>58184</v>
+        <v>4781</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>616676</v>
+        <v>616800</v>
       </c>
       <c r="R63" t="n">
-        <v>6651546</v>
+        <v>6651576</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7562,22 +7569,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7586,76 +7583,81 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866768</t>
+          <t>https://artportalen.se/Sighting/120541184</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>136866770</v>
+        <v>120541185</v>
       </c>
       <c r="B64" t="n">
-        <v>58184</v>
+        <v>4781</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>616702</v>
+        <v>616723</v>
       </c>
       <c r="R64" t="n">
-        <v>6651635</v>
+        <v>6651708</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7679,22 +7681,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:34</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:34</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7703,33 +7695,34 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866770</t>
+          <t>https://artportalen.se/Sighting/120541185</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>137250006</v>
+        <v>120666046</v>
       </c>
       <c r="B65" t="n">
-        <v>58184</v>
+        <v>58114</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7755,24 +7748,27 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>Stora Hålsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>616867</v>
+        <v>616874</v>
       </c>
       <c r="R65" t="n">
-        <v>6651589</v>
+        <v>6651669</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7796,22 +7792,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>11:19</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>11:19</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7826,27 +7812,27 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250006</t>
+          <t>https://artportalen.se/Sighting/120666046</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120519559</v>
+        <v>136866768</v>
       </c>
       <c r="B66" t="n">
-        <v>5004</v>
+        <v>58184</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7854,46 +7840,38 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>105212</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>616596</v>
+        <v>616676</v>
       </c>
       <c r="R66" t="n">
-        <v>6651599</v>
+        <v>6651546</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7917,12 +7895,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7931,81 +7919,72 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519559</t>
+          <t>https://artportalen.se/Sighting/136866768</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120519563</v>
+        <v>136866770</v>
       </c>
       <c r="B67" t="n">
-        <v>5199</v>
+        <v>58184</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>616596</v>
+        <v>616702</v>
       </c>
       <c r="R67" t="n">
-        <v>6651599</v>
+        <v>6651635</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8029,12 +8008,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8043,69 +8032,69 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519563</t>
+          <t>https://artportalen.se/Sighting/136866770</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>136866778</v>
+        <v>137250006</v>
       </c>
       <c r="B68" t="n">
-        <v>5202</v>
+        <v>58184</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>616599</v>
+        <v>616867</v>
       </c>
       <c r="R68" t="n">
-        <v>6651694</v>
+        <v>6651589</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8132,22 +8121,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8173,63 +8162,63 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866778</t>
+          <t>https://artportalen.se/Sighting/137250006</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120541189</v>
+        <v>120519559</v>
       </c>
       <c r="B69" t="n">
-        <v>8444</v>
+        <v>5004</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106554</v>
+        <v>105212</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>616925</v>
+        <v>616596</v>
       </c>
       <c r="R69" t="n">
-        <v>6651481</v>
+        <v>6651599</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8274,27 +8263,27 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541189</t>
+          <t>https://artportalen.se/Sighting/120519559</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>137250005</v>
+        <v>120519563</v>
       </c>
       <c r="B70" t="n">
-        <v>8453</v>
+        <v>5199</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8302,37 +8291,46 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>616838</v>
+        <v>616596</v>
       </c>
       <c r="R70" t="n">
-        <v>6651458</v>
+        <v>6651599</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8356,22 +8354,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8380,33 +8368,34 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250005</t>
+          <t>https://artportalen.se/Sighting/120519563</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120511304</v>
+        <v>136866778</v>
       </c>
       <c r="B71" t="n">
-        <v>58790</v>
+        <v>5202</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8414,16 +8403,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>208245</v>
+        <v>105930</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8434,17 +8423,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>616728</v>
+        <v>616599</v>
       </c>
       <c r="R71" t="n">
-        <v>6651675</v>
+        <v>6651694</v>
       </c>
       <c r="S71" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8468,22 +8457,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8498,27 +8487,27 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511304</t>
+          <t>https://artportalen.se/Sighting/136866778</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120512658</v>
+        <v>120541189</v>
       </c>
       <c r="B72" t="n">
-        <v>40269</v>
+        <v>8444</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8526,42 +8515,46 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>214815</v>
+        <v>106554</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Större träfjäril</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cossus cossus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>616900</v>
+        <v>616925</v>
       </c>
       <c r="R72" t="n">
-        <v>6651584</v>
+        <v>6651481</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8606,79 +8599,65 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120512658</t>
+          <t>https://artportalen.se/Sighting/120541189</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120511748</v>
+        <v>137250005</v>
       </c>
       <c r="B73" t="n">
-        <v>99118</v>
+        <v>8453</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>616739</v>
+        <v>616838</v>
       </c>
       <c r="R73" t="n">
-        <v>6651702</v>
+        <v>6651458</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8702,22 +8681,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8732,69 +8711,65 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511748</t>
+          <t>https://artportalen.se/Sighting/137250005</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120551257</v>
+        <v>120511304</v>
       </c>
       <c r="B74" t="n">
-        <v>99118</v>
+        <v>58790</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>616797</v>
+        <v>616728</v>
       </c>
       <c r="R74" t="n">
-        <v>6651566</v>
+        <v>6651675</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8823,7 +8798,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8833,7 +8808,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8848,74 +8823,70 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551257</t>
+          <t>https://artportalen.se/Sighting/120511304</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>136866776</v>
+        <v>120512658</v>
       </c>
       <c r="B75" t="n">
-        <v>99391</v>
+        <v>40269</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>214815</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Större träfjäril</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cossus cossus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>616618</v>
+        <v>616900</v>
       </c>
       <c r="R75" t="n">
-        <v>6651762</v>
+        <v>6651584</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8939,22 +8910,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8963,33 +8924,34 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866776</t>
+          <t>https://artportalen.se/Sighting/120512658</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>137250001</v>
+        <v>120511748</v>
       </c>
       <c r="B76" t="n">
-        <v>99391</v>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9014,20 +8976,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>616795</v>
+        <v>616739</v>
       </c>
       <c r="R76" t="n">
-        <v>6651571</v>
+        <v>6651702</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9051,22 +9027,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9081,27 +9057,27 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250001</t>
+          <t>https://artportalen.se/Sighting/120511748</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>137250011</v>
+        <v>120551257</v>
       </c>
       <c r="B77" t="n">
-        <v>99391</v>
+        <v>99118</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9126,22 +9102,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>616616</v>
+        <v>616797</v>
       </c>
       <c r="R77" t="n">
-        <v>6651766</v>
+        <v>6651566</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9168,22 +9143,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9198,62 +9173,71 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250011</t>
+          <t>https://artportalen.se/Sighting/120551257</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120551249</v>
+        <v>136866776</v>
       </c>
       <c r="B78" t="n">
-        <v>97983</v>
+        <v>99391</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>616771</v>
+        <v>616618</v>
       </c>
       <c r="R78" t="n">
-        <v>6651647</v>
+        <v>6651762</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9280,12 +9264,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9300,62 +9294,62 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551249</t>
+          <t>https://artportalen.se/Sighting/136866776</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120551250</v>
+        <v>137250001</v>
       </c>
       <c r="B79" t="n">
-        <v>97983</v>
+        <v>99391</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>616787</v>
+        <v>616795</v>
       </c>
       <c r="R79" t="n">
-        <v>6651642</v>
+        <v>6651571</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9382,12 +9376,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9402,65 +9406,70 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551250</t>
+          <t>https://artportalen.se/Sighting/137250001</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120511185</v>
+        <v>137250011</v>
       </c>
       <c r="B80" t="n">
-        <v>97986</v>
+        <v>99391</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>616730</v>
+        <v>616616</v>
       </c>
       <c r="R80" t="n">
-        <v>6651675</v>
+        <v>6651766</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9484,22 +9493,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9514,65 +9523,74 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511185</t>
+          <t>https://artportalen.se/Sighting/137250011</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120551251</v>
+        <v>137273220</v>
       </c>
       <c r="B81" t="n">
-        <v>92328</v>
+        <v>99394</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6040162</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>616656</v>
+        <v>616624</v>
       </c>
       <c r="R81" t="n">
-        <v>6651527</v>
+        <v>6651761</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9596,12 +9614,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9616,16 +9644,555 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137273220</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>137273221</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99394</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Stora Hålsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>616609</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6651753</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137273221</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>120551249</v>
+      </c>
+      <c r="B83" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>616771</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6651647</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120551249</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>120551250</v>
+      </c>
+      <c r="B84" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>616787</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6651642</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120551250</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>120511185</v>
+      </c>
+      <c r="B85" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>616730</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6651675</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511185</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>120551251</v>
+      </c>
+      <c r="B86" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>616656</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6651527</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/120551251</t>
         </is>
@@ -9713,6 +10280,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39562-2026 artfynd.xlsx
+++ b/artfynd/A 39562-2026 artfynd.xlsx
@@ -1793,7 +1793,7 @@
         <v>136866767</v>
       </c>
       <c r="B12" t="n">
-        <v>92781</v>
+        <v>92784</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136866777</v>
       </c>
       <c r="B13" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136866772</v>
       </c>
       <c r="B14" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136866774</v>
       </c>
       <c r="B18" t="n">
-        <v>96869</v>
+        <v>96872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137250000</v>
       </c>
       <c r="B19" t="n">
-        <v>91921</v>
+        <v>91924</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>136866776</v>
       </c>
       <c r="B78" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>137250001</v>
       </c>
       <c r="B79" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>137250011</v>
       </c>
       <c r="B80" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 39562-2026 artfynd.xlsx
+++ b/artfynd/A 39562-2026 artfynd.xlsx
@@ -1105,7 +1105,7 @@
         <v>136866766</v>
       </c>
       <c r="B6" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136866780</v>
       </c>
       <c r="B7" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>137250010</v>
       </c>
       <c r="B8" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>137252175</v>
       </c>
       <c r="B9" t="n">
-        <v>81472</v>
+        <v>81482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136866767</v>
       </c>
       <c r="B12" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136866777</v>
       </c>
       <c r="B13" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136866772</v>
       </c>
       <c r="B14" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136866774</v>
       </c>
       <c r="B18" t="n">
-        <v>96872</v>
+        <v>96882</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137250000</v>
       </c>
       <c r="B19" t="n">
-        <v>91924</v>
+        <v>91934</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136866775</v>
       </c>
       <c r="B32" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>136866769</v>
       </c>
       <c r="B42" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>137250002</v>
       </c>
       <c r="B43" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>137250003</v>
       </c>
       <c r="B44" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>137250009</v>
       </c>
       <c r="B45" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>136866771</v>
       </c>
       <c r="B46" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>136866773</v>
       </c>
       <c r="B47" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>137273223</v>
       </c>
       <c r="B48" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>137273225</v>
       </c>
       <c r="B49" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>137273224</v>
       </c>
       <c r="B51" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>136866779</v>
       </c>
       <c r="B53" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>137250004</v>
       </c>
       <c r="B61" t="n">
-        <v>5485</v>
+        <v>5491</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>136866768</v>
       </c>
       <c r="B66" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>136866770</v>
       </c>
       <c r="B67" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>137250006</v>
       </c>
       <c r="B68" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>136866778</v>
       </c>
       <c r="B71" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>137250005</v>
       </c>
       <c r="B73" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>136866776</v>
       </c>
       <c r="B78" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>137250001</v>
       </c>
       <c r="B79" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>137250011</v>
       </c>
       <c r="B80" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>137273220</v>
       </c>
       <c r="B81" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>137273221</v>
       </c>
       <c r="B82" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 39562-2026 artfynd.xlsx
+++ b/artfynd/A 39562-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ86"/>
+  <dimension ref="A1:AZ93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1793,7 +1793,7 @@
         <v>136866767</v>
       </c>
       <c r="B12" t="n">
-        <v>92794</v>
+        <v>92795</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136866777</v>
       </c>
       <c r="B13" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136866772</v>
       </c>
       <c r="B14" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136866774</v>
       </c>
       <c r="B18" t="n">
-        <v>96882</v>
+        <v>96883</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137250000</v>
       </c>
       <c r="B19" t="n">
-        <v>91934</v>
+        <v>91935</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3926,10 +3926,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120518661</v>
+        <v>137326760</v>
       </c>
       <c r="B31" t="n">
-        <v>79084</v>
+        <v>93494</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3937,36 +3937,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stora Hålsjön syd om, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>616852</v>
+        <v>616735</v>
       </c>
       <c r="R31" t="n">
         <v>6651662</v>
@@ -3996,27 +3991,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Flera fläckar utan apothecier och en klunga med apothecier!</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4031,27 +4021,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120518661</t>
+          <t>https://artportalen.se/Sighting/137326760</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136866775</v>
+        <v>120518661</v>
       </c>
       <c r="B32" t="n">
-        <v>79270</v>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4077,19 +4067,24 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Stora Hålsjön syd om, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>616710</v>
+        <v>616852</v>
       </c>
       <c r="R32" t="n">
-        <v>6651797</v>
+        <v>6651662</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4113,22 +4108,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Flera fläckar utan apothecier och en klunga med apothecier!</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4143,27 +4143,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866775</t>
+          <t>https://artportalen.se/Sighting/120518661</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120510603</v>
+        <v>136866775</v>
       </c>
       <c r="B33" t="n">
-        <v>79946</v>
+        <v>79270</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4171,37 +4171,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>616717</v>
+        <v>616710</v>
       </c>
       <c r="R33" t="n">
-        <v>6651623</v>
+        <v>6651797</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4225,22 +4225,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4255,24 +4255,24 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510603</t>
+          <t>https://artportalen.se/Sighting/136866775</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120518677</v>
+        <v>120510603</v>
       </c>
       <c r="B34" t="n">
         <v>79946</v>
@@ -4303,14 +4303,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stora Hålsjön syd om, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>616852</v>
+        <v>616717</v>
       </c>
       <c r="R34" t="n">
-        <v>6651662</v>
+        <v>6651623</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4378,13 +4378,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120518677</t>
+          <t>https://artportalen.se/Sighting/120510603</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120518963</v>
+        <v>120518677</v>
       </c>
       <c r="B35" t="n">
         <v>79946</v>
@@ -4419,13 +4419,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>616658</v>
+        <v>616852</v>
       </c>
       <c r="R35" t="n">
-        <v>6651670</v>
+        <v>6651662</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4490,13 +4490,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120518963</t>
+          <t>https://artportalen.se/Sighting/120518677</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120519139</v>
+        <v>120518963</v>
       </c>
       <c r="B36" t="n">
         <v>79946</v>
@@ -4531,13 +4531,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>616625</v>
+        <v>616658</v>
       </c>
       <c r="R36" t="n">
-        <v>6651656</v>
+        <v>6651670</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4602,13 +4602,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519139</t>
+          <t>https://artportalen.se/Sighting/120518963</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120527703</v>
+        <v>120519139</v>
       </c>
       <c r="B37" t="n">
         <v>79946</v>
@@ -4637,22 +4637,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Norr om Tarmlången, Upl</t>
+          <t>Stora Hålsjön syd om, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>616650</v>
+        <v>616625</v>
       </c>
       <c r="R37" t="n">
-        <v>6651661</v>
+        <v>6651656</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4681,7 +4678,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4691,7 +4688,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4700,31 +4697,30 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120527703</t>
+          <t>https://artportalen.se/Sighting/120519139</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120543208</v>
+        <v>120527703</v>
       </c>
       <c r="B38" t="n">
         <v>79946</v>
@@ -4753,19 +4749,22 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Norr om Tarmlången, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>616888</v>
+        <v>616650</v>
       </c>
       <c r="R38" t="n">
-        <v>6651557</v>
+        <v>6651661</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4792,41 +4791,52 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Sjögren Englund</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Sjögren Englund</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120543208</t>
+          <t>https://artportalen.se/Sighting/120527703</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120549513</v>
+        <v>120543208</v>
       </c>
       <c r="B39" t="n">
         <v>79946</v>
@@ -4855,22 +4865,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>616740</v>
+        <v>616888</v>
       </c>
       <c r="R39" t="n">
-        <v>6651532</v>
+        <v>6651557</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4908,31 +4915,30 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sofia Lundell</t>
+          <t>Elin Sjögren Englund</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sofia Lundell</t>
+          <t>Elin Sjögren Englund</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120549513</t>
+          <t>https://artportalen.se/Sighting/120543208</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120549579</v>
+        <v>120549513</v>
       </c>
       <c r="B40" t="n">
         <v>79946</v>
@@ -4970,10 +4976,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>616696</v>
+        <v>616740</v>
       </c>
       <c r="R40" t="n">
-        <v>6651548</v>
+        <v>6651532</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5032,13 +5038,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120549579</t>
+          <t>https://artportalen.se/Sighting/120549513</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120551237</v>
+        <v>120549579</v>
       </c>
       <c r="B41" t="n">
         <v>79946</v>
@@ -5067,19 +5073,22 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>616697</v>
+        <v>616696</v>
       </c>
       <c r="R41" t="n">
-        <v>6651696</v>
+        <v>6651548</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5117,33 +5126,34 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Sofia Lundell</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Sofia Lundell</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551237</t>
+          <t>https://artportalen.se/Sighting/120549579</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136866769</v>
+        <v>120551237</v>
       </c>
       <c r="B42" t="n">
-        <v>80132</v>
+        <v>79946</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5171,14 +5181,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>616663</v>
+        <v>616697</v>
       </c>
       <c r="R42" t="n">
-        <v>6651632</v>
+        <v>6651696</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5205,22 +5215,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5235,24 +5235,24 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866769</t>
+          <t>https://artportalen.se/Sighting/120551237</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>137250002</v>
+        <v>136866769</v>
       </c>
       <c r="B43" t="n">
         <v>80132</v>
@@ -5283,14 +5283,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>616868</v>
+        <v>616663</v>
       </c>
       <c r="R43" t="n">
-        <v>6651544</v>
+        <v>6651632</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5317,22 +5317,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5358,13 +5358,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250002</t>
+          <t>https://artportalen.se/Sighting/136866769</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>137250003</v>
+        <v>137250002</v>
       </c>
       <c r="B44" t="n">
         <v>80132</v>
@@ -5399,10 +5399,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>616909</v>
+        <v>616868</v>
       </c>
       <c r="R44" t="n">
-        <v>6651517</v>
+        <v>6651544</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5470,13 +5470,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250003</t>
+          <t>https://artportalen.se/Sighting/137250002</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>137250009</v>
+        <v>137250003</v>
       </c>
       <c r="B45" t="n">
         <v>80132</v>
@@ -5511,10 +5511,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>616729</v>
+        <v>616909</v>
       </c>
       <c r="R45" t="n">
-        <v>6651628</v>
+        <v>6651517</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5582,52 +5582,51 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250009</t>
+          <t>https://artportalen.se/Sighting/137250003</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136866771</v>
+        <v>137250009</v>
       </c>
       <c r="B46" t="n">
-        <v>58030</v>
+        <v>80132</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>616718</v>
+        <v>616729</v>
       </c>
       <c r="R46" t="n">
-        <v>6651643</v>
+        <v>6651628</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5654,22 +5653,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5695,55 +5694,54 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866771</t>
+          <t>https://artportalen.se/Sighting/137250009</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>136866773</v>
+        <v>137326756</v>
       </c>
       <c r="B47" t="n">
-        <v>58030</v>
+        <v>80132</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>616719</v>
+        <v>616677</v>
       </c>
       <c r="R47" t="n">
-        <v>6651683</v>
+        <v>6651534</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5767,22 +5765,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5797,69 +5795,65 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866773</t>
+          <t>https://artportalen.se/Sighting/137326756</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>137273223</v>
+        <v>137326761</v>
       </c>
       <c r="B48" t="n">
-        <v>58030</v>
+        <v>80132</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>616733</v>
+        <v>616691</v>
       </c>
       <c r="R48" t="n">
-        <v>6651699</v>
+        <v>6651643</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5888,7 +5882,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5898,7 +5892,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5913,66 +5907,65 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273223</t>
+          <t>https://artportalen.se/Sighting/137326761</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>137273225</v>
+        <v>137326763</v>
       </c>
       <c r="B49" t="n">
-        <v>58030</v>
+        <v>80132</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>616633</v>
+        <v>616607</v>
       </c>
       <c r="R49" t="n">
-        <v>6651595</v>
+        <v>6651640</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6001,7 +5994,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6011,7 +6004,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6026,27 +6019,27 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273225</t>
+          <t>https://artportalen.se/Sighting/137326763</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120510212</v>
+        <v>136866771</v>
       </c>
       <c r="B50" t="n">
-        <v>57141</v>
+        <v>58030</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6054,42 +6047,38 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>616701</v>
+        <v>616718</v>
       </c>
       <c r="R50" t="n">
-        <v>6651514</v>
+        <v>6651643</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6113,27 +6102,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Fjäderpenna på häll.</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6148,27 +6132,27 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510212</t>
+          <t>https://artportalen.se/Sighting/136866771</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>137273224</v>
+        <v>136866773</v>
       </c>
       <c r="B51" t="n">
-        <v>57220</v>
+        <v>58030</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6176,41 +6160,38 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>616823</v>
+        <v>616719</v>
       </c>
       <c r="R51" t="n">
-        <v>6651621</v>
+        <v>6651683</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6234,22 +6215,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6264,70 +6245,69 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273224</t>
+          <t>https://artportalen.se/Sighting/136866773</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120510599</v>
+        <v>137273223</v>
       </c>
       <c r="B52" t="n">
-        <v>6284</v>
+        <v>58030</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100524</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovlig flatbagge</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Calitys scabra</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Thunberg, 1784)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>616710</v>
+        <v>616733</v>
       </c>
       <c r="R52" t="n">
-        <v>6651594</v>
+        <v>6651699</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6351,12 +6331,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6365,34 +6355,33 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510599</t>
+          <t>https://artportalen.se/Sighting/137273223</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136866779</v>
+        <v>137273225</v>
       </c>
       <c r="B53" t="n">
-        <v>5188</v>
+        <v>58030</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6400,37 +6389,38 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>616605</v>
+        <v>616633</v>
       </c>
       <c r="R53" t="n">
-        <v>6651693</v>
+        <v>6651595</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6454,22 +6444,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6484,27 +6474,27 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866779</t>
+          <t>https://artportalen.se/Sighting/137273225</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120541190</v>
+        <v>137326762</v>
       </c>
       <c r="B54" t="n">
-        <v>44177</v>
+        <v>58030</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6512,46 +6502,38 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>101735</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>616925</v>
+        <v>616675</v>
       </c>
       <c r="R54" t="n">
-        <v>6651481</v>
+        <v>6651657</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6575,12 +6557,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6589,75 +6581,70 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541190</t>
+          <t>https://artportalen.se/Sighting/137326762</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120510178</v>
+        <v>120510212</v>
       </c>
       <c r="B55" t="n">
-        <v>5482</v>
+        <v>57141</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>101920</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>616618</v>
+        <v>616701</v>
       </c>
       <c r="R55" t="n">
         <v>6651514</v>
@@ -6690,89 +6677,98 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Fjäderpenna på häll.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510178</t>
+          <t>https://artportalen.se/Sighting/120510212</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120510277</v>
+        <v>137273224</v>
       </c>
       <c r="B56" t="n">
-        <v>5482</v>
+        <v>57220</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>101920</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>616622</v>
+        <v>616823</v>
       </c>
       <c r="R56" t="n">
-        <v>6651505</v>
+        <v>6651621</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6799,12 +6795,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6813,67 +6819,62 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510277</t>
+          <t>https://artportalen.se/Sighting/137273224</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120511479</v>
+        <v>120510599</v>
       </c>
       <c r="B57" t="n">
-        <v>5482</v>
+        <v>6284</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>101920</v>
+        <v>100524</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Skrovlig flatbagge</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Calitys scabra</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Thunberg, 1784)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6881,13 +6882,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>616731</v>
+        <v>616710</v>
       </c>
       <c r="R57" t="n">
-        <v>6651699</v>
+        <v>6651594</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6943,63 +6944,54 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511479</t>
+          <t>https://artportalen.se/Sighting/120510599</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120512577</v>
+        <v>136866779</v>
       </c>
       <c r="B58" t="n">
-        <v>5482</v>
+        <v>5188</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>101920</v>
+        <v>100526</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>616900</v>
+        <v>616605</v>
       </c>
       <c r="R58" t="n">
-        <v>6651584</v>
+        <v>6651693</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7023,12 +7015,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7037,56 +7039,55 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120512577</t>
+          <t>https://artportalen.se/Sighting/136866779</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120519343</v>
+        <v>120541190</v>
       </c>
       <c r="B59" t="n">
-        <v>5482</v>
+        <v>44177</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>101920</v>
+        <v>101735</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7095,23 +7096,23 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>616603</v>
+        <v>616925</v>
       </c>
       <c r="R59" t="n">
-        <v>6651619</v>
+        <v>6651481</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7156,24 +7157,24 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519343</t>
+          <t>https://artportalen.se/Sighting/120541190</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120590194</v>
+        <v>120510178</v>
       </c>
       <c r="B60" t="n">
         <v>5482</v>
@@ -7202,19 +7203,28 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, söder om, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>616745</v>
+        <v>616618</v>
       </c>
       <c r="R60" t="n">
-        <v>6651703</v>
+        <v>6651514</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7252,33 +7262,34 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120590194</t>
+          <t>https://artportalen.se/Sighting/120510178</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>137250004</v>
+        <v>120510277</v>
       </c>
       <c r="B61" t="n">
-        <v>5491</v>
+        <v>5482</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7304,19 +7315,28 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>616876</v>
+        <v>616622</v>
       </c>
       <c r="R61" t="n">
-        <v>6651538</v>
+        <v>6651505</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7340,22 +7360,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7364,62 +7374,67 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250004</t>
+          <t>https://artportalen.se/Sighting/120510277</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120511338</v>
+        <v>120511479</v>
       </c>
       <c r="B62" t="n">
-        <v>4781</v>
+        <v>5482</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>102306</v>
+        <v>101920</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7427,10 +7442,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>616705</v>
+        <v>616731</v>
       </c>
       <c r="R62" t="n">
-        <v>6651732</v>
+        <v>6651699</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7489,38 +7504,38 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511338</t>
+          <t>https://artportalen.se/Sighting/120511479</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120541184</v>
+        <v>120512577</v>
       </c>
       <c r="B63" t="n">
-        <v>4781</v>
+        <v>5482</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102306</v>
+        <v>101920</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7529,23 +7544,23 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>616800</v>
+        <v>616900</v>
       </c>
       <c r="R63" t="n">
-        <v>6651576</v>
+        <v>6651584</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7590,49 +7605,49 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541184</t>
+          <t>https://artportalen.se/Sighting/120512577</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120541185</v>
+        <v>120519343</v>
       </c>
       <c r="B64" t="n">
-        <v>4781</v>
+        <v>5482</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102306</v>
+        <v>101920</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7641,23 +7656,23 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>616723</v>
+        <v>616603</v>
       </c>
       <c r="R64" t="n">
-        <v>6651708</v>
+        <v>6651619</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7702,70 +7717,62 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541185</t>
+          <t>https://artportalen.se/Sighting/120519343</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120666046</v>
+        <v>120590194</v>
       </c>
       <c r="B65" t="n">
-        <v>58114</v>
+        <v>5482</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>101920</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stora Hålsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>616874</v>
+        <v>616745</v>
       </c>
       <c r="R65" t="n">
-        <v>6651669</v>
+        <v>6651703</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7823,52 +7830,51 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120666046</t>
+          <t>https://artportalen.se/Sighting/120590194</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>136866768</v>
+        <v>137250004</v>
       </c>
       <c r="B66" t="n">
-        <v>58194</v>
+        <v>5491</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>101920</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>616676</v>
+        <v>616876</v>
       </c>
       <c r="R66" t="n">
-        <v>6651546</v>
+        <v>6651538</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7895,22 +7901,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7936,55 +7942,59 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866768</t>
+          <t>https://artportalen.se/Sighting/137250004</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>136866770</v>
+        <v>120511338</v>
       </c>
       <c r="B67" t="n">
-        <v>58194</v>
+        <v>4781</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>616702</v>
+        <v>616705</v>
       </c>
       <c r="R67" t="n">
-        <v>6651635</v>
+        <v>6651732</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8008,22 +8018,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:34</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:34</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8032,72 +8032,81 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866770</t>
+          <t>https://artportalen.se/Sighting/120511338</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>137250006</v>
+        <v>120541184</v>
       </c>
       <c r="B68" t="n">
-        <v>58194</v>
+        <v>4781</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>616867</v>
+        <v>616800</v>
       </c>
       <c r="R68" t="n">
-        <v>6651589</v>
+        <v>6651576</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8121,22 +8130,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>11:19</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>11:19</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8145,80 +8144,81 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250006</t>
+          <t>https://artportalen.se/Sighting/120541184</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120519559</v>
+        <v>120541185</v>
       </c>
       <c r="B69" t="n">
-        <v>5004</v>
+        <v>4781</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>105212</v>
+        <v>102306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>616596</v>
+        <v>616723</v>
       </c>
       <c r="R69" t="n">
-        <v>6651599</v>
+        <v>6651708</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8263,74 +8263,73 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519559</t>
+          <t>https://artportalen.se/Sighting/120541185</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120519563</v>
+        <v>120666046</v>
       </c>
       <c r="B70" t="n">
-        <v>5199</v>
+        <v>58114</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Stora Hålsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>616596</v>
+        <v>616874</v>
       </c>
       <c r="R70" t="n">
-        <v>6651599</v>
+        <v>6651669</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8368,69 +8367,69 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519563</t>
+          <t>https://artportalen.se/Sighting/120666046</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>136866778</v>
+        <v>136866768</v>
       </c>
       <c r="B71" t="n">
-        <v>5208</v>
+        <v>58194</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>616599</v>
+        <v>616676</v>
       </c>
       <c r="R71" t="n">
-        <v>6651694</v>
+        <v>6651546</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8462,7 +8461,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8472,7 +8471,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8498,63 +8497,55 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866778</t>
+          <t>https://artportalen.se/Sighting/136866768</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120541189</v>
+        <v>136866770</v>
       </c>
       <c r="B72" t="n">
-        <v>8444</v>
+        <v>58194</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>616925</v>
+        <v>616702</v>
       </c>
       <c r="R72" t="n">
-        <v>6651481</v>
+        <v>6651635</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8578,12 +8569,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8592,69 +8593,69 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541189</t>
+          <t>https://artportalen.se/Sighting/136866770</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>137250005</v>
+        <v>137250006</v>
       </c>
       <c r="B73" t="n">
-        <v>8459</v>
+        <v>58194</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>616838</v>
+        <v>616867</v>
       </c>
       <c r="R73" t="n">
-        <v>6651458</v>
+        <v>6651589</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8686,7 +8687,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8696,7 +8697,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8722,16 +8723,16 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250005</t>
+          <t>https://artportalen.se/Sighting/137250006</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120511304</v>
+        <v>137326759</v>
       </c>
       <c r="B74" t="n">
-        <v>58790</v>
+        <v>58189</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8739,16 +8740,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>208245</v>
+        <v>103023</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8757,19 +8758,20 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>616728</v>
+        <v>616916</v>
       </c>
       <c r="R74" t="n">
-        <v>6651675</v>
+        <v>6651561</v>
       </c>
       <c r="S74" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8793,22 +8795,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8823,44 +8825,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511304</t>
+          <t>https://artportalen.se/Sighting/137326759</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120512658</v>
+        <v>120519559</v>
       </c>
       <c r="B75" t="n">
-        <v>40269</v>
+        <v>5004</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>214815</v>
+        <v>105212</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Större träfjäril</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cossus cossus</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8873,17 +8875,21 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>616900</v>
+        <v>616596</v>
       </c>
       <c r="R75" t="n">
-        <v>6651584</v>
+        <v>6651599</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8942,65 +8948,60 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120512658</t>
+          <t>https://artportalen.se/Sighting/120519559</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120511748</v>
+        <v>120519563</v>
       </c>
       <c r="B76" t="n">
-        <v>99118</v>
+        <v>5199</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>616739</v>
+        <v>616596</v>
       </c>
       <c r="R76" t="n">
-        <v>6651702</v>
+        <v>6651599</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9030,93 +9031,80 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511748</t>
+          <t>https://artportalen.se/Sighting/120519563</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120551257</v>
+        <v>136866778</v>
       </c>
       <c r="B77" t="n">
-        <v>99118</v>
+        <v>5208</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>616797</v>
+        <v>616599</v>
       </c>
       <c r="R77" t="n">
-        <v>6651566</v>
+        <v>6651694</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9143,22 +9131,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9173,74 +9161,74 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551257</t>
+          <t>https://artportalen.se/Sighting/136866778</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>136866776</v>
+        <v>120541189</v>
       </c>
       <c r="B78" t="n">
-        <v>99404</v>
+        <v>8444</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>616618</v>
+        <v>616925</v>
       </c>
       <c r="R78" t="n">
-        <v>6651762</v>
+        <v>6651481</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9264,22 +9252,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9288,55 +9266,56 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866776</t>
+          <t>https://artportalen.se/Sighting/120541189</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>137250001</v>
+        <v>137250005</v>
       </c>
       <c r="B79" t="n">
-        <v>99404</v>
+        <v>8459</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9346,10 +9325,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>616795</v>
+        <v>616838</v>
       </c>
       <c r="R79" t="n">
-        <v>6651571</v>
+        <v>6651458</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9381,7 +9360,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9391,7 +9370,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9417,59 +9396,54 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250001</t>
+          <t>https://artportalen.se/Sighting/137250005</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>137250011</v>
+        <v>120511304</v>
       </c>
       <c r="B80" t="n">
-        <v>99404</v>
+        <v>58790</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>616616</v>
+        <v>616728</v>
       </c>
       <c r="R80" t="n">
-        <v>6651766</v>
+        <v>6651675</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9493,22 +9467,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9523,71 +9497,67 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250011</t>
+          <t>https://artportalen.se/Sighting/120511304</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>137273220</v>
+        <v>120512658</v>
       </c>
       <c r="B81" t="n">
-        <v>99404</v>
+        <v>40269</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>214815</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Större träfjäril</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cossus cossus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>616624</v>
+        <v>616900</v>
       </c>
       <c r="R81" t="n">
-        <v>6651761</v>
+        <v>6651584</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9614,22 +9584,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>12:44</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>12:44</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9638,80 +9598,72 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273220</t>
+          <t>https://artportalen.se/Sighting/120512658</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>137273221</v>
+        <v>137326757</v>
       </c>
       <c r="B82" t="n">
-        <v>99404</v>
+        <v>99322</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>616609</v>
+        <v>616746</v>
       </c>
       <c r="R82" t="n">
-        <v>6651753</v>
+        <v>6651625</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9740,7 +9692,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9750,7 +9702,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9765,65 +9717,79 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273221</t>
+          <t>https://artportalen.se/Sighting/137326757</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120551249</v>
+        <v>120511748</v>
       </c>
       <c r="B83" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>616771</v>
+        <v>616739</v>
       </c>
       <c r="R83" t="n">
-        <v>6651647</v>
+        <v>6651702</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9850,9 +9816,19 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9867,62 +9843,66 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551249</t>
+          <t>https://artportalen.se/Sighting/120511748</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120551250</v>
+        <v>120551257</v>
       </c>
       <c r="B84" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>616787</v>
+        <v>616797</v>
       </c>
       <c r="R84" t="n">
-        <v>6651642</v>
+        <v>6651566</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9952,9 +9932,19 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9980,54 +9970,63 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551250</t>
+          <t>https://artportalen.se/Sighting/120551257</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120511185</v>
+        <v>136866776</v>
       </c>
       <c r="B85" t="n">
-        <v>97986</v>
+        <v>99405</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>616730</v>
+        <v>616618</v>
       </c>
       <c r="R85" t="n">
-        <v>6651675</v>
+        <v>6651762</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10051,22 +10050,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10081,62 +10080,62 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511185</t>
+          <t>https://artportalen.se/Sighting/136866776</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120551251</v>
+        <v>137250001</v>
       </c>
       <c r="B86" t="n">
-        <v>92328</v>
+        <v>99405</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6040162</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>616656</v>
+        <v>616795</v>
       </c>
       <c r="R86" t="n">
-        <v>6651527</v>
+        <v>6651571</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10163,12 +10162,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10183,16 +10192,793 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137250001</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>137250011</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99405</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>st Hålsjön S, Upl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>616616</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6651766</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137250011</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>137273220</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99405</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Stora Hålsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>616624</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6651761</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137273220</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>137273221</v>
+      </c>
+      <c r="B89" t="n">
+        <v>99405</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Stora Hålsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>616609</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6651753</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137273221</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>120551249</v>
+      </c>
+      <c r="B90" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>616771</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6651647</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120551249</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>120551250</v>
+      </c>
+      <c r="B91" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>616787</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6651642</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120551250</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>120511185</v>
+      </c>
+      <c r="B92" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>616730</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6651675</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511185</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>120551251</v>
+      </c>
+      <c r="B93" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>616656</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6651527</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/120551251</t>
         </is>
@@ -10285,6 +11071,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39562-2026 artfynd.xlsx
+++ b/artfynd/A 39562-2026 artfynd.xlsx
@@ -2466,7 +2466,7 @@
         <v>136866767</v>
       </c>
       <c r="B18" t="n">
-        <v>92798</v>
+        <v>92800</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136866777</v>
       </c>
       <c r="B19" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>136866772</v>
       </c>
       <c r="B20" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>137367392</v>
       </c>
       <c r="B21" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>136866774</v>
       </c>
       <c r="B25" t="n">
-        <v>96888</v>
+        <v>96890</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>137365059</v>
       </c>
       <c r="B26" t="n">
-        <v>96888</v>
+        <v>96890</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>137365060</v>
       </c>
       <c r="B27" t="n">
-        <v>96888</v>
+        <v>96890</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>137365066</v>
       </c>
       <c r="B28" t="n">
-        <v>96888</v>
+        <v>96890</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>137365068</v>
       </c>
       <c r="B29" t="n">
-        <v>96888</v>
+        <v>96890</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>137250000</v>
       </c>
       <c r="B30" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>137364327</v>
       </c>
       <c r="B32" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>137326760</v>
       </c>
       <c r="B43" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>137326757</v>
       </c>
       <c r="B105" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>136866776</v>
       </c>
       <c r="B108" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>137250001</v>
       </c>
       <c r="B109" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>137250011</v>
       </c>
       <c r="B110" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>137273220</v>
       </c>
       <c r="B111" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>137273221</v>
       </c>
       <c r="B112" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>137364328</v>
       </c>
       <c r="B113" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>137365241</v>
       </c>
       <c r="B114" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 39562-2026 artfynd.xlsx
+++ b/artfynd/A 39562-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ118"/>
+  <dimension ref="A1:AZ123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,7 +785,7 @@
         <v>137365067</v>
       </c>
       <c r="B3" t="n">
-        <v>83499</v>
+        <v>83504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136866766</v>
       </c>
       <c r="B7" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>136866780</v>
       </c>
       <c r="B8" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>137250010</v>
       </c>
       <c r="B9" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137252175</v>
+        <v>137400528</v>
       </c>
       <c r="B10" t="n">
-        <v>81485</v>
+        <v>91699</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,37 +1561,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1049</v>
+        <v>936</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spinnfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lentaria byssiseda</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Pers.) Corner</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>st Hålsjön, Upl</t>
+          <t>Stora Hålsjön2, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616848</v>
+        <v>616712</v>
       </c>
       <c r="R10" t="n">
-        <v>6651660</v>
+        <v>6651729</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1615,22 +1615,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,27 +1645,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137252175</t>
+          <t>https://artportalen.se/Sighting/137400528</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137364334</v>
+        <v>137252175</v>
       </c>
       <c r="B11" t="n">
-        <v>81485</v>
+        <v>81490</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,17 +1693,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>st Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>616850</v>
+        <v>616848</v>
       </c>
       <c r="R11" t="n">
-        <v>6651662</v>
+        <v>6651660</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1751,34 +1751,33 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137364334</t>
+          <t>https://artportalen.se/Sighting/137252175</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137365049</v>
+        <v>137364334</v>
       </c>
       <c r="B12" t="n">
-        <v>81485</v>
+        <v>81490</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>616676</v>
+        <v>616850</v>
       </c>
       <c r="R12" t="n">
-        <v>6651570</v>
+        <v>6651662</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1845,7 +1844,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1855,7 +1854,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,33 +1863,34 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137365049</t>
+          <t>https://artportalen.se/Sighting/137364334</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137365051</v>
+        <v>137365049</v>
       </c>
       <c r="B13" t="n">
-        <v>81485</v>
+        <v>81490</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>616854</v>
+        <v>616676</v>
       </c>
       <c r="R13" t="n">
-        <v>6651549</v>
+        <v>6651570</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1993,16 +1993,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137365051</t>
+          <t>https://artportalen.se/Sighting/137365049</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137365052</v>
+        <v>137365051</v>
       </c>
       <c r="B14" t="n">
-        <v>81485</v>
+        <v>81490</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>616877</v>
+        <v>616854</v>
       </c>
       <c r="R14" t="n">
-        <v>6651525</v>
+        <v>6651549</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2105,16 +2105,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137365052</t>
+          <t>https://artportalen.se/Sighting/137365051</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137365062</v>
+        <v>137365052</v>
       </c>
       <c r="B15" t="n">
-        <v>81485</v>
+        <v>81490</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>616647</v>
+        <v>616877</v>
       </c>
       <c r="R15" t="n">
-        <v>6651588</v>
+        <v>6651525</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2217,16 +2217,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137365062</t>
+          <t>https://artportalen.se/Sighting/137365052</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120590202</v>
+        <v>137365062</v>
       </c>
       <c r="B16" t="n">
-        <v>92147</v>
+        <v>81490</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,40 +2234,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1101</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, söder om, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>616867</v>
+        <v>616647</v>
       </c>
       <c r="R16" t="n">
-        <v>6651610</v>
+        <v>6651588</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2291,17 +2288,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På av mossa övervuxen granstubbe</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,31 +2312,30 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120590202</t>
+          <t>https://artportalen.se/Sighting/137365062</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120760977</v>
+        <v>120590202</v>
       </c>
       <c r="B17" t="n">
         <v>92147</v>
@@ -2362,31 +2363,23 @@
           <t>(Peck) Jülich</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, syd om, Upl</t>
+          <t>Stora Hålsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>616848</v>
+        <v>616867</v>
       </c>
       <c r="R17" t="n">
-        <v>6651616</v>
+        <v>6651610</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2416,6 +2409,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På av mossa övervuxen granstubbe</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2428,45 +2426,30 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stump</t>
-        </is>
-      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120760977</t>
+          <t>https://artportalen.se/Sighting/120590202</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136866767</v>
+        <v>120760977</v>
       </c>
       <c r="B18" t="n">
-        <v>92800</v>
+        <v>92147</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2491,20 +2474,31 @@
           <t>(Peck) Jülich</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Stora Hålsjön, syd om, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616676</v>
+        <v>616848</v>
       </c>
       <c r="R18" t="n">
-        <v>6651546</v>
+        <v>6651616</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2528,22 +2522,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2552,17 +2536,13 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -2572,33 +2552,33 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stump</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866767</t>
+          <t>https://artportalen.se/Sighting/120760977</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136866777</v>
+        <v>136866767</v>
       </c>
       <c r="B19" t="n">
-        <v>92164</v>
+        <v>92805</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2606,21 +2586,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1101</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2630,10 +2610,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616587</v>
+        <v>616676</v>
       </c>
       <c r="R19" t="n">
-        <v>6651708</v>
+        <v>6651546</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2665,7 +2645,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2675,7 +2655,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,6 +2666,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2701,38 +2701,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866777</t>
+          <t>https://artportalen.se/Sighting/136866767</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136866772</v>
+        <v>136866777</v>
       </c>
       <c r="B20" t="n">
-        <v>92343</v>
+        <v>92169</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1503</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>616702</v>
+        <v>616587</v>
       </c>
       <c r="R20" t="n">
-        <v>6651664</v>
+        <v>6651708</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,16 +2813,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866772</t>
+          <t>https://artportalen.se/Sighting/136866777</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137367392</v>
+        <v>136866772</v>
       </c>
       <c r="B21" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,31 +2847,20 @@
           <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>st Hålsjön, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>616705</v>
+        <v>616702</v>
       </c>
       <c r="R21" t="n">
-        <v>6651665</v>
+        <v>6651664</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2895,22 +2884,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2919,7 +2908,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2931,60 +2919,71 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tomas Falk, Sebastian Kirppu, Emil V. Nilsson, Ki Mähler</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137367392</t>
+          <t>https://artportalen.se/Sighting/136866772</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120513434</v>
+        <v>137367392</v>
       </c>
       <c r="B22" t="n">
-        <v>96601</v>
+        <v>92348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2170</v>
+        <v>1503</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stora Hålsjön syd om, Upl</t>
+          <t>st Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>616954</v>
+        <v>616705</v>
       </c>
       <c r="R22" t="n">
-        <v>6651400</v>
+        <v>6651665</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3008,22 +3007,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3032,30 +3031,31 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk, Sebastian Kirppu, Emil V. Nilsson, Ki Mähler</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120513434</t>
+          <t>https://artportalen.se/Sighting/137367392</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120518741</v>
+        <v>120513434</v>
       </c>
       <c r="B23" t="n">
         <v>96601</v>
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>616852</v>
+        <v>616954</v>
       </c>
       <c r="R23" t="n">
-        <v>6651662</v>
+        <v>6651400</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3161,13 +3161,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120518741</t>
+          <t>https://artportalen.se/Sighting/120513434</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120543211</v>
+        <v>120518741</v>
       </c>
       <c r="B24" t="n">
         <v>96601</v>
@@ -3198,17 +3198,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön syd om, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>616936</v>
+        <v>616852</v>
       </c>
       <c r="R24" t="n">
-        <v>6651400</v>
+        <v>6651662</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3235,9 +3235,19 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3252,27 +3262,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Sjögren Englund</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Sjögren Englund</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120543211</t>
+          <t>https://artportalen.se/Sighting/120518741</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136866774</v>
+        <v>120543211</v>
       </c>
       <c r="B25" t="n">
-        <v>96890</v>
+        <v>96601</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3300,17 +3310,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>616698</v>
+        <v>616936</v>
       </c>
       <c r="R25" t="n">
-        <v>6651745</v>
+        <v>6651400</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3334,22 +3344,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3364,27 +3364,27 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Elin Sjögren Englund</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Elin Sjögren Englund</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866774</t>
+          <t>https://artportalen.se/Sighting/120543211</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137365059</v>
+        <v>136866774</v>
       </c>
       <c r="B26" t="n">
-        <v>96890</v>
+        <v>96896</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3412,14 +3412,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>616757</v>
+        <v>616698</v>
       </c>
       <c r="R26" t="n">
-        <v>6651641</v>
+        <v>6651745</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3446,22 +3446,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3476,27 +3476,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137365059</t>
+          <t>https://artportalen.se/Sighting/136866774</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137365060</v>
+        <v>137365059</v>
       </c>
       <c r="B27" t="n">
-        <v>96890</v>
+        <v>96896</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>616720</v>
+        <v>616757</v>
       </c>
       <c r="R27" t="n">
-        <v>6651661</v>
+        <v>6651641</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3599,16 +3599,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137365060</t>
+          <t>https://artportalen.se/Sighting/137365059</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137365066</v>
+        <v>137365060</v>
       </c>
       <c r="B28" t="n">
-        <v>96890</v>
+        <v>96896</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>616676</v>
+        <v>616720</v>
       </c>
       <c r="R28" t="n">
-        <v>6651615</v>
+        <v>6651661</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3711,16 +3711,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137365066</t>
+          <t>https://artportalen.se/Sighting/137365060</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137365068</v>
+        <v>137365066</v>
       </c>
       <c r="B29" t="n">
-        <v>96890</v>
+        <v>96896</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>616625</v>
+        <v>616676</v>
       </c>
       <c r="R29" t="n">
-        <v>6651608</v>
+        <v>6651615</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3823,16 +3823,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137365068</t>
+          <t>https://artportalen.se/Sighting/137365066</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137250000</v>
+        <v>137365068</v>
       </c>
       <c r="B30" t="n">
-        <v>91940</v>
+        <v>96896</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3840,34 +3840,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3215</v>
+        <v>2170</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>616772</v>
+        <v>616625</v>
       </c>
       <c r="R30" t="n">
-        <v>6651614</v>
+        <v>6651608</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3899,7 +3899,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3924,76 +3924,65 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250000</t>
+          <t>https://artportalen.se/Sighting/137365068</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120761198</v>
+        <v>137250000</v>
       </c>
       <c r="B31" t="n">
-        <v>93197</v>
+        <v>91945</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>3215</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, syd om, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>616726</v>
+        <v>616772</v>
       </c>
       <c r="R31" t="n">
-        <v>6651651</v>
+        <v>6651614</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4017,12 +4006,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4031,77 +4030,82 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120761198</t>
+          <t>https://artportalen.se/Sighting/137250000</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137364327</v>
+        <v>120761198</v>
       </c>
       <c r="B32" t="n">
-        <v>92127</v>
+        <v>93197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>Stora Hålsjön, syd om, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>616709</v>
+        <v>616726</v>
       </c>
       <c r="R32" t="n">
-        <v>6651597</v>
+        <v>6651651</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4125,22 +4129,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:06</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:06</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4149,33 +4143,39 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137364327</t>
+          <t>https://artportalen.se/Sighting/120761198</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120519500</v>
+        <v>137364327</v>
       </c>
       <c r="B33" t="n">
-        <v>91282</v>
+        <v>92132</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4183,37 +4183,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5685</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>616604</v>
+        <v>616709</v>
       </c>
       <c r="R33" t="n">
-        <v>6651608</v>
+        <v>6651597</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4237,22 +4237,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4267,24 +4267,24 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519500</t>
+          <t>https://artportalen.se/Sighting/137364327</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120551261</v>
+        <v>120519500</v>
       </c>
       <c r="B34" t="n">
         <v>91282</v>
@@ -4315,17 +4315,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>616607</v>
+        <v>616604</v>
       </c>
       <c r="R34" t="n">
-        <v>6651614</v>
+        <v>6651608</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4352,9 +4352,19 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4369,65 +4379,65 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551261</t>
+          <t>https://artportalen.se/Sighting/120519500</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120511104</v>
+        <v>120551261</v>
       </c>
       <c r="B35" t="n">
-        <v>93235</v>
+        <v>91282</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>5685</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>616704</v>
+        <v>616607</v>
       </c>
       <c r="R35" t="n">
-        <v>6651675</v>
+        <v>6651614</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4454,19 +4464,9 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-20</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4481,24 +4481,24 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511104</t>
+          <t>https://artportalen.se/Sighting/120551261</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120511417</v>
+        <v>120511104</v>
       </c>
       <c r="B36" t="n">
         <v>93235</v>
@@ -4526,29 +4526,20 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>616708</v>
+        <v>616704</v>
       </c>
       <c r="R36" t="n">
-        <v>6651685</v>
+        <v>6651675</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4577,7 +4568,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4587,7 +4578,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4602,24 +4593,24 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511417</t>
+          <t>https://artportalen.se/Sighting/120511104</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120512327</v>
+        <v>120511417</v>
       </c>
       <c r="B37" t="n">
         <v>93235</v>
@@ -4649,7 +4640,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4659,14 +4650,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stora Hålsjön syd om, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>616886</v>
+        <v>616708</v>
       </c>
       <c r="R37" t="n">
-        <v>6651550</v>
+        <v>6651685</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4698,7 +4689,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4708,7 +4699,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4734,13 +4725,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120512327</t>
+          <t>https://artportalen.se/Sighting/120511417</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120549502</v>
+        <v>120512327</v>
       </c>
       <c r="B38" t="n">
         <v>93235</v>
@@ -4768,20 +4759,26 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön syd om, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>616708</v>
+        <v>616886</v>
       </c>
       <c r="R38" t="n">
-        <v>6651552</v>
+        <v>6651550</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4811,42 +4808,51 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Sofia Lundell</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Sofia Lundell</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120549502</t>
+          <t>https://artportalen.se/Sighting/120512327</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120590195</v>
+        <v>120549502</v>
       </c>
       <c r="B39" t="n">
         <v>93235</v>
@@ -4880,17 +4886,17 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, söder om, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>616874</v>
+        <v>616708</v>
       </c>
       <c r="R39" t="n">
-        <v>6651669</v>
+        <v>6651552</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4935,24 +4941,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Sofia Lundell</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Sofia Lundell</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120590195</t>
+          <t>https://artportalen.se/Sighting/120549502</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120590197</v>
+        <v>120590195</v>
       </c>
       <c r="B40" t="n">
         <v>93235</v>
@@ -4990,10 +4996,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>616705</v>
+        <v>616874</v>
       </c>
       <c r="R40" t="n">
-        <v>6651645</v>
+        <v>6651669</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5052,13 +5058,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120590197</t>
+          <t>https://artportalen.se/Sighting/120590195</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120590198</v>
+        <v>120590197</v>
       </c>
       <c r="B41" t="n">
         <v>93235</v>
@@ -5096,10 +5102,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>616898</v>
+        <v>616705</v>
       </c>
       <c r="R41" t="n">
-        <v>6651543</v>
+        <v>6651645</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5158,13 +5164,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120590198</t>
+          <t>https://artportalen.se/Sighting/120590197</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120761144</v>
+        <v>120590198</v>
       </c>
       <c r="B42" t="n">
         <v>93235</v>
@@ -5192,31 +5198,23 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, syd om, Upl</t>
+          <t>Stora Hålsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>616707</v>
+        <v>616898</v>
       </c>
       <c r="R42" t="n">
-        <v>6651675</v>
+        <v>6651543</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5258,35 +5256,30 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Tallskog på blockmark</t>
-        </is>
-      </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120761144</t>
+          <t>https://artportalen.se/Sighting/120590198</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>137326760</v>
+        <v>120761144</v>
       </c>
       <c r="B43" t="n">
-        <v>93501</v>
+        <v>93235</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5311,17 +5304,28 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>Stora Hålsjön, syd om, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>616735</v>
+        <v>616707</v>
       </c>
       <c r="R43" t="n">
-        <v>6651662</v>
+        <v>6651675</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5348,22 +5352,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:48</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:48</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5372,55 +5366,61 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Tallskog på blockmark</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137326760</t>
+          <t>https://artportalen.se/Sighting/120761144</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>137364332</v>
+        <v>137326760</v>
       </c>
       <c r="B44" t="n">
-        <v>79516</v>
+        <v>93507</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5430,13 +5430,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>616876</v>
+        <v>616735</v>
       </c>
       <c r="R44" t="n">
-        <v>6651591</v>
+        <v>6651662</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5475,12 +5475,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>10 meter upp på tallstam</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5495,70 +5490,65 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137364332</t>
+          <t>https://artportalen.se/Sighting/137326760</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120518661</v>
+        <v>137364332</v>
       </c>
       <c r="B45" t="n">
-        <v>79084</v>
+        <v>79521</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stora Hålsjön syd om, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>616852</v>
+        <v>616876</v>
       </c>
       <c r="R45" t="n">
-        <v>6651662</v>
+        <v>6651591</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5582,27 +5572,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Flera fläckar utan apothecier och en klunga med apothecier!</t>
+          <t>10 meter upp på tallstam</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5617,27 +5607,27 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120518661</t>
+          <t>https://artportalen.se/Sighting/137364332</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136866775</v>
+        <v>120518661</v>
       </c>
       <c r="B46" t="n">
-        <v>79273</v>
+        <v>79084</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5663,19 +5653,24 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Stora Hålsjön syd om, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>616710</v>
+        <v>616852</v>
       </c>
       <c r="R46" t="n">
-        <v>6651797</v>
+        <v>6651662</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5699,22 +5694,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Flera fläckar utan apothecier och en klunga med apothecier!</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5729,27 +5729,27 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866775</t>
+          <t>https://artportalen.se/Sighting/120518661</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>137365065</v>
+        <v>136866775</v>
       </c>
       <c r="B47" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5777,14 +5777,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>616739</v>
+        <v>616710</v>
       </c>
       <c r="R47" t="n">
-        <v>6651625</v>
+        <v>6651797</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5811,22 +5811,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5841,27 +5841,27 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137365065</t>
+          <t>https://artportalen.se/Sighting/136866775</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120510603</v>
+        <v>137365065</v>
       </c>
       <c r="B48" t="n">
-        <v>79946</v>
+        <v>79278</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5869,37 +5869,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>616717</v>
+        <v>616739</v>
       </c>
       <c r="R48" t="n">
-        <v>6651623</v>
+        <v>6651625</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5923,22 +5923,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5953,24 +5953,24 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510603</t>
+          <t>https://artportalen.se/Sighting/137365065</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120518677</v>
+        <v>120510603</v>
       </c>
       <c r="B49" t="n">
         <v>79946</v>
@@ -6001,14 +6001,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stora Hålsjön syd om, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>616852</v>
+        <v>616717</v>
       </c>
       <c r="R49" t="n">
-        <v>6651662</v>
+        <v>6651623</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6076,13 +6076,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120518677</t>
+          <t>https://artportalen.se/Sighting/120510603</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120518963</v>
+        <v>120518677</v>
       </c>
       <c r="B50" t="n">
         <v>79946</v>
@@ -6117,13 +6117,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>616658</v>
+        <v>616852</v>
       </c>
       <c r="R50" t="n">
-        <v>6651670</v>
+        <v>6651662</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6188,13 +6188,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120518963</t>
+          <t>https://artportalen.se/Sighting/120518677</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120519139</v>
+        <v>120518963</v>
       </c>
       <c r="B51" t="n">
         <v>79946</v>
@@ -6229,13 +6229,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>616625</v>
+        <v>616658</v>
       </c>
       <c r="R51" t="n">
-        <v>6651656</v>
+        <v>6651670</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6300,13 +6300,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519139</t>
+          <t>https://artportalen.se/Sighting/120518963</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120527703</v>
+        <v>120519139</v>
       </c>
       <c r="B52" t="n">
         <v>79946</v>
@@ -6335,22 +6335,19 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Norr om Tarmlången, Upl</t>
+          <t>Stora Hålsjön syd om, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>616650</v>
+        <v>616625</v>
       </c>
       <c r="R52" t="n">
-        <v>6651661</v>
+        <v>6651656</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6379,7 +6376,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6389,7 +6386,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6398,31 +6395,30 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120527703</t>
+          <t>https://artportalen.se/Sighting/120519139</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120543208</v>
+        <v>120527703</v>
       </c>
       <c r="B53" t="n">
         <v>79946</v>
@@ -6451,19 +6447,22 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Norr om Tarmlången, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>616888</v>
+        <v>616650</v>
       </c>
       <c r="R53" t="n">
-        <v>6651557</v>
+        <v>6651661</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6490,41 +6489,52 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elin Sjögren Englund</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Sjögren Englund</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120543208</t>
+          <t>https://artportalen.se/Sighting/120527703</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120549513</v>
+        <v>120543208</v>
       </c>
       <c r="B54" t="n">
         <v>79946</v>
@@ -6553,22 +6563,19 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>616740</v>
+        <v>616888</v>
       </c>
       <c r="R54" t="n">
-        <v>6651532</v>
+        <v>6651557</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6606,31 +6613,30 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Sofia Lundell</t>
+          <t>Elin Sjögren Englund</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Sofia Lundell</t>
+          <t>Elin Sjögren Englund</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120549513</t>
+          <t>https://artportalen.se/Sighting/120543208</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120549579</v>
+        <v>120549513</v>
       </c>
       <c r="B55" t="n">
         <v>79946</v>
@@ -6668,10 +6674,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>616696</v>
+        <v>616740</v>
       </c>
       <c r="R55" t="n">
-        <v>6651548</v>
+        <v>6651532</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6730,13 +6736,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120549579</t>
+          <t>https://artportalen.se/Sighting/120549513</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120551237</v>
+        <v>120549579</v>
       </c>
       <c r="B56" t="n">
         <v>79946</v>
@@ -6765,19 +6771,22 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>616697</v>
+        <v>616696</v>
       </c>
       <c r="R56" t="n">
-        <v>6651696</v>
+        <v>6651548</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6815,33 +6824,34 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Sofia Lundell</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Sofia Lundell</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551237</t>
+          <t>https://artportalen.se/Sighting/120549579</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>136866769</v>
+        <v>120551237</v>
       </c>
       <c r="B57" t="n">
-        <v>80135</v>
+        <v>79946</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6869,14 +6879,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>616663</v>
+        <v>616697</v>
       </c>
       <c r="R57" t="n">
-        <v>6651632</v>
+        <v>6651696</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6903,22 +6913,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6933,27 +6933,27 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866769</t>
+          <t>https://artportalen.se/Sighting/120551237</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>137250002</v>
+        <v>136866769</v>
       </c>
       <c r="B58" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6981,14 +6981,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>616868</v>
+        <v>616663</v>
       </c>
       <c r="R58" t="n">
-        <v>6651544</v>
+        <v>6651632</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7015,22 +7015,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7056,16 +7056,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250002</t>
+          <t>https://artportalen.se/Sighting/136866769</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>137250003</v>
+        <v>137250002</v>
       </c>
       <c r="B59" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7097,10 +7097,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>616909</v>
+        <v>616868</v>
       </c>
       <c r="R59" t="n">
-        <v>6651517</v>
+        <v>6651544</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7168,16 +7168,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250003</t>
+          <t>https://artportalen.se/Sighting/137250002</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>137250009</v>
+        <v>137250003</v>
       </c>
       <c r="B60" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>616729</v>
+        <v>616909</v>
       </c>
       <c r="R60" t="n">
-        <v>6651628</v>
+        <v>6651517</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7280,16 +7280,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250009</t>
+          <t>https://artportalen.se/Sighting/137250003</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>137326756</v>
+        <v>137250009</v>
       </c>
       <c r="B61" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7317,17 +7317,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>616677</v>
+        <v>616729</v>
       </c>
       <c r="R61" t="n">
-        <v>6651534</v>
+        <v>6651628</v>
       </c>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7381,27 +7381,27 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137326756</t>
+          <t>https://artportalen.se/Sighting/137250009</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>137326761</v>
+        <v>137326756</v>
       </c>
       <c r="B62" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7433,13 +7433,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>616691</v>
+        <v>616677</v>
       </c>
       <c r="R62" t="n">
-        <v>6651643</v>
+        <v>6651534</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7504,16 +7504,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137326761</t>
+          <t>https://artportalen.se/Sighting/137326756</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>137326763</v>
+        <v>137326761</v>
       </c>
       <c r="B63" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7545,13 +7545,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>616607</v>
+        <v>616691</v>
       </c>
       <c r="R63" t="n">
-        <v>6651640</v>
+        <v>6651643</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7616,16 +7616,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137326763</t>
+          <t>https://artportalen.se/Sighting/137326761</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>137365053</v>
+        <v>137326763</v>
       </c>
       <c r="B64" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7657,13 +7657,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>616875</v>
+        <v>616607</v>
       </c>
       <c r="R64" t="n">
-        <v>6651523</v>
+        <v>6651640</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7717,27 +7717,27 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137365053</t>
+          <t>https://artportalen.se/Sighting/137326763</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>137365061</v>
+        <v>137365053</v>
       </c>
       <c r="B65" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7769,10 +7769,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>616681</v>
+        <v>616875</v>
       </c>
       <c r="R65" t="n">
-        <v>6651672</v>
+        <v>6651523</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7840,16 +7840,16 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137365061</t>
+          <t>https://artportalen.se/Sighting/137365053</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>137365063</v>
+        <v>137365061</v>
       </c>
       <c r="B66" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7881,10 +7881,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>616692</v>
+        <v>616681</v>
       </c>
       <c r="R66" t="n">
-        <v>6651632</v>
+        <v>6651672</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7952,16 +7952,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137365063</t>
+          <t>https://artportalen.se/Sighting/137365061</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>137365064</v>
+        <v>137365063</v>
       </c>
       <c r="B67" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7993,10 +7993,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>616720</v>
+        <v>616692</v>
       </c>
       <c r="R67" t="n">
-        <v>6651629</v>
+        <v>6651632</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8028,7 +8028,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8064,16 +8064,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137365064</t>
+          <t>https://artportalen.se/Sighting/137365063</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>137365069</v>
+        <v>137365064</v>
       </c>
       <c r="B68" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8105,10 +8105,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>616630</v>
+        <v>616720</v>
       </c>
       <c r="R68" t="n">
-        <v>6651609</v>
+        <v>6651629</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8140,7 +8140,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8176,16 +8176,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137365069</t>
+          <t>https://artportalen.se/Sighting/137365064</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>137365070</v>
+        <v>137365069</v>
       </c>
       <c r="B69" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8217,10 +8217,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>616622</v>
+        <v>616630</v>
       </c>
       <c r="R69" t="n">
-        <v>6651610</v>
+        <v>6651609</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8252,7 +8252,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8288,52 +8288,51 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137365070</t>
+          <t>https://artportalen.se/Sighting/137365069</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>136866771</v>
+        <v>137365070</v>
       </c>
       <c r="B70" t="n">
-        <v>58031</v>
+        <v>80140</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>616718</v>
+        <v>616622</v>
       </c>
       <c r="R70" t="n">
-        <v>6651643</v>
+        <v>6651610</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8360,22 +8359,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8390,27 +8389,27 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866771</t>
+          <t>https://artportalen.se/Sighting/137365070</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>136866773</v>
+        <v>136866771</v>
       </c>
       <c r="B71" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8443,10 +8442,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>616719</v>
+        <v>616718</v>
       </c>
       <c r="R71" t="n">
-        <v>6651683</v>
+        <v>6651643</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8478,7 +8477,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8488,7 +8487,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8514,16 +8513,16 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866773</t>
+          <t>https://artportalen.se/Sighting/136866771</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>137273223</v>
+        <v>136866773</v>
       </c>
       <c r="B72" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8549,23 +8548,20 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>616733</v>
+        <v>616719</v>
       </c>
       <c r="R72" t="n">
-        <v>6651699</v>
+        <v>6651683</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8589,22 +8585,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8619,27 +8615,27 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273223</t>
+          <t>https://artportalen.se/Sighting/136866773</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>137273225</v>
+        <v>137273223</v>
       </c>
       <c r="B73" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8665,17 +8661,20 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>616633</v>
+        <v>616733</v>
       </c>
       <c r="R73" t="n">
-        <v>6651595</v>
+        <v>6651699</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8707,7 +8706,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8717,7 +8716,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8743,16 +8742,16 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273225</t>
+          <t>https://artportalen.se/Sighting/137273223</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>137326762</v>
+        <v>137273225</v>
       </c>
       <c r="B74" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8781,17 +8780,17 @@
       <c r="M74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>616675</v>
+        <v>616633</v>
       </c>
       <c r="R74" t="n">
-        <v>6651657</v>
+        <v>6651595</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8820,7 +8819,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8830,7 +8829,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8845,27 +8844,27 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137326762</t>
+          <t>https://artportalen.se/Sighting/137273225</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>137364335</v>
+        <v>137326762</v>
       </c>
       <c r="B75" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8891,23 +8890,20 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>616719</v>
+        <v>616675</v>
       </c>
       <c r="R75" t="n">
-        <v>6651691</v>
+        <v>6651657</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8936,7 +8932,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8946,7 +8942,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8961,27 +8957,27 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137364335</t>
+          <t>https://artportalen.se/Sighting/137326762</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>137365242</v>
+        <v>137364335</v>
       </c>
       <c r="B76" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9013,17 +9009,17 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>StHalsjon14okt2026 (1), Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>616588</v>
+        <v>616719</v>
       </c>
       <c r="R76" t="n">
-        <v>6651688</v>
+        <v>6651691</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9052,7 +9048,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9062,7 +9058,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9077,27 +9073,27 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137365242</t>
+          <t>https://artportalen.se/Sighting/137364335</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120510212</v>
+        <v>137365242</v>
       </c>
       <c r="B77" t="n">
-        <v>57141</v>
+        <v>58032</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9105,42 +9101,41 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>StHalsjon14okt2026 (1), Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>616701</v>
+        <v>616588</v>
       </c>
       <c r="R77" t="n">
-        <v>6651514</v>
+        <v>6651688</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9164,27 +9159,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Fjäderpenna på häll.</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9199,27 +9189,27 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510212</t>
+          <t>https://artportalen.se/Sighting/137365242</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>137273224</v>
+        <v>120510212</v>
       </c>
       <c r="B78" t="n">
-        <v>57221</v>
+        <v>57141</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9245,20 +9235,21 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>616823</v>
+        <v>616701</v>
       </c>
       <c r="R78" t="n">
-        <v>6651621</v>
+        <v>6651514</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9285,22 +9276,27 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Fjäderpenna på häll.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9315,70 +9311,69 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273224</t>
+          <t>https://artportalen.se/Sighting/120510212</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120510599</v>
+        <v>137273224</v>
       </c>
       <c r="B79" t="n">
-        <v>6284</v>
+        <v>57221</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100524</v>
+        <v>100138</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovlig flatbagge</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Calitys scabra</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Thunberg, 1784)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>616710</v>
+        <v>616823</v>
       </c>
       <c r="R79" t="n">
-        <v>6651594</v>
+        <v>6651621</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9402,12 +9397,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9416,72 +9421,76 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510599</t>
+          <t>https://artportalen.se/Sighting/137273224</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>136866779</v>
+        <v>120510599</v>
       </c>
       <c r="B80" t="n">
-        <v>5188</v>
+        <v>6284</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100526</v>
+        <v>100524</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skrovlig flatbagge</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Calitys scabra</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Thunberg, 1784)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>616605</v>
+        <v>616710</v>
       </c>
       <c r="R80" t="n">
-        <v>6651693</v>
+        <v>6651594</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9505,22 +9514,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>15:34</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>15:34</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9529,33 +9528,34 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866779</t>
+          <t>https://artportalen.se/Sighting/120510599</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120541190</v>
+        <v>136866779</v>
       </c>
       <c r="B81" t="n">
-        <v>44177</v>
+        <v>5188</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9563,46 +9563,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>101735</v>
+        <v>100526</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>616925</v>
+        <v>616605</v>
       </c>
       <c r="R81" t="n">
-        <v>6651481</v>
+        <v>6651693</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9626,12 +9617,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9640,56 +9641,55 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541190</t>
+          <t>https://artportalen.se/Sighting/136866779</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120510178</v>
+        <v>120541190</v>
       </c>
       <c r="B82" t="n">
-        <v>5482</v>
+        <v>44177</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>101920</v>
+        <v>101735</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9698,7 +9698,7 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -9708,13 +9708,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>616618</v>
+        <v>616925</v>
       </c>
       <c r="R82" t="n">
-        <v>6651514</v>
+        <v>6651481</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9759,24 +9759,24 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510178</t>
+          <t>https://artportalen.se/Sighting/120541190</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120510277</v>
+        <v>120510178</v>
       </c>
       <c r="B83" t="n">
         <v>5482</v>
@@ -9816,14 +9816,14 @@
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>616622</v>
+        <v>616618</v>
       </c>
       <c r="R83" t="n">
-        <v>6651505</v>
+        <v>6651514</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9882,13 +9882,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510277</t>
+          <t>https://artportalen.se/Sighting/120510178</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120511479</v>
+        <v>120510277</v>
       </c>
       <c r="B84" t="n">
         <v>5482</v>
@@ -9932,10 +9932,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>616731</v>
+        <v>616622</v>
       </c>
       <c r="R84" t="n">
-        <v>6651699</v>
+        <v>6651505</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9994,13 +9994,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511479</t>
+          <t>https://artportalen.se/Sighting/120510277</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120512577</v>
+        <v>120511479</v>
       </c>
       <c r="B85" t="n">
         <v>5482</v>
@@ -10044,10 +10044,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>616900</v>
+        <v>616731</v>
       </c>
       <c r="R85" t="n">
-        <v>6651584</v>
+        <v>6651699</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10106,13 +10106,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120512577</t>
+          <t>https://artportalen.se/Sighting/120511479</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120519343</v>
+        <v>120512577</v>
       </c>
       <c r="B86" t="n">
         <v>5482</v>
@@ -10156,10 +10156,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>616603</v>
+        <v>616900</v>
       </c>
       <c r="R86" t="n">
-        <v>6651619</v>
+        <v>6651584</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10218,13 +10218,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519343</t>
+          <t>https://artportalen.se/Sighting/120512577</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120590194</v>
+        <v>120519343</v>
       </c>
       <c r="B87" t="n">
         <v>5482</v>
@@ -10253,19 +10253,28 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, söder om, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>616745</v>
+        <v>616603</v>
       </c>
       <c r="R87" t="n">
-        <v>6651703</v>
+        <v>6651619</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10303,33 +10312,34 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120590194</t>
+          <t>https://artportalen.se/Sighting/120519343</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>137250004</v>
+        <v>120590194</v>
       </c>
       <c r="B88" t="n">
-        <v>5491</v>
+        <v>5482</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10357,17 +10367,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>Stora Hålsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>616876</v>
+        <v>616745</v>
       </c>
       <c r="R88" t="n">
-        <v>6651538</v>
+        <v>6651703</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10391,22 +10401,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10421,70 +10421,65 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250004</t>
+          <t>https://artportalen.se/Sighting/120590194</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120511338</v>
+        <v>137250004</v>
       </c>
       <c r="B89" t="n">
-        <v>4781</v>
+        <v>5491</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>102306</v>
+        <v>101920</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>616705</v>
+        <v>616876</v>
       </c>
       <c r="R89" t="n">
-        <v>6651732</v>
+        <v>6651538</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10508,12 +10503,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10522,31 +10527,30 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511338</t>
+          <t>https://artportalen.se/Sighting/137250004</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120541184</v>
+        <v>120511338</v>
       </c>
       <c r="B90" t="n">
         <v>4781</v>
@@ -10578,25 +10582,21 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>616800</v>
+        <v>616705</v>
       </c>
       <c r="R90" t="n">
-        <v>6651576</v>
+        <v>6651732</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10641,24 +10641,24 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541184</t>
+          <t>https://artportalen.se/Sighting/120511338</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120541185</v>
+        <v>120541184</v>
       </c>
       <c r="B91" t="n">
         <v>4781</v>
@@ -10702,10 +10702,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>616723</v>
+        <v>616800</v>
       </c>
       <c r="R91" t="n">
-        <v>6651708</v>
+        <v>6651576</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -10764,62 +10764,63 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541185</t>
+          <t>https://artportalen.se/Sighting/120541184</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120666046</v>
+        <v>120541185</v>
       </c>
       <c r="B92" t="n">
-        <v>58114</v>
+        <v>4781</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, söder om, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>616874</v>
+        <v>616723</v>
       </c>
       <c r="R92" t="n">
-        <v>6651669</v>
+        <v>6651708</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10857,33 +10858,34 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120666046</t>
+          <t>https://artportalen.se/Sighting/120541185</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>136866768</v>
+        <v>120666046</v>
       </c>
       <c r="B93" t="n">
-        <v>58195</v>
+        <v>58114</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10909,20 +10911,27 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Stora Hålsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>616676</v>
+        <v>616874</v>
       </c>
       <c r="R93" t="n">
-        <v>6651546</v>
+        <v>6651669</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10946,22 +10955,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10976,27 +10975,27 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866768</t>
+          <t>https://artportalen.se/Sighting/120666046</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>136866770</v>
+        <v>136866768</v>
       </c>
       <c r="B94" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11029,10 +11028,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>616702</v>
+        <v>616676</v>
       </c>
       <c r="R94" t="n">
-        <v>6651635</v>
+        <v>6651546</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11064,7 +11063,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11074,7 +11073,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11100,16 +11099,16 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866770</t>
+          <t>https://artportalen.se/Sighting/136866768</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>137250006</v>
+        <v>136866770</v>
       </c>
       <c r="B95" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11138,14 +11137,14 @@
       <c r="M95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>616867</v>
+        <v>616702</v>
       </c>
       <c r="R95" t="n">
-        <v>6651589</v>
+        <v>6651635</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11172,22 +11171,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11213,16 +11212,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250006</t>
+          <t>https://artportalen.se/Sighting/136866770</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>137364331</v>
+        <v>137250006</v>
       </c>
       <c r="B96" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11247,25 +11246,18 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>616886</v>
+        <v>616867</v>
       </c>
       <c r="R96" t="n">
-        <v>6651567</v>
+        <v>6651589</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11297,7 +11289,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11307,7 +11299,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11322,66 +11314,73 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137364331</t>
+          <t>https://artportalen.se/Sighting/137250006</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>137326759</v>
+        <v>137364331</v>
       </c>
       <c r="B97" t="n">
-        <v>58190</v>
+        <v>58196</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>616916</v>
+        <v>616886</v>
       </c>
       <c r="R97" t="n">
-        <v>6651561</v>
+        <v>6651567</v>
       </c>
       <c r="S97" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11410,7 +11409,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11420,7 +11419,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11435,27 +11434,27 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137326759</t>
+          <t>https://artportalen.se/Sighting/137364331</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120519559</v>
+        <v>137400529</v>
       </c>
       <c r="B98" t="n">
-        <v>5004</v>
+        <v>58196</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11463,46 +11462,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>105212</v>
+        <v>103021</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Stora Hålsjön2, Upl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>616596</v>
+        <v>616756</v>
       </c>
       <c r="R98" t="n">
-        <v>6651599</v>
+        <v>6651695</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11526,12 +11516,27 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Upprörd/varbande</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11540,81 +11545,75 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519559</t>
+          <t>https://artportalen.se/Sighting/137400529</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120519563</v>
+        <v>137400531</v>
       </c>
       <c r="B99" t="n">
-        <v>5199</v>
+        <v>58196</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Stora Hålsjön2, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>616596</v>
+        <v>616904</v>
       </c>
       <c r="R99" t="n">
-        <v>6651599</v>
+        <v>6651545</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11638,12 +11637,27 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11652,69 +11666,76 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519563</t>
+          <t>https://artportalen.se/Sighting/137400531</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>136866778</v>
+        <v>137404140</v>
       </c>
       <c r="B100" t="n">
-        <v>5208</v>
+        <v>58196</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Söder om Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>616599</v>
+        <v>616886</v>
       </c>
       <c r="R100" t="n">
-        <v>6651694</v>
+        <v>6651592</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11741,22 +11762,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11771,27 +11792,27 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866778</t>
+          <t>https://artportalen.se/Sighting/137404140</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120541189</v>
+        <v>137326759</v>
       </c>
       <c r="B101" t="n">
-        <v>8444</v>
+        <v>58191</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11799,46 +11820,38 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106554</v>
+        <v>103023</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>616925</v>
+        <v>616916</v>
       </c>
       <c r="R101" t="n">
-        <v>6651481</v>
+        <v>6651561</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11862,12 +11875,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11876,34 +11899,33 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541189</t>
+          <t>https://artportalen.se/Sighting/137326759</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>137250005</v>
+        <v>137404128</v>
       </c>
       <c r="B102" t="n">
-        <v>8459</v>
+        <v>58191</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11911,37 +11933,41 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106554</v>
+        <v>103023</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>Söder om Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>616838</v>
+        <v>616769</v>
       </c>
       <c r="R102" t="n">
-        <v>6651458</v>
+        <v>6651687</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11965,22 +11991,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11995,44 +12021,44 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250005</t>
+          <t>https://artportalen.se/Sighting/137404128</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120511304</v>
+        <v>120519559</v>
       </c>
       <c r="B103" t="n">
-        <v>58790</v>
+        <v>5004</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>208245</v>
+        <v>105212</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -12041,19 +12067,28 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>616728</v>
+        <v>616596</v>
       </c>
       <c r="R103" t="n">
-        <v>6651675</v>
+        <v>6651599</v>
       </c>
       <c r="S103" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12080,54 +12115,45 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511304</t>
+          <t>https://artportalen.se/Sighting/120519559</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120512658</v>
+        <v>120519563</v>
       </c>
       <c r="B104" t="n">
-        <v>40269</v>
+        <v>5199</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12135,16 +12161,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>214815</v>
+        <v>105930</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Större träfjäril</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cossus cossus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -12157,17 +12183,21 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>616900</v>
+        <v>616596</v>
       </c>
       <c r="R104" t="n">
-        <v>6651584</v>
+        <v>6651599</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12226,16 +12256,16 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120512658</t>
+          <t>https://artportalen.se/Sighting/120519563</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>137326757</v>
+        <v>136866778</v>
       </c>
       <c r="B105" t="n">
-        <v>99329</v>
+        <v>5208</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12243,37 +12273,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>219790</v>
+        <v>105930</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>616746</v>
+        <v>616599</v>
       </c>
       <c r="R105" t="n">
-        <v>6651625</v>
+        <v>6651694</v>
       </c>
       <c r="S105" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12297,22 +12327,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12327,79 +12357,74 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137326757</t>
+          <t>https://artportalen.se/Sighting/136866778</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120511748</v>
+        <v>120541189</v>
       </c>
       <c r="B106" t="n">
-        <v>99118</v>
+        <v>8444</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>616739</v>
+        <v>616925</v>
       </c>
       <c r="R106" t="n">
-        <v>6651702</v>
+        <v>6651481</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12426,93 +12451,80 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511748</t>
+          <t>https://artportalen.se/Sighting/120541189</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120551257</v>
+        <v>137250005</v>
       </c>
       <c r="B107" t="n">
-        <v>99118</v>
+        <v>8459</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>616797</v>
+        <v>616838</v>
       </c>
       <c r="R107" t="n">
-        <v>6651566</v>
+        <v>6651458</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12539,22 +12551,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12569,74 +12581,65 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551257</t>
+          <t>https://artportalen.se/Sighting/137250005</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>136866776</v>
+        <v>120511304</v>
       </c>
       <c r="B108" t="n">
-        <v>99412</v>
+        <v>58790</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>616618</v>
+        <v>616728</v>
       </c>
       <c r="R108" t="n">
-        <v>6651762</v>
+        <v>6651675</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12660,22 +12663,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12690,65 +12693,70 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866776</t>
+          <t>https://artportalen.se/Sighting/120511304</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>137250001</v>
+        <v>120512658</v>
       </c>
       <c r="B109" t="n">
-        <v>99412</v>
+        <v>40269</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>214815</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Större träfjäril</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cossus cossus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>616795</v>
+        <v>616900</v>
       </c>
       <c r="R109" t="n">
-        <v>6651571</v>
+        <v>6651584</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12772,22 +12780,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12796,76 +12794,72 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250001</t>
+          <t>https://artportalen.se/Sighting/120512658</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>137250011</v>
+        <v>137326757</v>
       </c>
       <c r="B110" t="n">
-        <v>99412</v>
+        <v>99335</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>616616</v>
+        <v>616746</v>
       </c>
       <c r="R110" t="n">
-        <v>6651766</v>
+        <v>6651625</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12894,7 +12888,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12904,7 +12898,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12919,27 +12913,27 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250011</t>
+          <t>https://artportalen.se/Sighting/137326757</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>137273220</v>
+        <v>120511748</v>
       </c>
       <c r="B111" t="n">
-        <v>99412</v>
+        <v>99118</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12966,24 +12960,29 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>616624</v>
+        <v>616739</v>
       </c>
       <c r="R111" t="n">
-        <v>6651761</v>
+        <v>6651702</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13010,22 +13009,22 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13040,27 +13039,27 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273220</t>
+          <t>https://artportalen.se/Sighting/120511748</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>137273221</v>
+        <v>120551257</v>
       </c>
       <c r="B112" t="n">
-        <v>99412</v>
+        <v>99118</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13087,27 +13086,22 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>616609</v>
+        <v>616797</v>
       </c>
       <c r="R112" t="n">
-        <v>6651753</v>
+        <v>6651566</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13131,22 +13125,22 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13161,27 +13155,27 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273221</t>
+          <t>https://artportalen.se/Sighting/120551257</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>137364328</v>
+        <v>136866776</v>
       </c>
       <c r="B113" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13208,27 +13202,24 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>616802</v>
+        <v>616618</v>
       </c>
       <c r="R113" t="n">
-        <v>6651571</v>
+        <v>6651762</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13255,22 +13246,22 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13279,34 +13270,33 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137364328</t>
+          <t>https://artportalen.se/Sighting/136866776</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>137365241</v>
+        <v>137250001</v>
       </c>
       <c r="B114" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13332,23 +13322,19 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>StHalsjon14okt2026 (1), Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>616585</v>
+        <v>616795</v>
       </c>
       <c r="R114" t="n">
-        <v>6651711</v>
+        <v>6651571</v>
       </c>
       <c r="S114" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13377,7 +13363,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13387,7 +13373,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13396,69 +13382,73 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137365241</t>
+          <t>https://artportalen.se/Sighting/137250001</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120551249</v>
+        <v>137250011</v>
       </c>
       <c r="B115" t="n">
-        <v>97983</v>
+        <v>99418</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>616771</v>
+        <v>616616</v>
       </c>
       <c r="R115" t="n">
-        <v>6651647</v>
+        <v>6651766</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13485,12 +13475,22 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13505,65 +13505,74 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551249</t>
+          <t>https://artportalen.se/Sighting/137250011</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120551250</v>
+        <v>137273220</v>
       </c>
       <c r="B116" t="n">
-        <v>97983</v>
+        <v>99418</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>616787</v>
+        <v>616624</v>
       </c>
       <c r="R116" t="n">
-        <v>6651642</v>
+        <v>6651761</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13587,12 +13596,22 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13607,62 +13626,71 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551250</t>
+          <t>https://artportalen.se/Sighting/137273220</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120511185</v>
+        <v>137273221</v>
       </c>
       <c r="B117" t="n">
-        <v>97986</v>
+        <v>99418</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>616730</v>
+        <v>616609</v>
       </c>
       <c r="R117" t="n">
-        <v>6651675</v>
+        <v>6651753</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13689,22 +13717,22 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13719,62 +13747,74 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511185</t>
+          <t>https://artportalen.se/Sighting/137273221</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120551251</v>
+        <v>137364328</v>
       </c>
       <c r="B118" t="n">
-        <v>92328</v>
+        <v>99418</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6040162</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>616656</v>
+        <v>616802</v>
       </c>
       <c r="R118" t="n">
-        <v>6651527</v>
+        <v>6651571</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13801,12 +13841,22 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13815,22 +13865,558 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137364328</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>137365241</v>
+      </c>
+      <c r="B119" t="n">
+        <v>99418</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>StHalsjon14okt2026 (1), Upl</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>616585</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6651711</v>
+      </c>
+      <c r="S119" t="n">
+        <v>6</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137365241</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>120551249</v>
+      </c>
+      <c r="B120" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>616771</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6651647</v>
+      </c>
+      <c r="S120" t="n">
+        <v>5</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120551249</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120551250</v>
+      </c>
+      <c r="B121" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>616787</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6651642</v>
+      </c>
+      <c r="S121" t="n">
+        <v>5</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120551250</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>120511185</v>
+      </c>
+      <c r="B122" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>616730</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6651675</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511185</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>120551251</v>
+      </c>
+      <c r="B123" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>616656</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6651527</v>
+      </c>
+      <c r="S123" t="n">
+        <v>5</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/120551251</t>
         </is>
@@ -13955,6 +14541,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39562-2026 artfynd.xlsx
+++ b/artfynd/A 39562-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ123"/>
+  <dimension ref="A1:AZ126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8406,49 +8406,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>136866771</v>
+        <v>137408230</v>
       </c>
       <c r="B71" t="n">
-        <v>58032</v>
+        <v>80140</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>616718</v>
+        <v>616871</v>
       </c>
       <c r="R71" t="n">
-        <v>6651643</v>
+        <v>6651543</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8472,22 +8471,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8502,24 +8501,24 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866771</t>
+          <t>https://artportalen.se/Sighting/137408230</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>136866773</v>
+        <v>136866771</v>
       </c>
       <c r="B72" t="n">
         <v>58032</v>
@@ -8555,10 +8554,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>616719</v>
+        <v>616718</v>
       </c>
       <c r="R72" t="n">
-        <v>6651683</v>
+        <v>6651643</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8590,7 +8589,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8600,7 +8599,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8626,13 +8625,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866773</t>
+          <t>https://artportalen.se/Sighting/136866771</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>137273223</v>
+        <v>136866773</v>
       </c>
       <c r="B73" t="n">
         <v>58032</v>
@@ -8661,23 +8660,20 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>616733</v>
+        <v>616719</v>
       </c>
       <c r="R73" t="n">
-        <v>6651699</v>
+        <v>6651683</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8701,22 +8697,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8731,24 +8727,24 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273223</t>
+          <t>https://artportalen.se/Sighting/136866773</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>137273225</v>
+        <v>137273223</v>
       </c>
       <c r="B74" t="n">
         <v>58032</v>
@@ -8777,17 +8773,20 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>616633</v>
+        <v>616733</v>
       </c>
       <c r="R74" t="n">
-        <v>6651595</v>
+        <v>6651699</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8819,7 +8818,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8829,7 +8828,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8855,13 +8854,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273225</t>
+          <t>https://artportalen.se/Sighting/137273223</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>137326762</v>
+        <v>137273225</v>
       </c>
       <c r="B75" t="n">
         <v>58032</v>
@@ -8893,17 +8892,17 @@
       <c r="M75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>616675</v>
+        <v>616633</v>
       </c>
       <c r="R75" t="n">
-        <v>6651657</v>
+        <v>6651595</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8932,7 +8931,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8942,7 +8941,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8957,24 +8956,24 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137326762</t>
+          <t>https://artportalen.se/Sighting/137273225</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>137364335</v>
+        <v>137326762</v>
       </c>
       <c r="B76" t="n">
         <v>58032</v>
@@ -9003,23 +9002,20 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>616719</v>
+        <v>616675</v>
       </c>
       <c r="R76" t="n">
-        <v>6651691</v>
+        <v>6651657</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9048,7 +9044,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9058,7 +9054,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9073,24 +9069,24 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137364335</t>
+          <t>https://artportalen.se/Sighting/137326762</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>137365242</v>
+        <v>137364335</v>
       </c>
       <c r="B77" t="n">
         <v>58032</v>
@@ -9125,17 +9121,17 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>StHalsjon14okt2026 (1), Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>616588</v>
+        <v>616719</v>
       </c>
       <c r="R77" t="n">
-        <v>6651688</v>
+        <v>6651691</v>
       </c>
       <c r="S77" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9164,7 +9160,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9174,7 +9170,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9189,27 +9185,27 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137365242</t>
+          <t>https://artportalen.se/Sighting/137364335</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120510212</v>
+        <v>137365242</v>
       </c>
       <c r="B78" t="n">
-        <v>57141</v>
+        <v>58032</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9217,42 +9213,41 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>StHalsjon14okt2026 (1), Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>616701</v>
+        <v>616588</v>
       </c>
       <c r="R78" t="n">
-        <v>6651514</v>
+        <v>6651688</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9276,27 +9271,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Fjäderpenna på häll.</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9311,27 +9301,27 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510212</t>
+          <t>https://artportalen.se/Sighting/137365242</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>137273224</v>
+        <v>120510212</v>
       </c>
       <c r="B79" t="n">
-        <v>57221</v>
+        <v>57141</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9357,20 +9347,21 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>616823</v>
+        <v>616701</v>
       </c>
       <c r="R79" t="n">
-        <v>6651621</v>
+        <v>6651514</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9397,22 +9388,27 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Fjäderpenna på häll.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9427,70 +9423,69 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273224</t>
+          <t>https://artportalen.se/Sighting/120510212</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120510599</v>
+        <v>137273224</v>
       </c>
       <c r="B80" t="n">
-        <v>6284</v>
+        <v>57221</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100524</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovlig flatbagge</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Calitys scabra</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Thunberg, 1784)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>616710</v>
+        <v>616823</v>
       </c>
       <c r="R80" t="n">
-        <v>6651594</v>
+        <v>6651621</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9514,12 +9509,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9528,34 +9533,33 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510599</t>
+          <t>https://artportalen.se/Sighting/137273224</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>136866779</v>
+        <v>137408208</v>
       </c>
       <c r="B81" t="n">
-        <v>5188</v>
+        <v>57221</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9563,37 +9567,38 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>616605</v>
+        <v>616830</v>
       </c>
       <c r="R81" t="n">
-        <v>6651693</v>
+        <v>6651776</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9617,22 +9622,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9647,74 +9652,70 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866779</t>
+          <t>https://artportalen.se/Sighting/137408208</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120541190</v>
+        <v>120510599</v>
       </c>
       <c r="B82" t="n">
-        <v>44177</v>
+        <v>6284</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>101735</v>
+        <v>100524</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Skrovlig flatbagge</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Calitys scabra</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Thunberg, 1784)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>616925</v>
+        <v>616710</v>
       </c>
       <c r="R82" t="n">
-        <v>6651481</v>
+        <v>6651594</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9759,74 +9760,65 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541190</t>
+          <t>https://artportalen.se/Sighting/120510599</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120510178</v>
+        <v>136866779</v>
       </c>
       <c r="B83" t="n">
-        <v>5482</v>
+        <v>5188</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>101920</v>
+        <v>100526</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>616618</v>
+        <v>616605</v>
       </c>
       <c r="R83" t="n">
-        <v>6651514</v>
+        <v>6651693</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9850,12 +9842,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9864,56 +9866,55 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510178</t>
+          <t>https://artportalen.se/Sighting/136866779</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120510277</v>
+        <v>120541190</v>
       </c>
       <c r="B84" t="n">
-        <v>5482</v>
+        <v>44177</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>101920</v>
+        <v>101735</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9922,23 +9923,23 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>616622</v>
+        <v>616925</v>
       </c>
       <c r="R84" t="n">
-        <v>6651505</v>
+        <v>6651481</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9983,71 +9984,62 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120510277</t>
+          <t>https://artportalen.se/Sighting/120541190</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120511479</v>
+        <v>137408229</v>
       </c>
       <c r="B85" t="n">
-        <v>5482</v>
+        <v>44236</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>101920</v>
+        <v>101735</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>616731</v>
+        <v>616921</v>
       </c>
       <c r="R85" t="n">
-        <v>6651699</v>
+        <v>6651583</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10074,12 +10066,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10088,31 +10090,30 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511479</t>
+          <t>https://artportalen.se/Sighting/137408229</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120512577</v>
+        <v>120510178</v>
       </c>
       <c r="B86" t="n">
         <v>5482</v>
@@ -10152,14 +10153,14 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>616900</v>
+        <v>616618</v>
       </c>
       <c r="R86" t="n">
-        <v>6651584</v>
+        <v>6651514</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10218,13 +10219,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120512577</t>
+          <t>https://artportalen.se/Sighting/120510178</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120519343</v>
+        <v>120510277</v>
       </c>
       <c r="B87" t="n">
         <v>5482</v>
@@ -10268,10 +10269,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>616603</v>
+        <v>616622</v>
       </c>
       <c r="R87" t="n">
-        <v>6651619</v>
+        <v>6651505</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10330,13 +10331,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519343</t>
+          <t>https://artportalen.se/Sighting/120510277</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120590194</v>
+        <v>120511479</v>
       </c>
       <c r="B88" t="n">
         <v>5482</v>
@@ -10365,19 +10366,28 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, söder om, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>616745</v>
+        <v>616731</v>
       </c>
       <c r="R88" t="n">
-        <v>6651703</v>
+        <v>6651699</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10415,33 +10425,34 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120590194</t>
+          <t>https://artportalen.se/Sighting/120511479</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>137250004</v>
+        <v>120512577</v>
       </c>
       <c r="B89" t="n">
-        <v>5491</v>
+        <v>5482</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10467,19 +10478,28 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>616876</v>
+        <v>616900</v>
       </c>
       <c r="R89" t="n">
-        <v>6651538</v>
+        <v>6651584</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10503,22 +10523,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10527,62 +10537,67 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250004</t>
+          <t>https://artportalen.se/Sighting/120512577</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120511338</v>
+        <v>120519343</v>
       </c>
       <c r="B90" t="n">
-        <v>4781</v>
+        <v>5482</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>102306</v>
+        <v>101920</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10590,10 +10605,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>616705</v>
+        <v>616603</v>
       </c>
       <c r="R90" t="n">
-        <v>6651732</v>
+        <v>6651619</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10652,63 +10667,54 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511338</t>
+          <t>https://artportalen.se/Sighting/120519343</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120541184</v>
+        <v>120590194</v>
       </c>
       <c r="B91" t="n">
-        <v>4781</v>
+        <v>5482</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>102306</v>
+        <v>101920</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>616800</v>
+        <v>616745</v>
       </c>
       <c r="R91" t="n">
-        <v>6651576</v>
+        <v>6651703</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10746,81 +10752,71 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541184</t>
+          <t>https://artportalen.se/Sighting/120590194</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120541185</v>
+        <v>137250004</v>
       </c>
       <c r="B92" t="n">
-        <v>4781</v>
+        <v>5491</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>102306</v>
+        <v>101920</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>616723</v>
+        <v>616876</v>
       </c>
       <c r="R92" t="n">
-        <v>6651708</v>
+        <v>6651538</v>
       </c>
       <c r="S92" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10844,12 +10840,22 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10858,80 +10864,76 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541185</t>
+          <t>https://artportalen.se/Sighting/137250004</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120666046</v>
+        <v>120511338</v>
       </c>
       <c r="B93" t="n">
-        <v>58114</v>
+        <v>4781</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, söder om, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>616874</v>
+        <v>616705</v>
       </c>
       <c r="R93" t="n">
-        <v>6651669</v>
+        <v>6651732</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10969,72 +10971,81 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120666046</t>
+          <t>https://artportalen.se/Sighting/120511338</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>136866768</v>
+        <v>120541184</v>
       </c>
       <c r="B94" t="n">
-        <v>58196</v>
+        <v>4781</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>616676</v>
+        <v>616800</v>
       </c>
       <c r="R94" t="n">
-        <v>6651546</v>
+        <v>6651576</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11058,22 +11069,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11082,72 +11083,81 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866768</t>
+          <t>https://artportalen.se/Sighting/120541184</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>136866770</v>
+        <v>120541185</v>
       </c>
       <c r="B95" t="n">
-        <v>58196</v>
+        <v>4781</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>616702</v>
+        <v>616723</v>
       </c>
       <c r="R95" t="n">
-        <v>6651635</v>
+        <v>6651708</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11171,22 +11181,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>14:34</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>14:34</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11195,33 +11195,34 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866770</t>
+          <t>https://artportalen.se/Sighting/120541185</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>137250006</v>
+        <v>120666046</v>
       </c>
       <c r="B96" t="n">
-        <v>58196</v>
+        <v>58114</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11247,20 +11248,27 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>Stora Hålsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>616867</v>
+        <v>616874</v>
       </c>
       <c r="R96" t="n">
-        <v>6651589</v>
+        <v>6651669</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11284,22 +11292,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>11:19</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>11:19</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11314,24 +11312,24 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250006</t>
+          <t>https://artportalen.se/Sighting/120666046</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>137364331</v>
+        <v>136866768</v>
       </c>
       <c r="B97" t="n">
         <v>58196</v>
@@ -11359,25 +11357,18 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>616886</v>
+        <v>616676</v>
       </c>
       <c r="R97" t="n">
-        <v>6651567</v>
+        <v>6651546</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11404,22 +11395,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11434,24 +11425,24 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137364331</t>
+          <t>https://artportalen.se/Sighting/136866768</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>137400529</v>
+        <v>136866770</v>
       </c>
       <c r="B98" t="n">
         <v>58196</v>
@@ -11480,16 +11471,17 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Stora Hålsjön2, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>616756</v>
+        <v>616702</v>
       </c>
       <c r="R98" t="n">
-        <v>6651695</v>
+        <v>6651635</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11516,27 +11508,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Upprörd/varbande</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11551,24 +11538,24 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137400529</t>
+          <t>https://artportalen.se/Sighting/136866770</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>137400531</v>
+        <v>137250006</v>
       </c>
       <c r="B99" t="n">
         <v>58196</v>
@@ -11597,23 +11584,20 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Stora Hålsjön2, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>616904</v>
+        <v>616867</v>
       </c>
       <c r="R99" t="n">
-        <v>6651545</v>
+        <v>6651589</v>
       </c>
       <c r="S99" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11637,27 +11621,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11672,24 +11651,24 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137400531</t>
+          <t>https://artportalen.se/Sighting/137250006</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>137404140</v>
+        <v>137364331</v>
       </c>
       <c r="B100" t="n">
         <v>58196</v>
@@ -11728,14 +11707,14 @@
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Söder om Stora Hålsjön, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q100" t="n">
         <v>616886</v>
       </c>
       <c r="R100" t="n">
-        <v>6651592</v>
+        <v>6651567</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11762,22 +11741,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11792,66 +11771,65 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137404140</t>
+          <t>https://artportalen.se/Sighting/137364331</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>137326759</v>
+        <v>137400529</v>
       </c>
       <c r="B101" t="n">
-        <v>58191</v>
+        <v>58196</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>Stora Hålsjön2, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>616916</v>
+        <v>616756</v>
       </c>
       <c r="R101" t="n">
-        <v>6651561</v>
+        <v>6651695</v>
       </c>
       <c r="S101" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11875,22 +11853,27 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Upprörd/varbande</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11905,49 +11888,49 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137326759</t>
+          <t>https://artportalen.se/Sighting/137400529</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>137404128</v>
+        <v>137400531</v>
       </c>
       <c r="B102" t="n">
-        <v>58191</v>
+        <v>58196</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11957,17 +11940,17 @@
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Söder om Stora Hålsjön, Upl</t>
+          <t>Stora Hålsjön2, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>616769</v>
+        <v>616904</v>
       </c>
       <c r="R102" t="n">
-        <v>6651687</v>
+        <v>6651545</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11996,7 +11979,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12006,7 +11989,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12021,27 +12009,27 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137404128</t>
+          <t>https://artportalen.se/Sighting/137400531</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120519559</v>
+        <v>137404140</v>
       </c>
       <c r="B103" t="n">
-        <v>5004</v>
+        <v>58196</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12049,46 +12037,45 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>105212</v>
+        <v>103021</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Söder om Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>616596</v>
+        <v>616886</v>
       </c>
       <c r="R103" t="n">
-        <v>6651599</v>
+        <v>6651592</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12112,12 +12099,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12126,34 +12123,33 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519559</t>
+          <t>https://artportalen.se/Sighting/137404140</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120519563</v>
+        <v>137326759</v>
       </c>
       <c r="B104" t="n">
-        <v>5199</v>
+        <v>58191</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12161,16 +12157,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>105930</v>
+        <v>103023</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -12179,28 +12175,20 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>616596</v>
+        <v>616916</v>
       </c>
       <c r="R104" t="n">
-        <v>6651599</v>
+        <v>6651561</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12224,12 +12212,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12238,34 +12236,33 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519563</t>
+          <t>https://artportalen.se/Sighting/137326759</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>136866778</v>
+        <v>137404128</v>
       </c>
       <c r="B105" t="n">
-        <v>5208</v>
+        <v>58191</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12273,16 +12270,16 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>105930</v>
+        <v>103023</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -12291,19 +12288,23 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Söder om Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>616599</v>
+        <v>616769</v>
       </c>
       <c r="R105" t="n">
-        <v>6651694</v>
+        <v>6651687</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12327,22 +12328,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12357,74 +12358,74 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866778</t>
+          <t>https://artportalen.se/Sighting/137404128</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120541189</v>
+        <v>120519559</v>
       </c>
       <c r="B106" t="n">
-        <v>8444</v>
+        <v>5004</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106554</v>
+        <v>105212</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>616925</v>
+        <v>616596</v>
       </c>
       <c r="R106" t="n">
-        <v>6651481</v>
+        <v>6651599</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12469,27 +12470,27 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541189</t>
+          <t>https://artportalen.se/Sighting/120519559</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>137250005</v>
+        <v>120519563</v>
       </c>
       <c r="B107" t="n">
-        <v>8459</v>
+        <v>5199</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12497,37 +12498,46 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>616838</v>
+        <v>616596</v>
       </c>
       <c r="R107" t="n">
-        <v>6651458</v>
+        <v>6651599</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12551,22 +12561,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12575,33 +12575,34 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250005</t>
+          <t>https://artportalen.se/Sighting/120519563</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120511304</v>
+        <v>136866778</v>
       </c>
       <c r="B108" t="n">
-        <v>58790</v>
+        <v>5208</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12609,16 +12610,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>208245</v>
+        <v>105930</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -12629,17 +12630,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>616728</v>
+        <v>616599</v>
       </c>
       <c r="R108" t="n">
-        <v>6651675</v>
+        <v>6651694</v>
       </c>
       <c r="S108" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12663,22 +12664,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12693,27 +12694,27 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511304</t>
+          <t>https://artportalen.se/Sighting/136866778</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120512658</v>
+        <v>120541189</v>
       </c>
       <c r="B109" t="n">
-        <v>40269</v>
+        <v>8444</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12721,42 +12722,46 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>214815</v>
+        <v>106554</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Större träfjäril</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cossus cossus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>616900</v>
+        <v>616925</v>
       </c>
       <c r="R109" t="n">
-        <v>6651584</v>
+        <v>6651481</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12801,27 +12806,27 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120512658</t>
+          <t>https://artportalen.se/Sighting/120541189</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>137326757</v>
+        <v>137250005</v>
       </c>
       <c r="B110" t="n">
-        <v>99335</v>
+        <v>8459</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12829,37 +12834,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219790</v>
+        <v>106554</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>616746</v>
+        <v>616838</v>
       </c>
       <c r="R110" t="n">
-        <v>6651625</v>
+        <v>6651458</v>
       </c>
       <c r="S110" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12888,7 +12893,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12898,7 +12903,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12913,79 +12918,65 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137326757</t>
+          <t>https://artportalen.se/Sighting/137250005</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120511748</v>
+        <v>120511304</v>
       </c>
       <c r="B111" t="n">
-        <v>99118</v>
+        <v>58790</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>616739</v>
+        <v>616728</v>
       </c>
       <c r="R111" t="n">
-        <v>6651702</v>
+        <v>6651675</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13014,7 +13005,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13024,7 +13015,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13039,69 +13030,70 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511748</t>
+          <t>https://artportalen.se/Sighting/120511304</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120551257</v>
+        <v>120512658</v>
       </c>
       <c r="B112" t="n">
-        <v>99118</v>
+        <v>40269</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>214815</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Större träfjäril</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cossus cossus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>616797</v>
+        <v>616900</v>
       </c>
       <c r="R112" t="n">
-        <v>6651566</v>
+        <v>6651584</v>
       </c>
       <c r="S112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13128,101 +13120,83 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551257</t>
+          <t>https://artportalen.se/Sighting/120512658</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>136866776</v>
+        <v>137326757</v>
       </c>
       <c r="B113" t="n">
-        <v>99418</v>
+        <v>99335</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>616618</v>
+        <v>616746</v>
       </c>
       <c r="R113" t="n">
-        <v>6651762</v>
+        <v>6651625</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13246,22 +13220,22 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13276,27 +13250,27 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866776</t>
+          <t>https://artportalen.se/Sighting/137326757</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>137250001</v>
+        <v>120511748</v>
       </c>
       <c r="B114" t="n">
-        <v>99418</v>
+        <v>99118</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13321,20 +13295,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>616795</v>
+        <v>616739</v>
       </c>
       <c r="R114" t="n">
-        <v>6651571</v>
+        <v>6651702</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13358,22 +13346,22 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13388,27 +13376,27 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250001</t>
+          <t>https://artportalen.se/Sighting/120511748</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>137250011</v>
+        <v>120551257</v>
       </c>
       <c r="B115" t="n">
-        <v>99418</v>
+        <v>99118</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13433,22 +13421,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>616616</v>
+        <v>616797</v>
       </c>
       <c r="R115" t="n">
-        <v>6651766</v>
+        <v>6651566</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13475,22 +13462,22 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13505,24 +13492,24 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250011</t>
+          <t>https://artportalen.se/Sighting/120551257</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>137273220</v>
+        <v>136866776</v>
       </c>
       <c r="B116" t="n">
         <v>99418</v>
@@ -13552,27 +13539,27 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>616624</v>
+        <v>616618</v>
       </c>
       <c r="R116" t="n">
-        <v>6651761</v>
+        <v>6651762</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13596,22 +13583,22 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13626,24 +13613,24 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273220</t>
+          <t>https://artportalen.se/Sighting/136866776</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>137273221</v>
+        <v>137250001</v>
       </c>
       <c r="B117" t="n">
         <v>99418</v>
@@ -13671,29 +13658,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>616609</v>
+        <v>616795</v>
       </c>
       <c r="R117" t="n">
-        <v>6651753</v>
+        <v>6651571</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13722,7 +13700,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13732,7 +13710,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13747,24 +13725,24 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273221</t>
+          <t>https://artportalen.se/Sighting/137250001</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>137364328</v>
+        <v>137250011</v>
       </c>
       <c r="B118" t="n">
         <v>99418</v>
@@ -13792,29 +13770,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>616802</v>
+        <v>616616</v>
       </c>
       <c r="R118" t="n">
-        <v>6651571</v>
+        <v>6651766</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13846,7 +13817,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13856,7 +13827,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13865,31 +13836,30 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137364328</t>
+          <t>https://artportalen.se/Sighting/137250011</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>137365241</v>
+        <v>137273220</v>
       </c>
       <c r="B119" t="n">
         <v>99418</v>
@@ -13917,24 +13887,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>StHalsjon14okt2026 (1), Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>616585</v>
+        <v>616624</v>
       </c>
       <c r="R119" t="n">
-        <v>6651711</v>
+        <v>6651761</v>
       </c>
       <c r="S119" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13963,7 +13938,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13973,7 +13948,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13982,72 +13957,80 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137365241</t>
+          <t>https://artportalen.se/Sighting/137273220</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120551249</v>
+        <v>137273221</v>
       </c>
       <c r="B120" t="n">
-        <v>97983</v>
+        <v>99418</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>616771</v>
+        <v>616609</v>
       </c>
       <c r="R120" t="n">
-        <v>6651647</v>
+        <v>6651753</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14071,12 +14054,22 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14091,62 +14084,74 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551249</t>
+          <t>https://artportalen.se/Sighting/137273221</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120551250</v>
+        <v>137364328</v>
       </c>
       <c r="B121" t="n">
-        <v>97983</v>
+        <v>99418</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>616787</v>
+        <v>616802</v>
       </c>
       <c r="R121" t="n">
-        <v>6651642</v>
+        <v>6651571</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14173,12 +14178,22 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14187,71 +14202,76 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551250</t>
+          <t>https://artportalen.se/Sighting/137364328</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120511185</v>
+        <v>137365241</v>
       </c>
       <c r="B122" t="n">
-        <v>97986</v>
+        <v>99418</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>StHalsjon14okt2026 (1), Upl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>616730</v>
+        <v>616585</v>
       </c>
       <c r="R122" t="n">
-        <v>6651675</v>
+        <v>6651711</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14275,22 +14295,22 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14299,55 +14319,56 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511185</t>
+          <t>https://artportalen.se/Sighting/137365241</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120551251</v>
+        <v>120551249</v>
       </c>
       <c r="B123" t="n">
-        <v>92328</v>
+        <v>97983</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6040162</v>
+        <v>221945</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14357,10 +14378,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>616656</v>
+        <v>616771</v>
       </c>
       <c r="R123" t="n">
-        <v>6651527</v>
+        <v>6651647</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14417,6 +14438,322 @@
       </c>
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120551249</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>120551250</v>
+      </c>
+      <c r="B124" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>616787</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6651642</v>
+      </c>
+      <c r="S124" t="n">
+        <v>5</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120551250</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>120511185</v>
+      </c>
+      <c r="B125" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>616730</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6651675</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511185</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>120551251</v>
+      </c>
+      <c r="B126" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>616656</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6651527</v>
+      </c>
+      <c r="S126" t="n">
+        <v>5</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/120551251</t>
         </is>
@@ -14546,6 +14883,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39562-2026 artfynd.xlsx
+++ b/artfynd/A 39562-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137365067</v>
       </c>
       <c r="B3" t="n">
-        <v>83504</v>
+        <v>83515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136866766</v>
       </c>
       <c r="B7" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>136866780</v>
       </c>
       <c r="B8" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>137250010</v>
       </c>
       <c r="B9" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>137400528</v>
       </c>
       <c r="B10" t="n">
-        <v>91699</v>
+        <v>91711</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>137252175</v>
       </c>
       <c r="B11" t="n">
-        <v>81490</v>
+        <v>81501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>137364334</v>
       </c>
       <c r="B12" t="n">
-        <v>81490</v>
+        <v>81501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>137365049</v>
       </c>
       <c r="B13" t="n">
-        <v>81490</v>
+        <v>81501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>137365051</v>
       </c>
       <c r="B14" t="n">
-        <v>81490</v>
+        <v>81501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>137365052</v>
       </c>
       <c r="B15" t="n">
-        <v>81490</v>
+        <v>81501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>137365062</v>
       </c>
       <c r="B16" t="n">
-        <v>81490</v>
+        <v>81501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136866767</v>
       </c>
       <c r="B19" t="n">
-        <v>92805</v>
+        <v>92817</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>136866777</v>
       </c>
       <c r="B20" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>136866772</v>
       </c>
       <c r="B21" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137367392</v>
       </c>
       <c r="B22" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>136866774</v>
       </c>
       <c r="B26" t="n">
-        <v>96896</v>
+        <v>96908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>137365059</v>
       </c>
       <c r="B27" t="n">
-        <v>96896</v>
+        <v>96908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>137365060</v>
       </c>
       <c r="B28" t="n">
-        <v>96896</v>
+        <v>96908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>137365066</v>
       </c>
       <c r="B29" t="n">
-        <v>96896</v>
+        <v>96908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>137365068</v>
       </c>
       <c r="B30" t="n">
-        <v>96896</v>
+        <v>96908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>137250000</v>
       </c>
       <c r="B31" t="n">
-        <v>91945</v>
+        <v>91957</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>137364327</v>
       </c>
       <c r="B33" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>137326760</v>
       </c>
       <c r="B44" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>137364332</v>
       </c>
       <c r="B45" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>136866775</v>
       </c>
       <c r="B47" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>137365065</v>
       </c>
       <c r="B48" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>136866769</v>
       </c>
       <c r="B58" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>137250002</v>
       </c>
       <c r="B59" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>137250003</v>
       </c>
       <c r="B60" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>137250009</v>
       </c>
       <c r="B61" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>137326756</v>
       </c>
       <c r="B62" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>137326761</v>
       </c>
       <c r="B63" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>137326763</v>
       </c>
       <c r="B64" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>137365053</v>
       </c>
       <c r="B65" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>137365061</v>
       </c>
       <c r="B66" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         <v>137365063</v>
       </c>
       <c r="B67" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>137365064</v>
       </c>
       <c r="B68" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>137365069</v>
       </c>
       <c r="B69" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>137365070</v>
       </c>
       <c r="B70" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>137408230</v>
       </c>
       <c r="B71" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>137326757</v>
       </c>
       <c r="B113" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>136866776</v>
       </c>
       <c r="B116" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>137250001</v>
       </c>
       <c r="B117" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         <v>137250011</v>
       </c>
       <c r="B118" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>137273220</v>
       </c>
       <c r="B119" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>137273221</v>
       </c>
       <c r="B120" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>137364328</v>
       </c>
       <c r="B121" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>137365241</v>
       </c>
       <c r="B122" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 39562-2026 artfynd.xlsx
+++ b/artfynd/A 39562-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137365067</v>
       </c>
       <c r="B3" t="n">
-        <v>83515</v>
+        <v>83516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>137250010</v>
       </c>
       <c r="B9" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>137400528</v>
       </c>
       <c r="B10" t="n">
-        <v>91711</v>
+        <v>91712</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>137252175</v>
       </c>
       <c r="B11" t="n">
-        <v>81501</v>
+        <v>81502</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>137364334</v>
       </c>
       <c r="B12" t="n">
-        <v>81501</v>
+        <v>81502</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>137365049</v>
       </c>
       <c r="B13" t="n">
-        <v>81501</v>
+        <v>81502</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>137365051</v>
       </c>
       <c r="B14" t="n">
-        <v>81501</v>
+        <v>81502</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>137365052</v>
       </c>
       <c r="B15" t="n">
-        <v>81501</v>
+        <v>81502</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>137365062</v>
       </c>
       <c r="B16" t="n">
-        <v>81501</v>
+        <v>81502</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137367392</v>
       </c>
       <c r="B22" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>137365059</v>
       </c>
       <c r="B27" t="n">
-        <v>96908</v>
+        <v>96909</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>137365060</v>
       </c>
       <c r="B28" t="n">
-        <v>96908</v>
+        <v>96909</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>137365066</v>
       </c>
       <c r="B29" t="n">
-        <v>96908</v>
+        <v>96909</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>137365068</v>
       </c>
       <c r="B30" t="n">
-        <v>96908</v>
+        <v>96909</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>137250000</v>
       </c>
       <c r="B31" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>137364327</v>
       </c>
       <c r="B33" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>137326760</v>
       </c>
       <c r="B44" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>137364332</v>
       </c>
       <c r="B45" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>137365065</v>
       </c>
       <c r="B48" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>137250002</v>
       </c>
       <c r="B59" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>137250003</v>
       </c>
       <c r="B60" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>137250009</v>
       </c>
       <c r="B61" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>137326756</v>
       </c>
       <c r="B62" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>137326761</v>
       </c>
       <c r="B63" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>137326763</v>
       </c>
       <c r="B64" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>137365053</v>
       </c>
       <c r="B65" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>137365061</v>
       </c>
       <c r="B66" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         <v>137365063</v>
       </c>
       <c r="B67" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>137365064</v>
       </c>
       <c r="B68" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>137365069</v>
       </c>
       <c r="B69" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>137365070</v>
       </c>
       <c r="B70" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>137408230</v>
       </c>
       <c r="B71" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>137326757</v>
       </c>
       <c r="B113" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>137250001</v>
       </c>
       <c r="B117" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         <v>137250011</v>
       </c>
       <c r="B118" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>137273220</v>
       </c>
       <c r="B119" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>137273221</v>
       </c>
       <c r="B120" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>137364328</v>
       </c>
       <c r="B121" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>137365241</v>
       </c>
       <c r="B122" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 39562-2026 artfynd.xlsx
+++ b/artfynd/A 39562-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ126"/>
+  <dimension ref="A1:AZ130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,7 +785,7 @@
         <v>137365067</v>
       </c>
       <c r="B3" t="n">
-        <v>83516</v>
+        <v>83518</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>137250010</v>
       </c>
       <c r="B9" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>137400528</v>
       </c>
       <c r="B10" t="n">
-        <v>91712</v>
+        <v>91715</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>137252175</v>
       </c>
       <c r="B11" t="n">
-        <v>81502</v>
+        <v>81504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>137364334</v>
       </c>
       <c r="B12" t="n">
-        <v>81502</v>
+        <v>81504</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>137365049</v>
       </c>
       <c r="B13" t="n">
-        <v>81502</v>
+        <v>81504</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>137365051</v>
       </c>
       <c r="B14" t="n">
-        <v>81502</v>
+        <v>81504</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>137365052</v>
       </c>
       <c r="B15" t="n">
-        <v>81502</v>
+        <v>81504</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>137365062</v>
       </c>
       <c r="B16" t="n">
-        <v>81502</v>
+        <v>81504</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137367392</v>
       </c>
       <c r="B22" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>137365059</v>
       </c>
       <c r="B27" t="n">
-        <v>96909</v>
+        <v>96912</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>137365060</v>
       </c>
       <c r="B28" t="n">
-        <v>96909</v>
+        <v>96912</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>137365066</v>
       </c>
       <c r="B29" t="n">
-        <v>96909</v>
+        <v>96912</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>137365068</v>
       </c>
       <c r="B30" t="n">
-        <v>96909</v>
+        <v>96912</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>137250000</v>
       </c>
       <c r="B31" t="n">
-        <v>91958</v>
+        <v>91961</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>137364327</v>
       </c>
       <c r="B33" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>137326760</v>
       </c>
       <c r="B44" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>137364332</v>
       </c>
       <c r="B45" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>137365065</v>
       </c>
       <c r="B48" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>137250002</v>
       </c>
       <c r="B59" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>137250003</v>
       </c>
       <c r="B60" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>137250009</v>
       </c>
       <c r="B61" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>137326756</v>
       </c>
       <c r="B62" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>137326761</v>
       </c>
       <c r="B63" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>137326763</v>
       </c>
       <c r="B64" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>137365053</v>
       </c>
       <c r="B65" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>137365061</v>
       </c>
       <c r="B66" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         <v>137365063</v>
       </c>
       <c r="B67" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>137365064</v>
       </c>
       <c r="B68" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>137365069</v>
       </c>
       <c r="B69" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>137365070</v>
       </c>
       <c r="B70" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>137408230</v>
       </c>
       <c r="B71" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -11219,10 +11219,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120666046</v>
+        <v>137453518</v>
       </c>
       <c r="B96" t="n">
-        <v>58114</v>
+        <v>58471</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11230,45 +11230,47 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, söder om, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>616874</v>
+        <v>616756</v>
       </c>
       <c r="R96" t="n">
-        <v>6651669</v>
+        <v>6651693</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11292,12 +11294,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>07:37</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>07:37</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11312,27 +11324,27 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120666046</t>
+          <t>https://artportalen.se/Sighting/137453518</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>136866768</v>
+        <v>120666046</v>
       </c>
       <c r="B97" t="n">
-        <v>58196</v>
+        <v>58114</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11358,20 +11370,27 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Stora Hålsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>616676</v>
+        <v>616874</v>
       </c>
       <c r="R97" t="n">
-        <v>6651546</v>
+        <v>6651669</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11395,22 +11414,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11425,24 +11434,24 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866768</t>
+          <t>https://artportalen.se/Sighting/120666046</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>136866770</v>
+        <v>136866768</v>
       </c>
       <c r="B98" t="n">
         <v>58196</v>
@@ -11478,10 +11487,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>616702</v>
+        <v>616676</v>
       </c>
       <c r="R98" t="n">
-        <v>6651635</v>
+        <v>6651546</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11513,7 +11522,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11523,7 +11532,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11549,13 +11558,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866770</t>
+          <t>https://artportalen.se/Sighting/136866768</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>137250006</v>
+        <v>136866770</v>
       </c>
       <c r="B99" t="n">
         <v>58196</v>
@@ -11587,14 +11596,14 @@
       <c r="M99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>616867</v>
+        <v>616702</v>
       </c>
       <c r="R99" t="n">
-        <v>6651589</v>
+        <v>6651635</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11621,22 +11630,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11662,13 +11671,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250006</t>
+          <t>https://artportalen.se/Sighting/136866770</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>137364331</v>
+        <v>137250006</v>
       </c>
       <c r="B100" t="n">
         <v>58196</v>
@@ -11696,25 +11705,18 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>616886</v>
+        <v>616867</v>
       </c>
       <c r="R100" t="n">
-        <v>6651567</v>
+        <v>6651589</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11746,7 +11748,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11756,7 +11758,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11771,24 +11773,24 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137364331</t>
+          <t>https://artportalen.se/Sighting/137250006</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>137400529</v>
+        <v>137364331</v>
       </c>
       <c r="B101" t="n">
         <v>58196</v>
@@ -11816,17 +11818,25 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Stora Hålsjön2, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>616756</v>
+        <v>616886</v>
       </c>
       <c r="R101" t="n">
-        <v>6651695</v>
+        <v>6651567</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11853,27 +11863,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Upprörd/varbande</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11899,13 +11904,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137400529</t>
+          <t>https://artportalen.se/Sighting/137364331</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>137400531</v>
+        <v>137400529</v>
       </c>
       <c r="B102" t="n">
         <v>58196</v>
@@ -11934,23 +11939,19 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Stora Hålsjön2, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>616904</v>
+        <v>616756</v>
       </c>
       <c r="R102" t="n">
-        <v>6651545</v>
+        <v>6651695</v>
       </c>
       <c r="S102" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11979,7 +11980,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11989,12 +11990,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Lockläte</t>
+          <t>Upprörd/varbande</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12020,13 +12021,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137400531</t>
+          <t>https://artportalen.se/Sighting/137400529</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>137404140</v>
+        <v>137400531</v>
       </c>
       <c r="B103" t="n">
         <v>58196</v>
@@ -12054,28 +12055,24 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Söder om Stora Hålsjön, Upl</t>
+          <t>Stora Hålsjön2, Upl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>616886</v>
+        <v>616904</v>
       </c>
       <c r="R103" t="n">
-        <v>6651592</v>
+        <v>6651545</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12104,7 +12101,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12114,7 +12111,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12129,66 +12131,73 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137404140</t>
+          <t>https://artportalen.se/Sighting/137400531</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>137326759</v>
+        <v>137404140</v>
       </c>
       <c r="B104" t="n">
-        <v>58191</v>
+        <v>58196</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>Söder om Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>616916</v>
+        <v>616886</v>
       </c>
       <c r="R104" t="n">
-        <v>6651561</v>
+        <v>6651592</v>
       </c>
       <c r="S104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12212,22 +12221,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12242,69 +12251,75 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137326759</t>
+          <t>https://artportalen.se/Sighting/137404140</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>137404128</v>
+        <v>137453556</v>
       </c>
       <c r="B105" t="n">
-        <v>58191</v>
+        <v>58196</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Söder om Stora Hålsjön, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>616769</v>
+        <v>616756</v>
       </c>
       <c r="R105" t="n">
-        <v>6651687</v>
+        <v>6651693</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12328,22 +12343,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12358,44 +12373,44 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137404128</t>
+          <t>https://artportalen.se/Sighting/137453556</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120519559</v>
+        <v>137326759</v>
       </c>
       <c r="B106" t="n">
-        <v>5004</v>
+        <v>58191</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>105212</v>
+        <v>103023</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -12404,28 +12419,20 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>616596</v>
+        <v>616916</v>
       </c>
       <c r="R106" t="n">
-        <v>6651599</v>
+        <v>6651561</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12449,12 +12456,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12463,34 +12480,33 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519559</t>
+          <t>https://artportalen.se/Sighting/137326759</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120519563</v>
+        <v>137404128</v>
       </c>
       <c r="B107" t="n">
-        <v>5199</v>
+        <v>58191</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12498,16 +12514,16 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>105930</v>
+        <v>103023</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -12516,25 +12532,20 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Söder om Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>616596</v>
+        <v>616769</v>
       </c>
       <c r="R107" t="n">
-        <v>6651599</v>
+        <v>6651687</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12561,12 +12572,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12575,34 +12596,33 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519563</t>
+          <t>https://artportalen.se/Sighting/137404128</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>136866778</v>
+        <v>137453535</v>
       </c>
       <c r="B108" t="n">
-        <v>5208</v>
+        <v>58191</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12610,16 +12630,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>105930</v>
+        <v>103023</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -12627,17 +12647,27 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>616599</v>
+        <v>616756</v>
       </c>
       <c r="R108" t="n">
-        <v>6651694</v>
+        <v>6651693</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12664,22 +12694,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12694,27 +12724,27 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866778</t>
+          <t>https://artportalen.se/Sighting/137453535</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120541189</v>
+        <v>137453523</v>
       </c>
       <c r="B109" t="n">
-        <v>8444</v>
+        <v>58696</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12722,46 +12752,47 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106554</v>
+        <v>103046</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Gråsiska</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Acanthis flammea</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>616925</v>
+        <v>616756</v>
       </c>
       <c r="R109" t="n">
-        <v>6651481</v>
+        <v>6651693</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12785,12 +12816,22 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12799,72 +12840,80 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541189</t>
+          <t>https://artportalen.se/Sighting/137453523</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>137250005</v>
+        <v>120519559</v>
       </c>
       <c r="B110" t="n">
-        <v>8459</v>
+        <v>5004</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106554</v>
+        <v>105212</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>616838</v>
+        <v>616596</v>
       </c>
       <c r="R110" t="n">
-        <v>6651458</v>
+        <v>6651599</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12888,22 +12937,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12912,33 +12951,34 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250005</t>
+          <t>https://artportalen.se/Sighting/120519559</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120511304</v>
+        <v>120519563</v>
       </c>
       <c r="B111" t="n">
-        <v>58790</v>
+        <v>5199</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12946,16 +12986,16 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>208245</v>
+        <v>105930</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -12964,19 +13004,28 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>616728</v>
+        <v>616596</v>
       </c>
       <c r="R111" t="n">
-        <v>6651675</v>
+        <v>6651599</v>
       </c>
       <c r="S111" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13003,54 +13052,45 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511304</t>
+          <t>https://artportalen.se/Sighting/120519563</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120512658</v>
+        <v>136866778</v>
       </c>
       <c r="B112" t="n">
-        <v>40269</v>
+        <v>5208</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13058,16 +13098,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>214815</v>
+        <v>105930</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Större träfjäril</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cossus cossus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -13076,24 +13116,19 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>616900</v>
+        <v>616599</v>
       </c>
       <c r="R112" t="n">
-        <v>6651584</v>
+        <v>6651694</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13117,12 +13152,22 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13131,34 +13176,33 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120512658</t>
+          <t>https://artportalen.se/Sighting/136866778</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>137326757</v>
+        <v>120541189</v>
       </c>
       <c r="B113" t="n">
-        <v>99348</v>
+        <v>8444</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13166,37 +13210,46 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219790</v>
+        <v>106554</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>616746</v>
+        <v>616925</v>
       </c>
       <c r="R113" t="n">
-        <v>6651625</v>
+        <v>6651481</v>
       </c>
       <c r="S113" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13220,22 +13273,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>10:14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>10:14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13244,85 +13287,72 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137326757</t>
+          <t>https://artportalen.se/Sighting/120541189</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120511748</v>
+        <v>137250005</v>
       </c>
       <c r="B114" t="n">
-        <v>99118</v>
+        <v>8459</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>616739</v>
+        <v>616838</v>
       </c>
       <c r="R114" t="n">
-        <v>6651702</v>
+        <v>6651458</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13346,22 +13376,22 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13376,69 +13406,65 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511748</t>
+          <t>https://artportalen.se/Sighting/137250005</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120551257</v>
+        <v>120511304</v>
       </c>
       <c r="B115" t="n">
-        <v>99118</v>
+        <v>58790</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>616797</v>
+        <v>616728</v>
       </c>
       <c r="R115" t="n">
-        <v>6651566</v>
+        <v>6651675</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13467,7 +13493,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13477,7 +13503,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13492,74 +13518,70 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551257</t>
+          <t>https://artportalen.se/Sighting/120511304</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>136866776</v>
+        <v>120512658</v>
       </c>
       <c r="B116" t="n">
-        <v>99430</v>
+        <v>40269</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>214815</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Större träfjäril</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cossus cossus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>616618</v>
+        <v>616900</v>
       </c>
       <c r="R116" t="n">
-        <v>6651762</v>
+        <v>6651584</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13583,22 +13605,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13607,71 +13619,72 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866776</t>
+          <t>https://artportalen.se/Sighting/120512658</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>137250001</v>
+        <v>137326757</v>
       </c>
       <c r="B117" t="n">
-        <v>99431</v>
+        <v>99351</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>616795</v>
+        <v>616746</v>
       </c>
       <c r="R117" t="n">
-        <v>6651571</v>
+        <v>6651625</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13700,7 +13713,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13710,7 +13723,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13725,27 +13738,27 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250001</t>
+          <t>https://artportalen.se/Sighting/137326757</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>137250011</v>
+        <v>120511748</v>
       </c>
       <c r="B118" t="n">
-        <v>99431</v>
+        <v>99118</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13770,25 +13783,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>616616</v>
+        <v>616739</v>
       </c>
       <c r="R118" t="n">
-        <v>6651766</v>
+        <v>6651702</v>
       </c>
       <c r="S118" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13812,22 +13834,22 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13842,27 +13864,27 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250011</t>
+          <t>https://artportalen.se/Sighting/120511748</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>137273220</v>
+        <v>120551257</v>
       </c>
       <c r="B119" t="n">
-        <v>99431</v>
+        <v>99118</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13889,27 +13911,22 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>616624</v>
+        <v>616797</v>
       </c>
       <c r="R119" t="n">
-        <v>6651761</v>
+        <v>6651566</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13933,22 +13950,22 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13963,27 +13980,27 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273220</t>
+          <t>https://artportalen.se/Sighting/120551257</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>137273221</v>
+        <v>136866776</v>
       </c>
       <c r="B120" t="n">
-        <v>99431</v>
+        <v>99430</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14010,27 +14027,27 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>616609</v>
+        <v>616618</v>
       </c>
       <c r="R120" t="n">
-        <v>6651753</v>
+        <v>6651762</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14054,22 +14071,22 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14084,27 +14101,27 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273221</t>
+          <t>https://artportalen.se/Sighting/136866776</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>137364328</v>
+        <v>137250001</v>
       </c>
       <c r="B121" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14129,26 +14146,14 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>616802</v>
+        <v>616795</v>
       </c>
       <c r="R121" t="n">
         <v>6651571</v>
@@ -14183,7 +14188,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14193,7 +14198,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14202,34 +14207,33 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137364328</t>
+          <t>https://artportalen.se/Sighting/137250001</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>137365241</v>
+        <v>137250011</v>
       </c>
       <c r="B122" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14255,23 +14259,24 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>StHalsjon14okt2026 (1), Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>616585</v>
+        <v>616616</v>
       </c>
       <c r="R122" t="n">
-        <v>6651711</v>
+        <v>6651766</v>
       </c>
       <c r="S122" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14300,7 +14305,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14310,7 +14315,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14319,72 +14324,80 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137365241</t>
+          <t>https://artportalen.se/Sighting/137250011</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120551249</v>
+        <v>137273220</v>
       </c>
       <c r="B123" t="n">
-        <v>97983</v>
+        <v>99434</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>616771</v>
+        <v>616624</v>
       </c>
       <c r="R123" t="n">
-        <v>6651647</v>
+        <v>6651761</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14408,12 +14421,22 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14428,65 +14451,74 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551249</t>
+          <t>https://artportalen.se/Sighting/137273220</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120551250</v>
+        <v>137273221</v>
       </c>
       <c r="B124" t="n">
-        <v>97983</v>
+        <v>99434</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>616787</v>
+        <v>616609</v>
       </c>
       <c r="R124" t="n">
-        <v>6651642</v>
+        <v>6651753</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14510,12 +14542,22 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14530,65 +14572,77 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551250</t>
+          <t>https://artportalen.se/Sighting/137273221</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120511185</v>
+        <v>137364328</v>
       </c>
       <c r="B125" t="n">
-        <v>97986</v>
+        <v>99434</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>616730</v>
+        <v>616802</v>
       </c>
       <c r="R125" t="n">
-        <v>6651675</v>
+        <v>6651571</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14612,22 +14666,22 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14636,71 +14690,76 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511185</t>
+          <t>https://artportalen.se/Sighting/137364328</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120551251</v>
+        <v>137365241</v>
       </c>
       <c r="B126" t="n">
-        <v>92328</v>
+        <v>99434</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6040162</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>StHalsjon14okt2026 (1), Upl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>616656</v>
+        <v>616585</v>
       </c>
       <c r="R126" t="n">
-        <v>6651527</v>
+        <v>6651711</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14724,12 +14783,22 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14738,22 +14807,441 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137365241</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>120551249</v>
+      </c>
+      <c r="B127" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>616771</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6651647</v>
+      </c>
+      <c r="S127" t="n">
+        <v>5</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120551249</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>120551250</v>
+      </c>
+      <c r="B128" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>616787</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6651642</v>
+      </c>
+      <c r="S128" t="n">
+        <v>5</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120551250</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>120511185</v>
+      </c>
+      <c r="B129" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>616730</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6651675</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511185</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>120551251</v>
+      </c>
+      <c r="B130" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>616656</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6651527</v>
+      </c>
+      <c r="S130" t="n">
+        <v>5</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/120551251</t>
         </is>
@@ -14886,6 +15374,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39562-2026 artfynd.xlsx
+++ b/artfynd/A 39562-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ130"/>
+  <dimension ref="A1:AZ131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,7 +785,7 @@
         <v>137365067</v>
       </c>
       <c r="B3" t="n">
-        <v>83518</v>
+        <v>83522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>137250010</v>
       </c>
       <c r="B9" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>137400528</v>
       </c>
       <c r="B10" t="n">
-        <v>91715</v>
+        <v>91719</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>137252175</v>
       </c>
       <c r="B11" t="n">
-        <v>81504</v>
+        <v>81508</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>137364334</v>
       </c>
       <c r="B12" t="n">
-        <v>81504</v>
+        <v>81508</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>137365049</v>
       </c>
       <c r="B13" t="n">
-        <v>81504</v>
+        <v>81508</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>137365051</v>
       </c>
       <c r="B14" t="n">
-        <v>81504</v>
+        <v>81508</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>137365052</v>
       </c>
       <c r="B15" t="n">
-        <v>81504</v>
+        <v>81508</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>137365062</v>
       </c>
       <c r="B16" t="n">
-        <v>81504</v>
+        <v>81508</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137367392</v>
       </c>
       <c r="B22" t="n">
-        <v>92364</v>
+        <v>92368</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>137365059</v>
       </c>
       <c r="B27" t="n">
-        <v>96912</v>
+        <v>96916</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>137365060</v>
       </c>
       <c r="B28" t="n">
-        <v>96912</v>
+        <v>96916</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>137365066</v>
       </c>
       <c r="B29" t="n">
-        <v>96912</v>
+        <v>96916</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>137365068</v>
       </c>
       <c r="B30" t="n">
-        <v>96912</v>
+        <v>96916</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>137250000</v>
       </c>
       <c r="B31" t="n">
-        <v>91961</v>
+        <v>91965</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>137364327</v>
       </c>
       <c r="B33" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>137326760</v>
       </c>
       <c r="B44" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>137364332</v>
       </c>
       <c r="B45" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>137365065</v>
       </c>
       <c r="B48" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>137250002</v>
       </c>
       <c r="B59" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>137250003</v>
       </c>
       <c r="B60" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>137250009</v>
       </c>
       <c r="B61" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>137326756</v>
       </c>
       <c r="B62" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>137326761</v>
       </c>
       <c r="B63" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>137326763</v>
       </c>
       <c r="B64" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>137365053</v>
       </c>
       <c r="B65" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>137365061</v>
       </c>
       <c r="B66" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         <v>137365063</v>
       </c>
       <c r="B67" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>137365064</v>
       </c>
       <c r="B68" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>137365069</v>
       </c>
       <c r="B69" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>137365070</v>
       </c>
       <c r="B70" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>137408230</v>
       </c>
       <c r="B71" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>137273223</v>
       </c>
       <c r="B74" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>137273225</v>
       </c>
       <c r="B75" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>137326762</v>
       </c>
       <c r="B76" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>137364335</v>
       </c>
       <c r="B77" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>137365242</v>
       </c>
       <c r="B78" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>137273224</v>
       </c>
       <c r="B80" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>137408208</v>
       </c>
       <c r="B81" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>137453518</v>
       </c>
       <c r="B96" t="n">
-        <v>58471</v>
+        <v>58474</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>137250006</v>
       </c>
       <c r="B100" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>137364331</v>
       </c>
       <c r="B101" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>137400529</v>
       </c>
       <c r="B102" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>137400531</v>
       </c>
       <c r="B103" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>137404140</v>
       </c>
       <c r="B104" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>137453556</v>
       </c>
       <c r="B105" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12390,49 +12390,56 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>137326759</v>
+        <v>137529388</v>
       </c>
       <c r="B106" t="n">
-        <v>58191</v>
+        <v>58199</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>Stora Hålsjön2, Upl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>616916</v>
+        <v>616796</v>
       </c>
       <c r="R106" t="n">
-        <v>6651561</v>
+        <v>6651575</v>
       </c>
       <c r="S106" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12456,22 +12463,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12486,27 +12493,27 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137326759</t>
+          <t>https://artportalen.se/Sighting/137529388</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>137404128</v>
+        <v>137326759</v>
       </c>
       <c r="B107" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12532,23 +12539,20 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Söder om Stora Hålsjön, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>616769</v>
+        <v>616916</v>
       </c>
       <c r="R107" t="n">
-        <v>6651687</v>
+        <v>6651561</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12572,22 +12576,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12602,27 +12606,27 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137404128</t>
+          <t>https://artportalen.se/Sighting/137326759</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>137453535</v>
+        <v>137404128</v>
       </c>
       <c r="B108" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12647,30 +12651,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>Söder om Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>616756</v>
+        <v>616769</v>
       </c>
       <c r="R108" t="n">
-        <v>6651693</v>
+        <v>6651687</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12694,22 +12692,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12724,27 +12722,27 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137453535</t>
+          <t>https://artportalen.se/Sighting/137404128</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>137453523</v>
+        <v>137453535</v>
       </c>
       <c r="B109" t="n">
-        <v>58696</v>
+        <v>58194</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12752,16 +12750,16 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103046</v>
+        <v>103023</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gråsiska</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Acanthis flammea</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -12816,22 +12814,22 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12857,33 +12855,33 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137453523</t>
+          <t>https://artportalen.se/Sighting/137453535</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120519559</v>
+        <v>137453523</v>
       </c>
       <c r="B110" t="n">
-        <v>5004</v>
+        <v>58699</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>105212</v>
+        <v>103046</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Gråsiska</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Acanthis flammea</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -12891,29 +12889,30 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>616596</v>
+        <v>616756</v>
       </c>
       <c r="R110" t="n">
-        <v>6651599</v>
+        <v>6651693</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12937,12 +12936,22 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12951,51 +12960,50 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519559</t>
+          <t>https://artportalen.se/Sighting/137453523</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120519563</v>
+        <v>120519559</v>
       </c>
       <c r="B111" t="n">
-        <v>5199</v>
+        <v>5004</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>105930</v>
+        <v>105212</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -13081,16 +13089,16 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120519563</t>
+          <t>https://artportalen.se/Sighting/120519559</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>136866778</v>
+        <v>120519563</v>
       </c>
       <c r="B112" t="n">
-        <v>5208</v>
+        <v>5199</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13116,19 +13124,28 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>616599</v>
+        <v>616596</v>
       </c>
       <c r="R112" t="n">
-        <v>6651694</v>
+        <v>6651599</v>
       </c>
       <c r="S112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13152,22 +13169,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>15:34</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>15:34</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13176,33 +13183,34 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866778</t>
+          <t>https://artportalen.se/Sighting/120519563</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120541189</v>
+        <v>136866778</v>
       </c>
       <c r="B113" t="n">
-        <v>8444</v>
+        <v>5208</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13210,46 +13218,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>616925</v>
+        <v>616599</v>
       </c>
       <c r="R113" t="n">
-        <v>6651481</v>
+        <v>6651694</v>
       </c>
       <c r="S113" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13273,12 +13272,22 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13287,34 +13296,33 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120541189</t>
+          <t>https://artportalen.se/Sighting/136866778</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>137250005</v>
+        <v>120541189</v>
       </c>
       <c r="B114" t="n">
-        <v>8459</v>
+        <v>8444</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13340,19 +13348,28 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>616838</v>
+        <v>616925</v>
       </c>
       <c r="R114" t="n">
-        <v>6651458</v>
+        <v>6651481</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13376,22 +13393,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13400,33 +13407,34 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250005</t>
+          <t>https://artportalen.se/Sighting/120541189</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120511304</v>
+        <v>137250005</v>
       </c>
       <c r="B115" t="n">
-        <v>58790</v>
+        <v>8459</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13434,37 +13442,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>208245</v>
+        <v>106554</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>616728</v>
+        <v>616838</v>
       </c>
       <c r="R115" t="n">
-        <v>6651675</v>
+        <v>6651458</v>
       </c>
       <c r="S115" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13488,22 +13496,22 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13518,27 +13526,27 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511304</t>
+          <t>https://artportalen.se/Sighting/137250005</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120512658</v>
+        <v>120511304</v>
       </c>
       <c r="B116" t="n">
-        <v>40269</v>
+        <v>58790</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13546,16 +13554,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>214815</v>
+        <v>208245</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Större träfjäril</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cossus cossus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -13564,24 +13572,19 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Hjärtmossberget, Upl</t>
+          <t>Stora Hålsjön, Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>616900</v>
+        <v>616728</v>
       </c>
       <c r="R116" t="n">
-        <v>6651584</v>
+        <v>6651675</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13608,45 +13611,54 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120512658</t>
+          <t>https://artportalen.se/Sighting/120511304</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>137326757</v>
+        <v>120512658</v>
       </c>
       <c r="B117" t="n">
-        <v>99351</v>
+        <v>40269</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13654,37 +13666,42 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219790</v>
+        <v>214815</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Större träfjäril</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cossus cossus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>Hjärtmossberget, Upl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>616746</v>
+        <v>616900</v>
       </c>
       <c r="R117" t="n">
-        <v>6651625</v>
+        <v>6651584</v>
       </c>
       <c r="S117" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13708,22 +13725,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>10:14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>10:14</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13732,85 +13739,72 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137326757</t>
+          <t>https://artportalen.se/Sighting/120512658</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120511748</v>
+        <v>137326757</v>
       </c>
       <c r="B118" t="n">
-        <v>99118</v>
+        <v>99355</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>616739</v>
+        <v>616746</v>
       </c>
       <c r="R118" t="n">
-        <v>6651702</v>
+        <v>6651625</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13834,22 +13828,22 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13864,24 +13858,24 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Nora Toftgård Shahnavaz, Sebastian Kirppu, Emil V. Nilsson, Ebba Ganslandt</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511748</t>
+          <t>https://artportalen.se/Sighting/137326757</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120551257</v>
+        <v>120511748</v>
       </c>
       <c r="B119" t="n">
         <v>99118</v>
@@ -13911,7 +13905,17 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -13920,13 +13924,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>616797</v>
+        <v>616739</v>
       </c>
       <c r="R119" t="n">
-        <v>6651566</v>
+        <v>6651702</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13955,7 +13959,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13965,7 +13969,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13980,27 +13984,27 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551257</t>
+          <t>https://artportalen.se/Sighting/120511748</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>136866776</v>
+        <v>120551257</v>
       </c>
       <c r="B120" t="n">
-        <v>99430</v>
+        <v>99118</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14027,24 +14031,19 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>St Hålsjön S, Upl</t>
+          <t>Hjortmossberget, Upl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>616618</v>
+        <v>616797</v>
       </c>
       <c r="R120" t="n">
-        <v>6651762</v>
+        <v>6651566</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14071,22 +14070,22 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14101,27 +14100,27 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866776</t>
+          <t>https://artportalen.se/Sighting/120551257</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>137250001</v>
+        <v>136866776</v>
       </c>
       <c r="B121" t="n">
-        <v>99434</v>
+        <v>99430</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14146,17 +14145,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>st Hålsjön S, Upl</t>
+          <t>St Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>616795</v>
+        <v>616618</v>
       </c>
       <c r="R121" t="n">
-        <v>6651571</v>
+        <v>6651762</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14183,22 +14191,22 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14224,16 +14232,16 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250001</t>
+          <t>https://artportalen.se/Sighting/136866776</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>137250011</v>
+        <v>137250001</v>
       </c>
       <c r="B122" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14259,21 +14267,16 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>616616</v>
+        <v>616795</v>
       </c>
       <c r="R122" t="n">
-        <v>6651766</v>
+        <v>6651571</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14305,7 +14308,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14315,7 +14318,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14341,16 +14344,16 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137250011</t>
+          <t>https://artportalen.se/Sighting/137250001</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>137273220</v>
+        <v>137250011</v>
       </c>
       <c r="B123" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14375,29 +14378,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Stora Hålsjön, Upl</t>
+          <t>st Hålsjön S, Upl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>616624</v>
+        <v>616616</v>
       </c>
       <c r="R123" t="n">
-        <v>6651761</v>
+        <v>6651766</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14426,7 +14425,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14436,7 +14435,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14451,27 +14450,27 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273220</t>
+          <t>https://artportalen.se/Sighting/137250011</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>137273221</v>
+        <v>137273220</v>
       </c>
       <c r="B124" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14498,7 +14497,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -14512,10 +14511,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>616609</v>
+        <v>616624</v>
       </c>
       <c r="R124" t="n">
-        <v>6651753</v>
+        <v>6651761</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14547,7 +14546,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14557,7 +14556,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14583,16 +14582,16 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273221</t>
+          <t>https://artportalen.se/Sighting/137273220</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>137364328</v>
+        <v>137273221</v>
       </c>
       <c r="B125" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14619,7 +14618,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14627,22 +14626,19 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>616802</v>
+        <v>616609</v>
       </c>
       <c r="R125" t="n">
-        <v>6651571</v>
+        <v>6651753</v>
       </c>
       <c r="S125" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14671,7 +14667,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14681,7 +14677,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14690,34 +14686,33 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137364328</t>
+          <t>https://artportalen.se/Sighting/137273221</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>137365241</v>
+        <v>137364328</v>
       </c>
       <c r="B126" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14742,24 +14737,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>StHalsjon14okt2026 (1), Upl</t>
+          <t>Stora Hålsjön, Upl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>616585</v>
+        <v>616802</v>
       </c>
       <c r="R126" t="n">
-        <v>6651711</v>
+        <v>6651571</v>
       </c>
       <c r="S126" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14788,7 +14791,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14798,7 +14801,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14814,65 +14817,69 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137365241</t>
+          <t>https://artportalen.se/Sighting/137364328</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120551249</v>
+        <v>137365241</v>
       </c>
       <c r="B127" t="n">
-        <v>97983</v>
+        <v>99438</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Hjortmossberget, Upl</t>
+          <t>StHalsjon14okt2026 (1), Upl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>616771</v>
+        <v>616585</v>
       </c>
       <c r="R127" t="n">
-        <v>6651647</v>
+        <v>6651711</v>
       </c>
       <c r="S127" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14896,12 +14903,22 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14910,30 +14927,31 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551249</t>
+          <t>https://artportalen.se/Sighting/137365241</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120551250</v>
+        <v>120551249</v>
       </c>
       <c r="B128" t="n">
         <v>97983</v>
@@ -14968,10 +14986,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>616787</v>
+        <v>616771</v>
       </c>
       <c r="R128" t="n">
-        <v>6651642</v>
+        <v>6651647</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -15029,16 +15047,16 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120551250</t>
+          <t>https://artportalen.se/Sighting/120551249</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120511185</v>
+        <v>120551250</v>
       </c>
       <c r="B129" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15046,16 +15064,16 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -15070,13 +15088,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>616730</v>
+        <v>616787</v>
       </c>
       <c r="R129" t="n">
-        <v>6651675</v>
+        <v>6651642</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15103,19 +15121,9 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2024-10-20</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>10:40</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15130,49 +15138,49 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120511185</t>
+          <t>https://artportalen.se/Sighting/120551250</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120551251</v>
+        <v>120511185</v>
       </c>
       <c r="B130" t="n">
-        <v>92328</v>
+        <v>97986</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6040162</v>
+        <v>221946</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15182,13 +15190,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>616656</v>
+        <v>616730</v>
       </c>
       <c r="R130" t="n">
-        <v>6651527</v>
+        <v>6651675</v>
       </c>
       <c r="S130" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15215,9 +15223,19 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15232,16 +15250,118 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511185</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>120551251</v>
+      </c>
+      <c r="B131" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Hjortmossberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>616656</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6651527</v>
+      </c>
+      <c r="S131" t="n">
+        <v>5</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg, Nya Skogsgruppen</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/120551251</t>
         </is>
@@ -15378,6 +15498,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
